--- a/backend/forms/output_data/SF1_filled_output.xlsx
+++ b/backend/forms/output_data/SF1_filled_output.xlsx
@@ -248,18 +248,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -765,7 +759,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
@@ -789,16 +783,16 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="21" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="21" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="22" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="22" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="21" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="21" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="23" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="23" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="24" applyAlignment="1">
@@ -807,89 +801,89 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="25" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -950,24 +944,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1043,12 +1019,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1606,7 +1576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AU71"/>
+  <dimension ref="A1:AU68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6285714285714" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.1333333333333" customWidth="1" min="1" max="1"/>
@@ -1675,22 +1645,22 @@
           <t xml:space="preserve">School ID </t>
         </is>
       </c>
-      <c r="F3" s="53" t="n">
+      <c r="F3" s="47" t="n">
         <v>302550</v>
       </c>
-      <c r="G3" s="54" t="n"/>
-      <c r="H3" s="54" t="n"/>
-      <c r="I3" s="55" t="n"/>
+      <c r="G3" s="48" t="n"/>
+      <c r="H3" s="48" t="n"/>
+      <c r="I3" s="49" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="53" t="inlineStr">
+      <c r="K3" s="47" t="inlineStr">
         <is>
           <t>Region VI</t>
         </is>
       </c>
-      <c r="L3" s="54" t="n"/>
-      <c r="M3" s="54" t="n"/>
-      <c r="N3" s="54" t="n"/>
-      <c r="O3" s="55" t="n"/>
+      <c r="L3" s="48" t="n"/>
+      <c r="M3" s="48" t="n"/>
+      <c r="N3" s="48" t="n"/>
+      <c r="O3" s="49" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
@@ -1698,23 +1668,23 @@
         </is>
       </c>
       <c r="S3" s="2" t="n"/>
-      <c r="T3" s="53" t="inlineStr">
+      <c r="T3" s="47" t="inlineStr">
         <is>
           <t>Iloilo</t>
         </is>
       </c>
-      <c r="U3" s="54" t="n"/>
-      <c r="V3" s="54" t="n"/>
-      <c r="W3" s="54" t="n"/>
-      <c r="X3" s="54" t="n"/>
-      <c r="Y3" s="54" t="n"/>
-      <c r="Z3" s="54" t="n"/>
-      <c r="AA3" s="54" t="n"/>
-      <c r="AB3" s="54" t="n"/>
-      <c r="AC3" s="54" t="n"/>
-      <c r="AD3" s="54" t="n"/>
-      <c r="AE3" s="54" t="n"/>
-      <c r="AF3" s="55" t="n"/>
+      <c r="U3" s="48" t="n"/>
+      <c r="V3" s="48" t="n"/>
+      <c r="W3" s="48" t="n"/>
+      <c r="X3" s="48" t="n"/>
+      <c r="Y3" s="48" t="n"/>
+      <c r="Z3" s="48" t="n"/>
+      <c r="AA3" s="48" t="n"/>
+      <c r="AB3" s="48" t="n"/>
+      <c r="AC3" s="48" t="n"/>
+      <c r="AD3" s="48" t="n"/>
+      <c r="AE3" s="48" t="n"/>
+      <c r="AF3" s="49" t="n"/>
       <c r="AG3" s="2" t="n"/>
       <c r="AH3" s="2" t="n"/>
       <c r="AI3" s="2" t="n"/>
@@ -1737,31 +1707,35 @@
           <t xml:space="preserve">School Name </t>
         </is>
       </c>
-      <c r="F4" s="53" t="inlineStr">
+      <c r="F4" s="47" t="inlineStr">
         <is>
           <t>Pavia National High School</t>
         </is>
       </c>
-      <c r="G4" s="54" t="n"/>
-      <c r="H4" s="54" t="n"/>
-      <c r="I4" s="54" t="n"/>
-      <c r="J4" s="54" t="n"/>
-      <c r="K4" s="54" t="n"/>
-      <c r="L4" s="54" t="n"/>
-      <c r="M4" s="54" t="n"/>
-      <c r="N4" s="54" t="n"/>
-      <c r="O4" s="55" t="n"/>
+      <c r="G4" s="48" t="n"/>
+      <c r="H4" s="48" t="n"/>
+      <c r="I4" s="48" t="n"/>
+      <c r="J4" s="48" t="n"/>
+      <c r="K4" s="48" t="n"/>
+      <c r="L4" s="48" t="n"/>
+      <c r="M4" s="48" t="n"/>
+      <c r="N4" s="48" t="n"/>
+      <c r="O4" s="49" t="n"/>
       <c r="P4" s="2" t="n"/>
       <c r="Q4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">School Year </t>
         </is>
       </c>
-      <c r="T4" s="53" t="n"/>
-      <c r="U4" s="54" t="n"/>
-      <c r="V4" s="54" t="n"/>
-      <c r="W4" s="54" t="n"/>
-      <c r="X4" s="55" t="n"/>
+      <c r="T4" s="47" t="inlineStr">
+        <is>
+          <t>2026 - 2027</t>
+        </is>
+      </c>
+      <c r="U4" s="48" t="n"/>
+      <c r="V4" s="48" t="n"/>
+      <c r="W4" s="48" t="n"/>
+      <c r="X4" s="49" t="n"/>
       <c r="Y4" s="2" t="n"/>
       <c r="Z4" s="4" t="inlineStr">
         <is>
@@ -1769,9 +1743,11 @@
         </is>
       </c>
       <c r="AD4" s="2" t="n"/>
-      <c r="AE4" s="53" t="n"/>
-      <c r="AF4" s="54" t="n"/>
-      <c r="AG4" s="55" t="n"/>
+      <c r="AE4" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF4" s="48" t="n"/>
+      <c r="AG4" s="49" t="n"/>
       <c r="AH4" s="2" t="n"/>
       <c r="AI4" s="2" t="n"/>
       <c r="AJ4" s="4" t="inlineStr">
@@ -1779,15 +1755,19 @@
           <t xml:space="preserve">Section </t>
         </is>
       </c>
-      <c r="AM4" s="53" t="n"/>
-      <c r="AN4" s="54" t="n"/>
-      <c r="AO4" s="54" t="n"/>
-      <c r="AP4" s="54" t="n"/>
-      <c r="AQ4" s="54" t="n"/>
-      <c r="AR4" s="54" t="n"/>
-      <c r="AS4" s="54" t="n"/>
-      <c r="AT4" s="54" t="n"/>
-      <c r="AU4" s="55" t="n"/>
+      <c r="AM4" s="47" t="inlineStr">
+        <is>
+          <t>RIGEL</t>
+        </is>
+      </c>
+      <c r="AN4" s="48" t="n"/>
+      <c r="AO4" s="48" t="n"/>
+      <c r="AP4" s="48" t="n"/>
+      <c r="AQ4" s="48" t="n"/>
+      <c r="AR4" s="48" t="n"/>
+      <c r="AS4" s="48" t="n"/>
+      <c r="AT4" s="48" t="n"/>
+      <c r="AU4" s="49" t="n"/>
     </row>
     <row r="5" ht="24.75" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
@@ -1795,17 +1775,17 @@
           <t>LRN</t>
         </is>
       </c>
-      <c r="B5" s="56" t="n"/>
+      <c r="B5" s="50" t="n"/>
       <c r="C5" s="19" t="inlineStr">
         <is>
           <t>NAME
 (Last Name, First Name, Middle Name)</t>
         </is>
       </c>
-      <c r="D5" s="57" t="n"/>
-      <c r="E5" s="57" t="n"/>
-      <c r="F5" s="56" t="n"/>
-      <c r="G5" s="58" t="inlineStr">
+      <c r="D5" s="51" t="n"/>
+      <c r="E5" s="51" t="n"/>
+      <c r="F5" s="50" t="n"/>
+      <c r="G5" s="52" t="inlineStr">
         <is>
           <t>Sex (M/F)</t>
         </is>
@@ -1816,19 +1796,19 @@
 (mm/dd/yyyy)</t>
         </is>
       </c>
-      <c r="I5" s="56" t="n"/>
-      <c r="J5" s="59" t="inlineStr">
+      <c r="I5" s="50" t="n"/>
+      <c r="J5" s="53" t="inlineStr">
         <is>
           <t>AGE as of 1st Friday June</t>
         </is>
       </c>
-      <c r="K5" s="56" t="n"/>
+      <c r="K5" s="50" t="n"/>
       <c r="L5" s="19" t="inlineStr">
         <is>
           <t>MOTHER TONGUE (Grade 1 to 3 Only)</t>
         </is>
       </c>
-      <c r="M5" s="56" t="n"/>
+      <c r="M5" s="50" t="n"/>
       <c r="N5" s="19" t="inlineStr">
         <is>
           <t>IP
@@ -1845,46 +1825,46 @@
           <t>ADDRESS</t>
         </is>
       </c>
-      <c r="Q5" s="54" t="n"/>
-      <c r="R5" s="54" t="n"/>
-      <c r="S5" s="54" t="n"/>
-      <c r="T5" s="54" t="n"/>
-      <c r="U5" s="54" t="n"/>
-      <c r="V5" s="54" t="n"/>
-      <c r="W5" s="54" t="n"/>
-      <c r="X5" s="54" t="n"/>
-      <c r="Y5" s="54" t="n"/>
-      <c r="Z5" s="54" t="n"/>
-      <c r="AA5" s="55" t="n"/>
+      <c r="Q5" s="48" t="n"/>
+      <c r="R5" s="48" t="n"/>
+      <c r="S5" s="48" t="n"/>
+      <c r="T5" s="48" t="n"/>
+      <c r="U5" s="48" t="n"/>
+      <c r="V5" s="48" t="n"/>
+      <c r="W5" s="48" t="n"/>
+      <c r="X5" s="48" t="n"/>
+      <c r="Y5" s="48" t="n"/>
+      <c r="Z5" s="48" t="n"/>
+      <c r="AA5" s="49" t="n"/>
       <c r="AB5" s="19" t="inlineStr">
         <is>
           <t>PARENTS</t>
         </is>
       </c>
-      <c r="AC5" s="54" t="n"/>
-      <c r="AD5" s="54" t="n"/>
-      <c r="AE5" s="54" t="n"/>
-      <c r="AF5" s="54" t="n"/>
-      <c r="AG5" s="54" t="n"/>
-      <c r="AH5" s="54" t="n"/>
-      <c r="AI5" s="54" t="n"/>
-      <c r="AJ5" s="55" t="n"/>
+      <c r="AC5" s="48" t="n"/>
+      <c r="AD5" s="48" t="n"/>
+      <c r="AE5" s="48" t="n"/>
+      <c r="AF5" s="48" t="n"/>
+      <c r="AG5" s="48" t="n"/>
+      <c r="AH5" s="48" t="n"/>
+      <c r="AI5" s="48" t="n"/>
+      <c r="AJ5" s="49" t="n"/>
       <c r="AK5" s="19" t="inlineStr">
         <is>
           <t>GUARDIAN
 (if Not Parent)</t>
         </is>
       </c>
-      <c r="AL5" s="54" t="n"/>
-      <c r="AM5" s="54" t="n"/>
-      <c r="AN5" s="54" t="n"/>
-      <c r="AO5" s="55" t="n"/>
+      <c r="AL5" s="48" t="n"/>
+      <c r="AM5" s="48" t="n"/>
+      <c r="AN5" s="48" t="n"/>
+      <c r="AO5" s="49" t="n"/>
       <c r="AP5" s="19" t="inlineStr">
         <is>
           <t>Contact Number of Parent or Guardian</t>
         </is>
       </c>
-      <c r="AQ5" s="56" t="n"/>
+      <c r="AQ5" s="50" t="n"/>
       <c r="AR5" s="19" t="inlineStr">
         <is>
           <t>Learning Modality</t>
@@ -1895,92 +1875,92 @@
           <t>REMARKS</t>
         </is>
       </c>
-      <c r="AT5" s="55" t="n"/>
+      <c r="AT5" s="49" t="n"/>
       <c r="AU5" s="2" t="n"/>
     </row>
     <row r="6" ht="39.75" customHeight="1">
-      <c r="A6" s="60" t="n"/>
-      <c r="B6" s="61" t="n"/>
-      <c r="C6" s="60" t="n"/>
-      <c r="D6" s="62" t="n"/>
-      <c r="E6" s="62" t="n"/>
-      <c r="F6" s="61" t="n"/>
-      <c r="G6" s="63" t="n"/>
-      <c r="H6" s="60" t="n"/>
-      <c r="I6" s="61" t="n"/>
-      <c r="J6" s="60" t="n"/>
-      <c r="K6" s="61" t="n"/>
-      <c r="L6" s="60" t="n"/>
-      <c r="M6" s="61" t="n"/>
-      <c r="N6" s="63" t="n"/>
-      <c r="O6" s="63" t="n"/>
+      <c r="A6" s="54" t="n"/>
+      <c r="B6" s="55" t="n"/>
+      <c r="C6" s="54" t="n"/>
+      <c r="D6" s="56" t="n"/>
+      <c r="E6" s="56" t="n"/>
+      <c r="F6" s="55" t="n"/>
+      <c r="G6" s="57" t="n"/>
+      <c r="H6" s="54" t="n"/>
+      <c r="I6" s="55" t="n"/>
+      <c r="J6" s="54" t="n"/>
+      <c r="K6" s="55" t="n"/>
+      <c r="L6" s="54" t="n"/>
+      <c r="M6" s="55" t="n"/>
+      <c r="N6" s="57" t="n"/>
+      <c r="O6" s="57" t="n"/>
       <c r="P6" s="19" t="inlineStr">
         <is>
           <t>House #/ Street/ Sitio/ Purok</t>
         </is>
       </c>
-      <c r="Q6" s="55" t="n"/>
+      <c r="Q6" s="49" t="n"/>
       <c r="R6" s="19" t="inlineStr">
         <is>
           <t>Barangay</t>
         </is>
       </c>
-      <c r="S6" s="54" t="n"/>
-      <c r="T6" s="55" t="n"/>
+      <c r="S6" s="48" t="n"/>
+      <c r="T6" s="49" t="n"/>
       <c r="U6" s="19" t="inlineStr">
         <is>
           <t>Municipality/ City</t>
         </is>
       </c>
-      <c r="V6" s="55" t="n"/>
+      <c r="V6" s="49" t="n"/>
       <c r="W6" s="19" t="inlineStr">
         <is>
           <t>Province</t>
         </is>
       </c>
-      <c r="X6" s="54" t="n"/>
-      <c r="Y6" s="54" t="n"/>
-      <c r="Z6" s="54" t="n"/>
-      <c r="AA6" s="55" t="n"/>
+      <c r="X6" s="48" t="n"/>
+      <c r="Y6" s="48" t="n"/>
+      <c r="Z6" s="48" t="n"/>
+      <c r="AA6" s="49" t="n"/>
       <c r="AB6" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Father's Name (Last Name, First Name, Middle Name)     </t>
         </is>
       </c>
-      <c r="AC6" s="54" t="n"/>
-      <c r="AD6" s="54" t="n"/>
-      <c r="AE6" s="55" t="n"/>
+      <c r="AC6" s="48" t="n"/>
+      <c r="AD6" s="48" t="n"/>
+      <c r="AE6" s="49" t="n"/>
       <c r="AF6" s="19" t="inlineStr">
         <is>
           <t>Mother's Maiden Name (Last Name, First Name, Middle Name)</t>
         </is>
       </c>
-      <c r="AG6" s="54" t="n"/>
-      <c r="AH6" s="54" t="n"/>
-      <c r="AI6" s="54" t="n"/>
-      <c r="AJ6" s="55" t="n"/>
+      <c r="AG6" s="48" t="n"/>
+      <c r="AH6" s="48" t="n"/>
+      <c r="AI6" s="48" t="n"/>
+      <c r="AJ6" s="49" t="n"/>
       <c r="AK6" s="19" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="AL6" s="54" t="n"/>
-      <c r="AM6" s="54" t="n"/>
-      <c r="AN6" s="55" t="n"/>
+      <c r="AL6" s="48" t="n"/>
+      <c r="AM6" s="48" t="n"/>
+      <c r="AN6" s="49" t="n"/>
       <c r="AO6" s="19" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="AP6" s="60" t="n"/>
-      <c r="AQ6" s="61" t="n"/>
-      <c r="AR6" s="63" t="n"/>
+      <c r="AP6" s="54" t="n"/>
+      <c r="AQ6" s="55" t="n"/>
+      <c r="AR6" s="57" t="n"/>
       <c r="AS6" s="19" t="inlineStr">
         <is>
           <t>(Please refer to the legend on last page)</t>
         </is>
       </c>
-      <c r="AT6" s="55" t="n"/>
+      <c r="AT6" s="49" t="n"/>
       <c r="AU6" s="2" t="n"/>
     </row>
     <row r="7" ht="37.5" customHeight="1">
@@ -1989,36 +1969,36 @@
           <t>117591120157</t>
         </is>
       </c>
-      <c r="B7" s="55" t="n"/>
+      <c r="B7" s="49" t="n"/>
       <c r="C7" s="24" t="inlineStr">
         <is>
           <t>CRUZ, MICHAEL JOHN</t>
         </is>
       </c>
-      <c r="D7" s="54" t="n"/>
-      <c r="E7" s="54" t="n"/>
-      <c r="F7" s="55" t="n"/>
+      <c r="D7" s="48" t="n"/>
+      <c r="E7" s="48" t="n"/>
+      <c r="F7" s="49" t="n"/>
       <c r="G7" s="21" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H7" s="64" t="inlineStr">
+      <c r="H7" s="58" t="inlineStr">
         <is>
           <t>2005-12-09</t>
         </is>
       </c>
-      <c r="I7" s="55" t="n"/>
+      <c r="I7" s="49" t="n"/>
       <c r="J7" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="K7" s="55" t="n"/>
+      <c r="K7" s="49" t="n"/>
       <c r="L7" s="24" t="inlineStr">
         <is>
           <t>Hiligaynon</t>
         </is>
       </c>
-      <c r="M7" s="55" t="n"/>
+      <c r="M7" s="49" t="n"/>
       <c r="N7" s="24" t="n"/>
       <c r="O7" s="24" t="inlineStr">
         <is>
@@ -2026,60 +2006,60 @@
         </is>
       </c>
       <c r="P7" s="24" t="n"/>
-      <c r="Q7" s="55" t="n"/>
+      <c r="Q7" s="49" t="n"/>
       <c r="R7" s="24" t="inlineStr">
         <is>
-          <t>PAGSANGA‑AN</t>
-        </is>
-      </c>
-      <c r="S7" s="54" t="n"/>
-      <c r="T7" s="55" t="n"/>
+          <t>PAGSANGAÂ€‘AN</t>
+        </is>
+      </c>
+      <c r="S7" s="48" t="n"/>
+      <c r="T7" s="49" t="n"/>
       <c r="U7" s="24" t="inlineStr">
         <is>
           <t>PAVIA</t>
         </is>
       </c>
-      <c r="V7" s="55" t="n"/>
+      <c r="V7" s="49" t="n"/>
       <c r="W7" s="24" t="inlineStr">
         <is>
           <t>ILOILO</t>
         </is>
       </c>
-      <c r="X7" s="54" t="n"/>
-      <c r="Y7" s="54" t="n"/>
-      <c r="Z7" s="54" t="n"/>
-      <c r="AA7" s="55" t="n"/>
+      <c r="X7" s="48" t="n"/>
+      <c r="Y7" s="48" t="n"/>
+      <c r="Z7" s="48" t="n"/>
+      <c r="AA7" s="49" t="n"/>
       <c r="AB7" s="24" t="inlineStr">
         <is>
           <t>CRUZ, ROBERTO NAVARRO</t>
         </is>
       </c>
-      <c r="AC7" s="54" t="n"/>
-      <c r="AD7" s="54" t="n"/>
-      <c r="AE7" s="55" t="n"/>
+      <c r="AC7" s="48" t="n"/>
+      <c r="AD7" s="48" t="n"/>
+      <c r="AE7" s="49" t="n"/>
       <c r="AF7" s="24" t="inlineStr">
         <is>
           <t>SANTOS, ALICIA NAVARRO</t>
         </is>
       </c>
-      <c r="AG7" s="54" t="n"/>
-      <c r="AH7" s="54" t="n"/>
-      <c r="AI7" s="54" t="n"/>
-      <c r="AJ7" s="55" t="n"/>
+      <c r="AG7" s="48" t="n"/>
+      <c r="AH7" s="48" t="n"/>
+      <c r="AI7" s="48" t="n"/>
+      <c r="AJ7" s="49" t="n"/>
       <c r="AK7" s="24" t="n"/>
-      <c r="AL7" s="54" t="n"/>
-      <c r="AM7" s="54" t="n"/>
-      <c r="AN7" s="55" t="n"/>
+      <c r="AL7" s="48" t="n"/>
+      <c r="AM7" s="48" t="n"/>
+      <c r="AN7" s="49" t="n"/>
       <c r="AO7" s="24" t="n"/>
-      <c r="AP7" s="65" t="n"/>
-      <c r="AQ7" s="55" t="n"/>
+      <c r="AP7" s="59" t="n"/>
+      <c r="AQ7" s="49" t="n"/>
       <c r="AR7" s="21" t="inlineStr">
         <is>
           <t>Face To Face</t>
         </is>
       </c>
       <c r="AS7" s="21" t="n"/>
-      <c r="AT7" s="55" t="n"/>
+      <c r="AT7" s="49" t="n"/>
       <c r="AU7" s="2" t="n"/>
     </row>
     <row r="8" ht="27.75" customHeight="1">
@@ -2088,36 +2068,36 @@
           <t>117591120153</t>
         </is>
       </c>
-      <c r="B8" s="55" t="n"/>
+      <c r="B8" s="49" t="n"/>
       <c r="C8" s="24" t="inlineStr">
         <is>
           <t>DELGADO, MARK ANTHONY TORRES</t>
         </is>
       </c>
-      <c r="D8" s="54" t="n"/>
-      <c r="E8" s="54" t="n"/>
-      <c r="F8" s="55" t="n"/>
+      <c r="D8" s="48" t="n"/>
+      <c r="E8" s="48" t="n"/>
+      <c r="F8" s="49" t="n"/>
       <c r="G8" s="21" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H8" s="64" t="inlineStr">
+      <c r="H8" s="58" t="inlineStr">
         <is>
           <t>2005-08-12</t>
         </is>
       </c>
-      <c r="I8" s="55" t="n"/>
+      <c r="I8" s="49" t="n"/>
       <c r="J8" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="K8" s="55" t="n"/>
+      <c r="K8" s="49" t="n"/>
       <c r="L8" s="24" t="inlineStr">
         <is>
           <t>Waray</t>
         </is>
       </c>
-      <c r="M8" s="55" t="n"/>
+      <c r="M8" s="49" t="n"/>
       <c r="N8" s="24" t="n"/>
       <c r="O8" s="24" t="inlineStr">
         <is>
@@ -2125,60 +2105,60 @@
         </is>
       </c>
       <c r="P8" s="24" t="n"/>
-      <c r="Q8" s="55" t="n"/>
+      <c r="Q8" s="49" t="n"/>
       <c r="R8" s="24" t="inlineStr">
         <is>
-          <t>JIBAO‑AN</t>
-        </is>
-      </c>
-      <c r="S8" s="54" t="n"/>
-      <c r="T8" s="55" t="n"/>
+          <t>JIBAOÂ€‘AN</t>
+        </is>
+      </c>
+      <c r="S8" s="48" t="n"/>
+      <c r="T8" s="49" t="n"/>
       <c r="U8" s="24" t="inlineStr">
         <is>
           <t>PAVIA</t>
         </is>
       </c>
-      <c r="V8" s="55" t="n"/>
+      <c r="V8" s="49" t="n"/>
       <c r="W8" s="24" t="inlineStr">
         <is>
           <t>ILOILO</t>
         </is>
       </c>
-      <c r="X8" s="54" t="n"/>
-      <c r="Y8" s="54" t="n"/>
-      <c r="Z8" s="54" t="n"/>
-      <c r="AA8" s="55" t="n"/>
+      <c r="X8" s="48" t="n"/>
+      <c r="Y8" s="48" t="n"/>
+      <c r="Z8" s="48" t="n"/>
+      <c r="AA8" s="49" t="n"/>
       <c r="AB8" s="24" t="inlineStr">
         <is>
-          <t>DELGADO, FERNANDO TORRES</t>
-        </is>
-      </c>
-      <c r="AC8" s="54" t="n"/>
-      <c r="AD8" s="54" t="n"/>
-      <c r="AE8" s="55" t="n"/>
+          <t>SANTOS, FERNANDO TORRES DELGADO LOPEZ</t>
+        </is>
+      </c>
+      <c r="AC8" s="48" t="n"/>
+      <c r="AD8" s="48" t="n"/>
+      <c r="AE8" s="49" t="n"/>
       <c r="AF8" s="24" t="inlineStr">
         <is>
-          <t>SANTOS, LOURDES TORRES</t>
-        </is>
-      </c>
-      <c r="AG8" s="54" t="n"/>
-      <c r="AH8" s="54" t="n"/>
-      <c r="AI8" s="54" t="n"/>
-      <c r="AJ8" s="55" t="n"/>
+          <t>MARQUEZ, LOURDES TORRES SANTOS GARCIA</t>
+        </is>
+      </c>
+      <c r="AG8" s="48" t="n"/>
+      <c r="AH8" s="48" t="n"/>
+      <c r="AI8" s="48" t="n"/>
+      <c r="AJ8" s="49" t="n"/>
       <c r="AK8" s="24" t="n"/>
-      <c r="AL8" s="54" t="n"/>
-      <c r="AM8" s="54" t="n"/>
-      <c r="AN8" s="55" t="n"/>
+      <c r="AL8" s="48" t="n"/>
+      <c r="AM8" s="48" t="n"/>
+      <c r="AN8" s="49" t="n"/>
       <c r="AO8" s="24" t="n"/>
-      <c r="AP8" s="65" t="n"/>
-      <c r="AQ8" s="55" t="n"/>
+      <c r="AP8" s="59" t="n"/>
+      <c r="AQ8" s="49" t="n"/>
       <c r="AR8" s="21" t="inlineStr">
         <is>
           <t>Face To Face</t>
         </is>
       </c>
       <c r="AS8" s="21" t="n"/>
-      <c r="AT8" s="55" t="n"/>
+      <c r="AT8" s="49" t="n"/>
       <c r="AU8" s="2" t="n"/>
     </row>
     <row r="9" ht="27.75" customHeight="1">
@@ -2187,36 +2167,36 @@
           <t>117591120155</t>
         </is>
       </c>
-      <c r="B9" s="55" t="n"/>
+      <c r="B9" s="49" t="n"/>
       <c r="C9" s="24" t="inlineStr">
         <is>
           <t>DIAZ, KEVIN JEROME MANALO</t>
         </is>
       </c>
-      <c r="D9" s="54" t="n"/>
-      <c r="E9" s="54" t="n"/>
-      <c r="F9" s="55" t="n"/>
+      <c r="D9" s="48" t="n"/>
+      <c r="E9" s="48" t="n"/>
+      <c r="F9" s="49" t="n"/>
       <c r="G9" s="21" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H9" s="64" t="inlineStr">
+      <c r="H9" s="58" t="inlineStr">
         <is>
           <t>2005-09-18</t>
         </is>
       </c>
-      <c r="I9" s="55" t="n"/>
+      <c r="I9" s="49" t="n"/>
       <c r="J9" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="K9" s="55" t="n"/>
+      <c r="K9" s="49" t="n"/>
       <c r="L9" s="24" t="inlineStr">
         <is>
           <t>Hiligaynon</t>
         </is>
       </c>
-      <c r="M9" s="55" t="n"/>
+      <c r="M9" s="49" t="n"/>
       <c r="N9" s="24" t="n"/>
       <c r="O9" s="24" t="inlineStr">
         <is>
@@ -2224,60 +2204,60 @@
         </is>
       </c>
       <c r="P9" s="24" t="n"/>
-      <c r="Q9" s="55" t="n"/>
+      <c r="Q9" s="49" t="n"/>
       <c r="R9" s="24" t="inlineStr">
         <is>
           <t>ANILAO</t>
         </is>
       </c>
-      <c r="S9" s="54" t="n"/>
-      <c r="T9" s="55" t="n"/>
+      <c r="S9" s="48" t="n"/>
+      <c r="T9" s="49" t="n"/>
       <c r="U9" s="24" t="inlineStr">
         <is>
           <t>PAVIA</t>
         </is>
       </c>
-      <c r="V9" s="55" t="n"/>
+      <c r="V9" s="49" t="n"/>
       <c r="W9" s="24" t="inlineStr">
         <is>
           <t>ILOILO</t>
         </is>
       </c>
-      <c r="X9" s="54" t="n"/>
-      <c r="Y9" s="54" t="n"/>
-      <c r="Z9" s="54" t="n"/>
-      <c r="AA9" s="55" t="n"/>
+      <c r="X9" s="48" t="n"/>
+      <c r="Y9" s="48" t="n"/>
+      <c r="Z9" s="48" t="n"/>
+      <c r="AA9" s="49" t="n"/>
       <c r="AB9" s="24" t="inlineStr">
         <is>
           <t>DIAZ, JOSE MANALO</t>
         </is>
       </c>
-      <c r="AC9" s="54" t="n"/>
-      <c r="AD9" s="54" t="n"/>
-      <c r="AE9" s="55" t="n"/>
+      <c r="AC9" s="48" t="n"/>
+      <c r="AD9" s="48" t="n"/>
+      <c r="AE9" s="49" t="n"/>
       <c r="AF9" s="24" t="inlineStr">
         <is>
           <t>SANTOS, TERESA MANALO</t>
         </is>
       </c>
-      <c r="AG9" s="54" t="n"/>
-      <c r="AH9" s="54" t="n"/>
-      <c r="AI9" s="54" t="n"/>
-      <c r="AJ9" s="55" t="n"/>
+      <c r="AG9" s="48" t="n"/>
+      <c r="AH9" s="48" t="n"/>
+      <c r="AI9" s="48" t="n"/>
+      <c r="AJ9" s="49" t="n"/>
       <c r="AK9" s="24" t="n"/>
-      <c r="AL9" s="54" t="n"/>
-      <c r="AM9" s="54" t="n"/>
-      <c r="AN9" s="55" t="n"/>
+      <c r="AL9" s="48" t="n"/>
+      <c r="AM9" s="48" t="n"/>
+      <c r="AN9" s="49" t="n"/>
       <c r="AO9" s="24" t="n"/>
-      <c r="AP9" s="65" t="n"/>
-      <c r="AQ9" s="55" t="n"/>
+      <c r="AP9" s="59" t="n"/>
+      <c r="AQ9" s="49" t="n"/>
       <c r="AR9" s="21" t="inlineStr">
         <is>
           <t>Face To Face</t>
         </is>
       </c>
       <c r="AS9" s="21" t="n"/>
-      <c r="AT9" s="55" t="n"/>
+      <c r="AT9" s="49" t="n"/>
       <c r="AU9" s="2" t="n"/>
     </row>
     <row r="10" ht="27.75" customHeight="1">
@@ -2286,36 +2266,36 @@
           <t>117591120151</t>
         </is>
       </c>
-      <c r="B10" s="55" t="n"/>
+      <c r="B10" s="49" t="n"/>
       <c r="C10" s="24" t="inlineStr">
         <is>
           <t>GARCIA, JUAN CARLOS DELOS SANTOS</t>
         </is>
       </c>
-      <c r="D10" s="54" t="n"/>
-      <c r="E10" s="54" t="n"/>
-      <c r="F10" s="55" t="n"/>
+      <c r="D10" s="48" t="n"/>
+      <c r="E10" s="48" t="n"/>
+      <c r="F10" s="49" t="n"/>
       <c r="G10" s="21" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H10" s="64" t="inlineStr">
+      <c r="H10" s="58" t="inlineStr">
         <is>
           <t>2005-11-03</t>
         </is>
       </c>
-      <c r="I10" s="55" t="n"/>
+      <c r="I10" s="49" t="n"/>
       <c r="J10" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="K10" s="55" t="n"/>
+      <c r="K10" s="49" t="n"/>
       <c r="L10" s="24" t="inlineStr">
         <is>
           <t>Cebuano</t>
         </is>
       </c>
-      <c r="M10" s="55" t="n"/>
+      <c r="M10" s="49" t="n"/>
       <c r="N10" s="24" t="n"/>
       <c r="O10" s="24" t="inlineStr">
         <is>
@@ -2323,60 +2303,60 @@
         </is>
       </c>
       <c r="P10" s="24" t="n"/>
-      <c r="Q10" s="55" t="n"/>
+      <c r="Q10" s="49" t="n"/>
       <c r="R10" s="24" t="inlineStr">
         <is>
           <t>BALABAG</t>
         </is>
       </c>
-      <c r="S10" s="54" t="n"/>
-      <c r="T10" s="55" t="n"/>
+      <c r="S10" s="48" t="n"/>
+      <c r="T10" s="49" t="n"/>
       <c r="U10" s="24" t="inlineStr">
         <is>
           <t>PAVIA</t>
         </is>
       </c>
-      <c r="V10" s="55" t="n"/>
+      <c r="V10" s="49" t="n"/>
       <c r="W10" s="24" t="inlineStr">
         <is>
           <t>ILOILO</t>
         </is>
       </c>
-      <c r="X10" s="54" t="n"/>
-      <c r="Y10" s="54" t="n"/>
-      <c r="Z10" s="54" t="n"/>
-      <c r="AA10" s="55" t="n"/>
+      <c r="X10" s="48" t="n"/>
+      <c r="Y10" s="48" t="n"/>
+      <c r="Z10" s="48" t="n"/>
+      <c r="AA10" s="49" t="n"/>
       <c r="AB10" s="24" t="inlineStr">
         <is>
-          <t>GARCIA, RICARDO LOPEZ</t>
-        </is>
-      </c>
-      <c r="AC10" s="54" t="n"/>
-      <c r="AD10" s="54" t="n"/>
-      <c r="AE10" s="55" t="n"/>
+          <t>GOMEZ, RICARDO LOPEZ GARCIA DIAZ</t>
+        </is>
+      </c>
+      <c r="AC10" s="48" t="n"/>
+      <c r="AD10" s="48" t="n"/>
+      <c r="AE10" s="49" t="n"/>
       <c r="AF10" s="24" t="inlineStr">
         <is>
-          <t>SANTOS, ELENA DELOS</t>
-        </is>
-      </c>
-      <c r="AG10" s="54" t="n"/>
-      <c r="AH10" s="54" t="n"/>
-      <c r="AI10" s="54" t="n"/>
-      <c r="AJ10" s="55" t="n"/>
+          <t>LOPEZ, ELENA DELOS SANTOS PEREZ</t>
+        </is>
+      </c>
+      <c r="AG10" s="48" t="n"/>
+      <c r="AH10" s="48" t="n"/>
+      <c r="AI10" s="48" t="n"/>
+      <c r="AJ10" s="49" t="n"/>
       <c r="AK10" s="24" t="n"/>
-      <c r="AL10" s="54" t="n"/>
-      <c r="AM10" s="54" t="n"/>
-      <c r="AN10" s="55" t="n"/>
+      <c r="AL10" s="48" t="n"/>
+      <c r="AM10" s="48" t="n"/>
+      <c r="AN10" s="49" t="n"/>
       <c r="AO10" s="24" t="n"/>
-      <c r="AP10" s="65" t="n"/>
-      <c r="AQ10" s="55" t="n"/>
+      <c r="AP10" s="59" t="n"/>
+      <c r="AQ10" s="49" t="n"/>
       <c r="AR10" s="21" t="inlineStr">
         <is>
           <t>Face To Face</t>
         </is>
       </c>
       <c r="AS10" s="21" t="n"/>
-      <c r="AT10" s="55" t="n"/>
+      <c r="AT10" s="49" t="n"/>
       <c r="AU10" s="2" t="n"/>
     </row>
     <row r="11" ht="37.5" customHeight="1">
@@ -2385,36 +2365,36 @@
           <t>117591120149</t>
         </is>
       </c>
-      <c r="B11" s="55" t="n"/>
+      <c r="B11" s="49" t="n"/>
       <c r="C11" s="24" t="inlineStr">
         <is>
           <t>TAN, ADRIAN DOMINIC LUNMAWAG</t>
         </is>
       </c>
-      <c r="D11" s="54" t="n"/>
-      <c r="E11" s="54" t="n"/>
-      <c r="F11" s="55" t="n"/>
+      <c r="D11" s="48" t="n"/>
+      <c r="E11" s="48" t="n"/>
+      <c r="F11" s="49" t="n"/>
       <c r="G11" s="21" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H11" s="64" t="inlineStr">
+      <c r="H11" s="58" t="inlineStr">
         <is>
           <t>2005-07-29</t>
         </is>
       </c>
-      <c r="I11" s="55" t="n"/>
+      <c r="I11" s="49" t="n"/>
       <c r="J11" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="K11" s="55" t="n"/>
+      <c r="K11" s="49" t="n"/>
       <c r="L11" s="24" t="inlineStr">
         <is>
           <t>Hiligaynon</t>
         </is>
       </c>
-      <c r="M11" s="55" t="n"/>
+      <c r="M11" s="49" t="n"/>
       <c r="N11" s="24" t="n"/>
       <c r="O11" s="24" t="inlineStr">
         <is>
@@ -2422,115 +2402,115 @@
         </is>
       </c>
       <c r="P11" s="24" t="n"/>
-      <c r="Q11" s="55" t="n"/>
+      <c r="Q11" s="49" t="n"/>
       <c r="R11" s="24" t="inlineStr">
         <is>
           <t>POBLACION ILAYA</t>
         </is>
       </c>
-      <c r="S11" s="54" t="n"/>
-      <c r="T11" s="55" t="n"/>
+      <c r="S11" s="48" t="n"/>
+      <c r="T11" s="49" t="n"/>
       <c r="U11" s="24" t="inlineStr">
         <is>
           <t>PAVIA</t>
         </is>
       </c>
-      <c r="V11" s="55" t="n"/>
+      <c r="V11" s="49" t="n"/>
       <c r="W11" s="24" t="inlineStr">
         <is>
           <t>ILOILO</t>
         </is>
       </c>
-      <c r="X11" s="54" t="n"/>
-      <c r="Y11" s="54" t="n"/>
-      <c r="Z11" s="54" t="n"/>
-      <c r="AA11" s="55" t="n"/>
+      <c r="X11" s="48" t="n"/>
+      <c r="Y11" s="48" t="n"/>
+      <c r="Z11" s="48" t="n"/>
+      <c r="AA11" s="49" t="n"/>
       <c r="AB11" s="24" t="inlineStr">
         <is>
-          <t>TAN, ROGELIO MACAPAGAL</t>
-        </is>
-      </c>
-      <c r="AC11" s="54" t="n"/>
-      <c r="AD11" s="54" t="n"/>
-      <c r="AE11" s="55" t="n"/>
+          <t>CRUZ, ROGELIO MACAPAGAL TAN RAMOS</t>
+        </is>
+      </c>
+      <c r="AC11" s="48" t="n"/>
+      <c r="AD11" s="48" t="n"/>
+      <c r="AE11" s="49" t="n"/>
       <c r="AF11" s="24" t="inlineStr">
         <is>
-          <t>SANTOS, MARILYN LUNMAWAG</t>
-        </is>
-      </c>
-      <c r="AG11" s="54" t="n"/>
-      <c r="AH11" s="54" t="n"/>
-      <c r="AI11" s="54" t="n"/>
-      <c r="AJ11" s="55" t="n"/>
+          <t>SANTOS, MARILYN LUNMAWAG SANTOS LOPEZ</t>
+        </is>
+      </c>
+      <c r="AG11" s="48" t="n"/>
+      <c r="AH11" s="48" t="n"/>
+      <c r="AI11" s="48" t="n"/>
+      <c r="AJ11" s="49" t="n"/>
       <c r="AK11" s="24" t="n"/>
-      <c r="AL11" s="54" t="n"/>
-      <c r="AM11" s="54" t="n"/>
-      <c r="AN11" s="55" t="n"/>
+      <c r="AL11" s="48" t="n"/>
+      <c r="AM11" s="48" t="n"/>
+      <c r="AN11" s="49" t="n"/>
       <c r="AO11" s="24" t="n"/>
-      <c r="AP11" s="65" t="n"/>
-      <c r="AQ11" s="55" t="n"/>
+      <c r="AP11" s="59" t="n"/>
+      <c r="AQ11" s="49" t="n"/>
       <c r="AR11" s="21" t="inlineStr">
         <is>
           <t>Face To Face</t>
         </is>
       </c>
       <c r="AS11" s="21" t="n"/>
-      <c r="AT11" s="55" t="n"/>
+      <c r="AT11" s="49" t="n"/>
       <c r="AU11" s="2" t="n"/>
     </row>
     <row r="12" ht="37.5" customHeight="1">
       <c r="A12" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="55" t="n"/>
+      <c r="B12" s="49" t="n"/>
       <c r="C12" s="24" t="inlineStr">
         <is>
           <t>&lt;=== TOTAL MALE</t>
         </is>
       </c>
-      <c r="D12" s="54" t="n"/>
-      <c r="E12" s="54" t="n"/>
-      <c r="F12" s="55" t="n"/>
+      <c r="D12" s="48" t="n"/>
+      <c r="E12" s="48" t="n"/>
+      <c r="F12" s="49" t="n"/>
       <c r="G12" s="21" t="n"/>
-      <c r="H12" s="64" t="n"/>
-      <c r="I12" s="55" t="n"/>
+      <c r="H12" s="58" t="n"/>
+      <c r="I12" s="49" t="n"/>
       <c r="J12" s="21" t="n"/>
-      <c r="K12" s="55" t="n"/>
+      <c r="K12" s="49" t="n"/>
       <c r="L12" s="24" t="n"/>
-      <c r="M12" s="55" t="n"/>
+      <c r="M12" s="49" t="n"/>
       <c r="N12" s="24" t="n"/>
       <c r="O12" s="24" t="n"/>
       <c r="P12" s="24" t="n"/>
-      <c r="Q12" s="55" t="n"/>
+      <c r="Q12" s="49" t="n"/>
       <c r="R12" s="24" t="n"/>
-      <c r="S12" s="54" t="n"/>
-      <c r="T12" s="55" t="n"/>
+      <c r="S12" s="48" t="n"/>
+      <c r="T12" s="49" t="n"/>
       <c r="U12" s="24" t="n"/>
-      <c r="V12" s="55" t="n"/>
+      <c r="V12" s="49" t="n"/>
       <c r="W12" s="24" t="n"/>
-      <c r="X12" s="54" t="n"/>
-      <c r="Y12" s="54" t="n"/>
-      <c r="Z12" s="54" t="n"/>
-      <c r="AA12" s="55" t="n"/>
+      <c r="X12" s="48" t="n"/>
+      <c r="Y12" s="48" t="n"/>
+      <c r="Z12" s="48" t="n"/>
+      <c r="AA12" s="49" t="n"/>
       <c r="AB12" s="24" t="n"/>
-      <c r="AC12" s="54" t="n"/>
-      <c r="AD12" s="54" t="n"/>
-      <c r="AE12" s="55" t="n"/>
+      <c r="AC12" s="48" t="n"/>
+      <c r="AD12" s="48" t="n"/>
+      <c r="AE12" s="49" t="n"/>
       <c r="AF12" s="24" t="n"/>
-      <c r="AG12" s="54" t="n"/>
-      <c r="AH12" s="54" t="n"/>
-      <c r="AI12" s="54" t="n"/>
-      <c r="AJ12" s="55" t="n"/>
+      <c r="AG12" s="48" t="n"/>
+      <c r="AH12" s="48" t="n"/>
+      <c r="AI12" s="48" t="n"/>
+      <c r="AJ12" s="49" t="n"/>
       <c r="AK12" s="24" t="n"/>
-      <c r="AL12" s="54" t="n"/>
-      <c r="AM12" s="54" t="n"/>
-      <c r="AN12" s="55" t="n"/>
+      <c r="AL12" s="48" t="n"/>
+      <c r="AM12" s="48" t="n"/>
+      <c r="AN12" s="49" t="n"/>
       <c r="AO12" s="24" t="n"/>
-      <c r="AP12" s="65" t="n"/>
-      <c r="AQ12" s="55" t="n"/>
+      <c r="AP12" s="59" t="n"/>
+      <c r="AQ12" s="49" t="n"/>
       <c r="AR12" s="21" t="n"/>
       <c r="AS12" s="21" t="n"/>
-      <c r="AT12" s="55" t="n"/>
+      <c r="AT12" s="49" t="n"/>
       <c r="AU12" s="2" t="n"/>
     </row>
     <row r="13" ht="27.75" customHeight="1">
@@ -2539,36 +2519,36 @@
           <t>117591120152</t>
         </is>
       </c>
-      <c r="B13" s="55" t="n"/>
+      <c r="B13" s="49" t="n"/>
       <c r="C13" s="24" t="inlineStr">
         <is>
           <t>LOPEZ, ANGELA MAE SANTOS</t>
         </is>
       </c>
-      <c r="D13" s="54" t="n"/>
-      <c r="E13" s="54" t="n"/>
-      <c r="F13" s="55" t="n"/>
+      <c r="D13" s="48" t="n"/>
+      <c r="E13" s="48" t="n"/>
+      <c r="F13" s="49" t="n"/>
       <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H13" s="64" t="inlineStr">
+      <c r="H13" s="58" t="inlineStr">
         <is>
           <t>2006-05-22</t>
         </is>
       </c>
-      <c r="I13" s="55" t="n"/>
+      <c r="I13" s="49" t="n"/>
       <c r="J13" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="K13" s="55" t="n"/>
+      <c r="K13" s="49" t="n"/>
       <c r="L13" s="24" t="inlineStr">
         <is>
           <t>Hiligaynon</t>
         </is>
       </c>
-      <c r="M13" s="55" t="n"/>
+      <c r="M13" s="49" t="n"/>
       <c r="N13" s="24" t="n"/>
       <c r="O13" s="24" t="inlineStr">
         <is>
@@ -2576,60 +2556,60 @@
         </is>
       </c>
       <c r="P13" s="24" t="n"/>
-      <c r="Q13" s="55" t="n"/>
+      <c r="Q13" s="49" t="n"/>
       <c r="R13" s="24" t="inlineStr">
         <is>
           <t>AMPARO</t>
         </is>
       </c>
-      <c r="S13" s="54" t="n"/>
-      <c r="T13" s="55" t="n"/>
+      <c r="S13" s="48" t="n"/>
+      <c r="T13" s="49" t="n"/>
       <c r="U13" s="24" t="inlineStr">
         <is>
           <t>PAVIA</t>
         </is>
       </c>
-      <c r="V13" s="55" t="n"/>
+      <c r="V13" s="49" t="n"/>
       <c r="W13" s="24" t="inlineStr">
         <is>
           <t>ILOILO</t>
         </is>
       </c>
-      <c r="X13" s="54" t="n"/>
-      <c r="Y13" s="54" t="n"/>
-      <c r="Z13" s="54" t="n"/>
-      <c r="AA13" s="55" t="n"/>
+      <c r="X13" s="48" t="n"/>
+      <c r="Y13" s="48" t="n"/>
+      <c r="Z13" s="48" t="n"/>
+      <c r="AA13" s="49" t="n"/>
       <c r="AB13" s="24" t="inlineStr">
         <is>
-          <t>LOPEZ, EDUARDO SANTOS</t>
-        </is>
-      </c>
-      <c r="AC13" s="54" t="n"/>
-      <c r="AD13" s="54" t="n"/>
-      <c r="AE13" s="55" t="n"/>
+          <t>VILLANUEVA, EDUARDO SANTOS LOPEZ SANTOS</t>
+        </is>
+      </c>
+      <c r="AC13" s="48" t="n"/>
+      <c r="AD13" s="48" t="n"/>
+      <c r="AE13" s="49" t="n"/>
       <c r="AF13" s="24" t="inlineStr">
         <is>
-          <t>DELGADO, ROSALIE SANTOS</t>
-        </is>
-      </c>
-      <c r="AG13" s="54" t="n"/>
-      <c r="AH13" s="54" t="n"/>
-      <c r="AI13" s="54" t="n"/>
-      <c r="AJ13" s="55" t="n"/>
+          <t>TORRES, ROSALIE SANTOS DELGADO REYES</t>
+        </is>
+      </c>
+      <c r="AG13" s="48" t="n"/>
+      <c r="AH13" s="48" t="n"/>
+      <c r="AI13" s="48" t="n"/>
+      <c r="AJ13" s="49" t="n"/>
       <c r="AK13" s="24" t="n"/>
-      <c r="AL13" s="54" t="n"/>
-      <c r="AM13" s="54" t="n"/>
-      <c r="AN13" s="55" t="n"/>
+      <c r="AL13" s="48" t="n"/>
+      <c r="AM13" s="48" t="n"/>
+      <c r="AN13" s="49" t="n"/>
       <c r="AO13" s="24" t="n"/>
-      <c r="AP13" s="65" t="n"/>
-      <c r="AQ13" s="55" t="n"/>
+      <c r="AP13" s="59" t="n"/>
+      <c r="AQ13" s="49" t="n"/>
       <c r="AR13" s="21" t="inlineStr">
         <is>
           <t>Face To Face</t>
         </is>
       </c>
       <c r="AS13" s="21" t="n"/>
-      <c r="AT13" s="55" t="n"/>
+      <c r="AT13" s="49" t="n"/>
       <c r="AU13" s="2" t="n"/>
     </row>
     <row r="14" ht="27.75" customHeight="1">
@@ -2638,36 +2618,36 @@
           <t>117591120158</t>
         </is>
       </c>
-      <c r="B14" s="55" t="n"/>
+      <c r="B14" s="49" t="n"/>
       <c r="C14" s="24" t="inlineStr">
         <is>
           <t>MARTINEZ, ANGELA ROSE LOPEZ</t>
         </is>
       </c>
-      <c r="D14" s="54" t="n"/>
-      <c r="E14" s="54" t="n"/>
-      <c r="F14" s="55" t="n"/>
+      <c r="D14" s="48" t="n"/>
+      <c r="E14" s="48" t="n"/>
+      <c r="F14" s="49" t="n"/>
       <c r="G14" s="21" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H14" s="64" t="inlineStr">
+      <c r="H14" s="58" t="inlineStr">
         <is>
           <t>2006-03-27</t>
         </is>
       </c>
-      <c r="I14" s="55" t="n"/>
+      <c r="I14" s="49" t="n"/>
       <c r="J14" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="K14" s="55" t="n"/>
+      <c r="K14" s="49" t="n"/>
       <c r="L14" s="24" t="inlineStr">
         <is>
           <t>Tagalog</t>
         </is>
       </c>
-      <c r="M14" s="55" t="n"/>
+      <c r="M14" s="49" t="n"/>
       <c r="N14" s="24" t="n"/>
       <c r="O14" s="24" t="inlineStr">
         <is>
@@ -2675,60 +2655,60 @@
         </is>
       </c>
       <c r="P14" s="24" t="n"/>
-      <c r="Q14" s="55" t="n"/>
+      <c r="Q14" s="49" t="n"/>
       <c r="R14" s="24" t="inlineStr">
         <is>
           <t>UNGKA II</t>
         </is>
       </c>
-      <c r="S14" s="54" t="n"/>
-      <c r="T14" s="55" t="n"/>
+      <c r="S14" s="48" t="n"/>
+      <c r="T14" s="49" t="n"/>
       <c r="U14" s="24" t="inlineStr">
         <is>
           <t>PAVIA</t>
         </is>
       </c>
-      <c r="V14" s="55" t="n"/>
+      <c r="V14" s="49" t="n"/>
       <c r="W14" s="24" t="inlineStr">
         <is>
           <t>ILOILO</t>
         </is>
       </c>
-      <c r="X14" s="54" t="n"/>
-      <c r="Y14" s="54" t="n"/>
-      <c r="Z14" s="54" t="n"/>
-      <c r="AA14" s="55" t="n"/>
+      <c r="X14" s="48" t="n"/>
+      <c r="Y14" s="48" t="n"/>
+      <c r="Z14" s="48" t="n"/>
+      <c r="AA14" s="49" t="n"/>
       <c r="AB14" s="24" t="inlineStr">
         <is>
           <t>MARTINEZ, DANILO LOPEZ</t>
         </is>
       </c>
-      <c r="AC14" s="54" t="n"/>
-      <c r="AD14" s="54" t="n"/>
-      <c r="AE14" s="55" t="n"/>
+      <c r="AC14" s="48" t="n"/>
+      <c r="AD14" s="48" t="n"/>
+      <c r="AE14" s="49" t="n"/>
       <c r="AF14" s="24" t="inlineStr">
         <is>
           <t>SANTOS, SOFIA LOPEZ</t>
         </is>
       </c>
-      <c r="AG14" s="54" t="n"/>
-      <c r="AH14" s="54" t="n"/>
-      <c r="AI14" s="54" t="n"/>
-      <c r="AJ14" s="55" t="n"/>
+      <c r="AG14" s="48" t="n"/>
+      <c r="AH14" s="48" t="n"/>
+      <c r="AI14" s="48" t="n"/>
+      <c r="AJ14" s="49" t="n"/>
       <c r="AK14" s="24" t="n"/>
-      <c r="AL14" s="54" t="n"/>
-      <c r="AM14" s="54" t="n"/>
-      <c r="AN14" s="55" t="n"/>
+      <c r="AL14" s="48" t="n"/>
+      <c r="AM14" s="48" t="n"/>
+      <c r="AN14" s="49" t="n"/>
       <c r="AO14" s="24" t="n"/>
-      <c r="AP14" s="65" t="n"/>
-      <c r="AQ14" s="55" t="n"/>
+      <c r="AP14" s="59" t="n"/>
+      <c r="AQ14" s="49" t="n"/>
       <c r="AR14" s="21" t="inlineStr">
         <is>
           <t>Face To Face</t>
         </is>
       </c>
       <c r="AS14" s="21" t="n"/>
-      <c r="AT14" s="55" t="n"/>
+      <c r="AT14" s="49" t="n"/>
       <c r="AU14" s="2" t="n"/>
     </row>
     <row r="15" ht="27.75" customHeight="1">
@@ -2737,36 +2717,36 @@
           <t>117591120156</t>
         </is>
       </c>
-      <c r="B15" s="55" t="n"/>
+      <c r="B15" s="49" t="n"/>
       <c r="C15" s="24" t="inlineStr">
         <is>
           <t>REYES, LIZA MARIE GONZALEZ</t>
         </is>
       </c>
-      <c r="D15" s="54" t="n"/>
-      <c r="E15" s="54" t="n"/>
-      <c r="F15" s="55" t="n"/>
+      <c r="D15" s="48" t="n"/>
+      <c r="E15" s="48" t="n"/>
+      <c r="F15" s="49" t="n"/>
       <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H15" s="64" t="inlineStr">
+      <c r="H15" s="58" t="inlineStr">
         <is>
           <t>2006-06-05</t>
         </is>
       </c>
-      <c r="I15" s="55" t="n"/>
+      <c r="I15" s="49" t="n"/>
       <c r="J15" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="K15" s="55" t="n"/>
+      <c r="K15" s="49" t="n"/>
       <c r="L15" s="24" t="inlineStr">
         <is>
           <t>Cebuano</t>
         </is>
       </c>
-      <c r="M15" s="55" t="n"/>
+      <c r="M15" s="49" t="n"/>
       <c r="N15" s="24" t="n"/>
       <c r="O15" s="24" t="inlineStr">
         <is>
@@ -2774,60 +2754,60 @@
         </is>
       </c>
       <c r="P15" s="24" t="n"/>
-      <c r="Q15" s="55" t="n"/>
+      <c r="Q15" s="49" t="n"/>
       <c r="R15" s="24" t="inlineStr">
         <is>
           <t>CABUGAO SUR</t>
         </is>
       </c>
-      <c r="S15" s="54" t="n"/>
-      <c r="T15" s="55" t="n"/>
+      <c r="S15" s="48" t="n"/>
+      <c r="T15" s="49" t="n"/>
       <c r="U15" s="24" t="inlineStr">
         <is>
           <t>PAVIA</t>
         </is>
       </c>
-      <c r="V15" s="55" t="n"/>
+      <c r="V15" s="49" t="n"/>
       <c r="W15" s="24" t="inlineStr">
         <is>
           <t>ILOILO</t>
         </is>
       </c>
-      <c r="X15" s="54" t="n"/>
-      <c r="Y15" s="54" t="n"/>
-      <c r="Z15" s="54" t="n"/>
-      <c r="AA15" s="55" t="n"/>
+      <c r="X15" s="48" t="n"/>
+      <c r="Y15" s="48" t="n"/>
+      <c r="Z15" s="48" t="n"/>
+      <c r="AA15" s="49" t="n"/>
       <c r="AB15" s="24" t="inlineStr">
         <is>
           <t>REYES, MANUEL GONZALEZ</t>
         </is>
       </c>
-      <c r="AC15" s="54" t="n"/>
-      <c r="AD15" s="54" t="n"/>
-      <c r="AE15" s="55" t="n"/>
+      <c r="AC15" s="48" t="n"/>
+      <c r="AD15" s="48" t="n"/>
+      <c r="AE15" s="49" t="n"/>
       <c r="AF15" s="24" t="inlineStr">
         <is>
           <t>SANTOS, PATRICIA GONZALEZ</t>
         </is>
       </c>
-      <c r="AG15" s="54" t="n"/>
-      <c r="AH15" s="54" t="n"/>
-      <c r="AI15" s="54" t="n"/>
-      <c r="AJ15" s="55" t="n"/>
+      <c r="AG15" s="48" t="n"/>
+      <c r="AH15" s="48" t="n"/>
+      <c r="AI15" s="48" t="n"/>
+      <c r="AJ15" s="49" t="n"/>
       <c r="AK15" s="24" t="n"/>
-      <c r="AL15" s="54" t="n"/>
-      <c r="AM15" s="54" t="n"/>
-      <c r="AN15" s="55" t="n"/>
+      <c r="AL15" s="48" t="n"/>
+      <c r="AM15" s="48" t="n"/>
+      <c r="AN15" s="49" t="n"/>
       <c r="AO15" s="24" t="n"/>
-      <c r="AP15" s="65" t="n"/>
-      <c r="AQ15" s="55" t="n"/>
+      <c r="AP15" s="59" t="n"/>
+      <c r="AQ15" s="49" t="n"/>
       <c r="AR15" s="21" t="inlineStr">
         <is>
           <t>Face To Face</t>
         </is>
       </c>
       <c r="AS15" s="21" t="n"/>
-      <c r="AT15" s="55" t="n"/>
+      <c r="AT15" s="49" t="n"/>
       <c r="AU15" s="2" t="n"/>
     </row>
     <row r="16" ht="27.75" customHeight="1">
@@ -2836,36 +2816,36 @@
           <t>117591120150</t>
         </is>
       </c>
-      <c r="B16" s="55" t="n"/>
+      <c r="B16" s="49" t="n"/>
       <c r="C16" s="24" t="inlineStr">
         <is>
           <t>REYES, MARIA ANGELICA</t>
         </is>
       </c>
-      <c r="D16" s="54" t="n"/>
-      <c r="E16" s="54" t="n"/>
-      <c r="F16" s="55" t="n"/>
+      <c r="D16" s="48" t="n"/>
+      <c r="E16" s="48" t="n"/>
+      <c r="F16" s="49" t="n"/>
       <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H16" s="64" t="inlineStr">
+      <c r="H16" s="58" t="inlineStr">
         <is>
           <t>2006-02-15</t>
         </is>
       </c>
-      <c r="I16" s="55" t="n"/>
+      <c r="I16" s="49" t="n"/>
       <c r="J16" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="K16" s="55" t="n"/>
+      <c r="K16" s="49" t="n"/>
       <c r="L16" s="24" t="inlineStr">
         <is>
           <t>Tagalog</t>
         </is>
       </c>
-      <c r="M16" s="55" t="n"/>
+      <c r="M16" s="49" t="n"/>
       <c r="N16" s="24" t="n"/>
       <c r="O16" s="24" t="inlineStr">
         <is>
@@ -2873,60 +2853,60 @@
         </is>
       </c>
       <c r="P16" s="24" t="n"/>
-      <c r="Q16" s="55" t="n"/>
+      <c r="Q16" s="49" t="n"/>
       <c r="R16" s="24" t="inlineStr">
         <is>
           <t>UNGKA I</t>
         </is>
       </c>
-      <c r="S16" s="54" t="n"/>
-      <c r="T16" s="55" t="n"/>
+      <c r="S16" s="48" t="n"/>
+      <c r="T16" s="49" t="n"/>
       <c r="U16" s="24" t="inlineStr">
         <is>
           <t>PAVIA</t>
         </is>
       </c>
-      <c r="V16" s="55" t="n"/>
+      <c r="V16" s="49" t="n"/>
       <c r="W16" s="24" t="inlineStr">
         <is>
           <t>ILOILO</t>
         </is>
       </c>
-      <c r="X16" s="54" t="n"/>
-      <c r="Y16" s="54" t="n"/>
-      <c r="Z16" s="54" t="n"/>
-      <c r="AA16" s="55" t="n"/>
+      <c r="X16" s="48" t="n"/>
+      <c r="Y16" s="48" t="n"/>
+      <c r="Z16" s="48" t="n"/>
+      <c r="AA16" s="49" t="n"/>
       <c r="AB16" s="24" t="inlineStr">
         <is>
-          <t>REYES, ANTONIO MACAPAGAL</t>
-        </is>
-      </c>
-      <c r="AC16" s="54" t="n"/>
-      <c r="AD16" s="54" t="n"/>
-      <c r="AE16" s="55" t="n"/>
+          <t>REYES, ANTONIO MACAPAGAL REYES GARCIA</t>
+        </is>
+      </c>
+      <c r="AC16" s="48" t="n"/>
+      <c r="AD16" s="48" t="n"/>
+      <c r="AE16" s="49" t="n"/>
       <c r="AF16" s="24" t="inlineStr">
         <is>
-          <t>BAUTISTA, CARMEN DELOS</t>
-        </is>
-      </c>
-      <c r="AG16" s="54" t="n"/>
-      <c r="AH16" s="54" t="n"/>
-      <c r="AI16" s="54" t="n"/>
-      <c r="AJ16" s="55" t="n"/>
+          <t>SANTOS, CARMEN DELOS BAUTISTA TORRES</t>
+        </is>
+      </c>
+      <c r="AG16" s="48" t="n"/>
+      <c r="AH16" s="48" t="n"/>
+      <c r="AI16" s="48" t="n"/>
+      <c r="AJ16" s="49" t="n"/>
       <c r="AK16" s="24" t="n"/>
-      <c r="AL16" s="54" t="n"/>
-      <c r="AM16" s="54" t="n"/>
-      <c r="AN16" s="55" t="n"/>
+      <c r="AL16" s="48" t="n"/>
+      <c r="AM16" s="48" t="n"/>
+      <c r="AN16" s="49" t="n"/>
       <c r="AO16" s="24" t="n"/>
-      <c r="AP16" s="65" t="n"/>
-      <c r="AQ16" s="55" t="n"/>
+      <c r="AP16" s="59" t="n"/>
+      <c r="AQ16" s="49" t="n"/>
       <c r="AR16" s="21" t="inlineStr">
         <is>
           <t>Face To Face</t>
         </is>
       </c>
       <c r="AS16" s="21" t="n"/>
-      <c r="AT16" s="55" t="n"/>
+      <c r="AT16" s="49" t="n"/>
       <c r="AU16" s="2" t="n"/>
     </row>
     <row r="17" ht="27.75" customHeight="1">
@@ -2935,36 +2915,36 @@
           <t>117591120154</t>
         </is>
       </c>
-      <c r="B17" s="55" t="n"/>
+      <c r="B17" s="49" t="n"/>
       <c r="C17" s="24" t="inlineStr">
         <is>
           <t>TORRES, JESSICA CLAIRE</t>
         </is>
       </c>
-      <c r="D17" s="54" t="n"/>
-      <c r="E17" s="54" t="n"/>
-      <c r="F17" s="55" t="n"/>
+      <c r="D17" s="48" t="n"/>
+      <c r="E17" s="48" t="n"/>
+      <c r="F17" s="49" t="n"/>
       <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H17" s="64" t="inlineStr">
+      <c r="H17" s="58" t="inlineStr">
         <is>
           <t>2006-01-30</t>
         </is>
       </c>
-      <c r="I17" s="55" t="n"/>
+      <c r="I17" s="49" t="n"/>
       <c r="J17" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="K17" s="55" t="n"/>
+      <c r="K17" s="49" t="n"/>
       <c r="L17" s="24" t="inlineStr">
         <is>
           <t>Tagalog</t>
         </is>
       </c>
-      <c r="M17" s="55" t="n"/>
+      <c r="M17" s="49" t="n"/>
       <c r="N17" s="24" t="n"/>
       <c r="O17" s="24" t="inlineStr">
         <is>
@@ -2972,2235 +2952,2076 @@
         </is>
       </c>
       <c r="P17" s="24" t="n"/>
-      <c r="Q17" s="55" t="n"/>
+      <c r="Q17" s="49" t="n"/>
       <c r="R17" s="24" t="inlineStr">
         <is>
           <t>CABUGAO NORTE</t>
         </is>
       </c>
-      <c r="S17" s="54" t="n"/>
-      <c r="T17" s="55" t="n"/>
+      <c r="S17" s="48" t="n"/>
+      <c r="T17" s="49" t="n"/>
       <c r="U17" s="24" t="inlineStr">
         <is>
           <t>PAVIA</t>
         </is>
       </c>
-      <c r="V17" s="55" t="n"/>
+      <c r="V17" s="49" t="n"/>
       <c r="W17" s="24" t="inlineStr">
         <is>
           <t>ILOILO</t>
         </is>
       </c>
-      <c r="X17" s="54" t="n"/>
-      <c r="Y17" s="54" t="n"/>
-      <c r="Z17" s="54" t="n"/>
-      <c r="AA17" s="55" t="n"/>
+      <c r="X17" s="48" t="n"/>
+      <c r="Y17" s="48" t="n"/>
+      <c r="Z17" s="48" t="n"/>
+      <c r="AA17" s="49" t="n"/>
       <c r="AB17" s="24" t="inlineStr">
         <is>
           <t>TORRES, RAMON SANTOS</t>
         </is>
       </c>
-      <c r="AC17" s="54" t="n"/>
-      <c r="AD17" s="54" t="n"/>
-      <c r="AE17" s="55" t="n"/>
+      <c r="AC17" s="48" t="n"/>
+      <c r="AD17" s="48" t="n"/>
+      <c r="AE17" s="49" t="n"/>
       <c r="AF17" s="24" t="inlineStr">
         <is>
           <t>REYES, GLORIA MENDOZA</t>
         </is>
       </c>
-      <c r="AG17" s="54" t="n"/>
-      <c r="AH17" s="54" t="n"/>
-      <c r="AI17" s="54" t="n"/>
-      <c r="AJ17" s="55" t="n"/>
+      <c r="AG17" s="48" t="n"/>
+      <c r="AH17" s="48" t="n"/>
+      <c r="AI17" s="48" t="n"/>
+      <c r="AJ17" s="49" t="n"/>
       <c r="AK17" s="24" t="n"/>
-      <c r="AL17" s="54" t="n"/>
-      <c r="AM17" s="54" t="n"/>
-      <c r="AN17" s="55" t="n"/>
+      <c r="AL17" s="48" t="n"/>
+      <c r="AM17" s="48" t="n"/>
+      <c r="AN17" s="49" t="n"/>
       <c r="AO17" s="24" t="n"/>
-      <c r="AP17" s="65" t="n"/>
-      <c r="AQ17" s="55" t="n"/>
+      <c r="AP17" s="59" t="n"/>
+      <c r="AQ17" s="49" t="n"/>
       <c r="AR17" s="21" t="inlineStr">
         <is>
           <t>Face To Face</t>
         </is>
       </c>
       <c r="AS17" s="21" t="n"/>
-      <c r="AT17" s="55" t="n"/>
+      <c r="AT17" s="49" t="n"/>
       <c r="AU17" s="2" t="n"/>
     </row>
     <row r="18" ht="37.5" customHeight="1">
       <c r="A18" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="B18" s="55" t="n"/>
+      <c r="B18" s="49" t="n"/>
       <c r="C18" s="24" t="inlineStr">
         <is>
           <t>&lt;=== TOTAL FEMALE</t>
         </is>
       </c>
-      <c r="D18" s="54" t="n"/>
-      <c r="E18" s="54" t="n"/>
-      <c r="F18" s="55" t="n"/>
+      <c r="D18" s="48" t="n"/>
+      <c r="E18" s="48" t="n"/>
+      <c r="F18" s="49" t="n"/>
       <c r="G18" s="21" t="n"/>
-      <c r="H18" s="64" t="n"/>
-      <c r="I18" s="55" t="n"/>
+      <c r="H18" s="58" t="n"/>
+      <c r="I18" s="49" t="n"/>
       <c r="J18" s="21" t="n"/>
-      <c r="K18" s="55" t="n"/>
+      <c r="K18" s="49" t="n"/>
       <c r="L18" s="24" t="n"/>
-      <c r="M18" s="55" t="n"/>
+      <c r="M18" s="49" t="n"/>
       <c r="N18" s="24" t="n"/>
       <c r="O18" s="24" t="n"/>
       <c r="P18" s="24" t="n"/>
-      <c r="Q18" s="55" t="n"/>
+      <c r="Q18" s="49" t="n"/>
       <c r="R18" s="24" t="n"/>
-      <c r="S18" s="54" t="n"/>
-      <c r="T18" s="55" t="n"/>
+      <c r="S18" s="48" t="n"/>
+      <c r="T18" s="49" t="n"/>
       <c r="U18" s="24" t="n"/>
-      <c r="V18" s="55" t="n"/>
+      <c r="V18" s="49" t="n"/>
       <c r="W18" s="24" t="n"/>
-      <c r="X18" s="54" t="n"/>
-      <c r="Y18" s="54" t="n"/>
-      <c r="Z18" s="54" t="n"/>
-      <c r="AA18" s="55" t="n"/>
+      <c r="X18" s="48" t="n"/>
+      <c r="Y18" s="48" t="n"/>
+      <c r="Z18" s="48" t="n"/>
+      <c r="AA18" s="49" t="n"/>
       <c r="AB18" s="24" t="n"/>
-      <c r="AC18" s="54" t="n"/>
-      <c r="AD18" s="54" t="n"/>
-      <c r="AE18" s="55" t="n"/>
+      <c r="AC18" s="48" t="n"/>
+      <c r="AD18" s="48" t="n"/>
+      <c r="AE18" s="49" t="n"/>
       <c r="AF18" s="24" t="n"/>
-      <c r="AG18" s="54" t="n"/>
-      <c r="AH18" s="54" t="n"/>
-      <c r="AI18" s="54" t="n"/>
-      <c r="AJ18" s="55" t="n"/>
+      <c r="AG18" s="48" t="n"/>
+      <c r="AH18" s="48" t="n"/>
+      <c r="AI18" s="48" t="n"/>
+      <c r="AJ18" s="49" t="n"/>
       <c r="AK18" s="24" t="n"/>
-      <c r="AL18" s="54" t="n"/>
-      <c r="AM18" s="54" t="n"/>
-      <c r="AN18" s="55" t="n"/>
+      <c r="AL18" s="48" t="n"/>
+      <c r="AM18" s="48" t="n"/>
+      <c r="AN18" s="49" t="n"/>
       <c r="AO18" s="24" t="n"/>
-      <c r="AP18" s="65" t="n"/>
-      <c r="AQ18" s="55" t="n"/>
+      <c r="AP18" s="59" t="n"/>
+      <c r="AQ18" s="49" t="n"/>
       <c r="AR18" s="21" t="n"/>
       <c r="AS18" s="21" t="n"/>
-      <c r="AT18" s="55" t="n"/>
+      <c r="AT18" s="49" t="n"/>
       <c r="AU18" s="2" t="n"/>
     </row>
     <row r="19" ht="27.75" customHeight="1">
       <c r="A19" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="55" t="n"/>
+      <c r="B19" s="49" t="n"/>
       <c r="C19" s="24" t="inlineStr">
         <is>
           <t>&lt;=== TOTAL COMBINED</t>
         </is>
       </c>
-      <c r="D19" s="54" t="n"/>
-      <c r="E19" s="54" t="n"/>
-      <c r="F19" s="55" t="n"/>
+      <c r="D19" s="48" t="n"/>
+      <c r="E19" s="48" t="n"/>
+      <c r="F19" s="49" t="n"/>
       <c r="G19" s="21" t="n"/>
-      <c r="H19" s="64" t="n"/>
-      <c r="I19" s="55" t="n"/>
+      <c r="H19" s="58" t="n"/>
+      <c r="I19" s="49" t="n"/>
       <c r="J19" s="21" t="n"/>
-      <c r="K19" s="55" t="n"/>
+      <c r="K19" s="49" t="n"/>
       <c r="L19" s="24" t="n"/>
-      <c r="M19" s="55" t="n"/>
+      <c r="M19" s="49" t="n"/>
       <c r="N19" s="24" t="n"/>
       <c r="O19" s="24" t="n"/>
       <c r="P19" s="24" t="n"/>
-      <c r="Q19" s="55" t="n"/>
+      <c r="Q19" s="49" t="n"/>
       <c r="R19" s="24" t="n"/>
-      <c r="S19" s="54" t="n"/>
-      <c r="T19" s="55" t="n"/>
+      <c r="S19" s="48" t="n"/>
+      <c r="T19" s="49" t="n"/>
       <c r="U19" s="24" t="n"/>
-      <c r="V19" s="55" t="n"/>
+      <c r="V19" s="49" t="n"/>
       <c r="W19" s="24" t="n"/>
-      <c r="X19" s="54" t="n"/>
-      <c r="Y19" s="54" t="n"/>
-      <c r="Z19" s="54" t="n"/>
-      <c r="AA19" s="55" t="n"/>
+      <c r="X19" s="48" t="n"/>
+      <c r="Y19" s="48" t="n"/>
+      <c r="Z19" s="48" t="n"/>
+      <c r="AA19" s="49" t="n"/>
       <c r="AB19" s="24" t="n"/>
-      <c r="AC19" s="54" t="n"/>
-      <c r="AD19" s="54" t="n"/>
-      <c r="AE19" s="55" t="n"/>
+      <c r="AC19" s="48" t="n"/>
+      <c r="AD19" s="48" t="n"/>
+      <c r="AE19" s="49" t="n"/>
       <c r="AF19" s="24" t="n"/>
-      <c r="AG19" s="54" t="n"/>
-      <c r="AH19" s="54" t="n"/>
-      <c r="AI19" s="54" t="n"/>
-      <c r="AJ19" s="55" t="n"/>
+      <c r="AG19" s="48" t="n"/>
+      <c r="AH19" s="48" t="n"/>
+      <c r="AI19" s="48" t="n"/>
+      <c r="AJ19" s="49" t="n"/>
       <c r="AK19" s="24" t="n"/>
-      <c r="AL19" s="54" t="n"/>
-      <c r="AM19" s="54" t="n"/>
-      <c r="AN19" s="55" t="n"/>
+      <c r="AL19" s="48" t="n"/>
+      <c r="AM19" s="48" t="n"/>
+      <c r="AN19" s="49" t="n"/>
       <c r="AO19" s="24" t="n"/>
-      <c r="AP19" s="65" t="n"/>
-      <c r="AQ19" s="55" t="n"/>
+      <c r="AP19" s="59" t="n"/>
+      <c r="AQ19" s="49" t="n"/>
       <c r="AR19" s="21" t="n"/>
       <c r="AS19" s="21" t="n"/>
-      <c r="AT19" s="55" t="n"/>
+      <c r="AT19" s="49" t="n"/>
       <c r="AU19" s="2" t="n"/>
     </row>
-    <row r="20" ht="46.5" customHeight="1">
+    <row r="20" hidden="1" ht="46.5" customHeight="1">
       <c r="A20" s="24" t="n"/>
-      <c r="B20" s="55" t="n"/>
+      <c r="B20" s="49" t="n"/>
       <c r="C20" s="24" t="n"/>
-      <c r="D20" s="54" t="n"/>
-      <c r="E20" s="54" t="n"/>
-      <c r="F20" s="55" t="n"/>
+      <c r="D20" s="48" t="n"/>
+      <c r="E20" s="48" t="n"/>
+      <c r="F20" s="49" t="n"/>
       <c r="G20" s="21" t="n"/>
-      <c r="H20" s="64" t="n"/>
-      <c r="I20" s="55" t="n"/>
+      <c r="H20" s="58" t="n"/>
+      <c r="I20" s="49" t="n"/>
       <c r="J20" s="21" t="n"/>
-      <c r="K20" s="55" t="n"/>
+      <c r="K20" s="49" t="n"/>
       <c r="L20" s="24" t="n"/>
-      <c r="M20" s="55" t="n"/>
+      <c r="M20" s="49" t="n"/>
       <c r="N20" s="24" t="n"/>
       <c r="O20" s="24" t="n"/>
       <c r="P20" s="24" t="n"/>
-      <c r="Q20" s="55" t="n"/>
+      <c r="Q20" s="49" t="n"/>
       <c r="R20" s="24" t="n"/>
-      <c r="S20" s="54" t="n"/>
-      <c r="T20" s="55" t="n"/>
+      <c r="S20" s="48" t="n"/>
+      <c r="T20" s="49" t="n"/>
       <c r="U20" s="24" t="n"/>
-      <c r="V20" s="55" t="n"/>
+      <c r="V20" s="49" t="n"/>
       <c r="W20" s="24" t="n"/>
-      <c r="X20" s="54" t="n"/>
-      <c r="Y20" s="54" t="n"/>
-      <c r="Z20" s="54" t="n"/>
-      <c r="AA20" s="55" t="n"/>
+      <c r="X20" s="48" t="n"/>
+      <c r="Y20" s="48" t="n"/>
+      <c r="Z20" s="48" t="n"/>
+      <c r="AA20" s="49" t="n"/>
       <c r="AB20" s="24" t="n"/>
-      <c r="AC20" s="54" t="n"/>
-      <c r="AD20" s="54" t="n"/>
-      <c r="AE20" s="55" t="n"/>
+      <c r="AC20" s="48" t="n"/>
+      <c r="AD20" s="48" t="n"/>
+      <c r="AE20" s="49" t="n"/>
       <c r="AF20" s="24" t="n"/>
-      <c r="AG20" s="54" t="n"/>
-      <c r="AH20" s="54" t="n"/>
-      <c r="AI20" s="54" t="n"/>
-      <c r="AJ20" s="55" t="n"/>
+      <c r="AG20" s="48" t="n"/>
+      <c r="AH20" s="48" t="n"/>
+      <c r="AI20" s="48" t="n"/>
+      <c r="AJ20" s="49" t="n"/>
       <c r="AK20" s="24" t="n"/>
-      <c r="AL20" s="54" t="n"/>
-      <c r="AM20" s="54" t="n"/>
-      <c r="AN20" s="55" t="n"/>
+      <c r="AL20" s="48" t="n"/>
+      <c r="AM20" s="48" t="n"/>
+      <c r="AN20" s="49" t="n"/>
       <c r="AO20" s="24" t="n"/>
-      <c r="AP20" s="65" t="n"/>
-      <c r="AQ20" s="55" t="n"/>
+      <c r="AP20" s="59" t="n"/>
+      <c r="AQ20" s="49" t="n"/>
       <c r="AR20" s="21" t="n"/>
       <c r="AS20" s="21" t="n"/>
-      <c r="AT20" s="55" t="n"/>
+      <c r="AT20" s="49" t="n"/>
       <c r="AU20" s="2" t="n"/>
     </row>
-    <row r="21" ht="37.5" customHeight="1">
+    <row r="21" hidden="1" ht="37.5" customHeight="1">
       <c r="A21" s="24" t="n"/>
-      <c r="B21" s="55" t="n"/>
+      <c r="B21" s="49" t="n"/>
       <c r="C21" s="24" t="n"/>
-      <c r="D21" s="54" t="n"/>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="55" t="n"/>
+      <c r="D21" s="48" t="n"/>
+      <c r="E21" s="48" t="n"/>
+      <c r="F21" s="49" t="n"/>
       <c r="G21" s="21" t="n"/>
-      <c r="H21" s="64" t="n"/>
-      <c r="I21" s="55" t="n"/>
+      <c r="H21" s="58" t="n"/>
+      <c r="I21" s="49" t="n"/>
       <c r="J21" s="21" t="n"/>
-      <c r="K21" s="55" t="n"/>
+      <c r="K21" s="49" t="n"/>
       <c r="L21" s="24" t="n"/>
-      <c r="M21" s="55" t="n"/>
+      <c r="M21" s="49" t="n"/>
       <c r="N21" s="24" t="n"/>
       <c r="O21" s="24" t="n"/>
       <c r="P21" s="24" t="n"/>
-      <c r="Q21" s="55" t="n"/>
+      <c r="Q21" s="49" t="n"/>
       <c r="R21" s="24" t="n"/>
-      <c r="S21" s="54" t="n"/>
-      <c r="T21" s="55" t="n"/>
+      <c r="S21" s="48" t="n"/>
+      <c r="T21" s="49" t="n"/>
       <c r="U21" s="24" t="n"/>
-      <c r="V21" s="55" t="n"/>
+      <c r="V21" s="49" t="n"/>
       <c r="W21" s="24" t="n"/>
-      <c r="X21" s="54" t="n"/>
-      <c r="Y21" s="54" t="n"/>
-      <c r="Z21" s="54" t="n"/>
-      <c r="AA21" s="55" t="n"/>
+      <c r="X21" s="48" t="n"/>
+      <c r="Y21" s="48" t="n"/>
+      <c r="Z21" s="48" t="n"/>
+      <c r="AA21" s="49" t="n"/>
       <c r="AB21" s="24" t="n"/>
-      <c r="AC21" s="54" t="n"/>
-      <c r="AD21" s="54" t="n"/>
-      <c r="AE21" s="55" t="n"/>
+      <c r="AC21" s="48" t="n"/>
+      <c r="AD21" s="48" t="n"/>
+      <c r="AE21" s="49" t="n"/>
       <c r="AF21" s="24" t="n"/>
-      <c r="AG21" s="54" t="n"/>
-      <c r="AH21" s="54" t="n"/>
-      <c r="AI21" s="54" t="n"/>
-      <c r="AJ21" s="55" t="n"/>
+      <c r="AG21" s="48" t="n"/>
+      <c r="AH21" s="48" t="n"/>
+      <c r="AI21" s="48" t="n"/>
+      <c r="AJ21" s="49" t="n"/>
       <c r="AK21" s="24" t="n"/>
-      <c r="AL21" s="54" t="n"/>
-      <c r="AM21" s="54" t="n"/>
-      <c r="AN21" s="55" t="n"/>
+      <c r="AL21" s="48" t="n"/>
+      <c r="AM21" s="48" t="n"/>
+      <c r="AN21" s="49" t="n"/>
       <c r="AO21" s="24" t="n"/>
-      <c r="AP21" s="65" t="n"/>
-      <c r="AQ21" s="55" t="n"/>
+      <c r="AP21" s="59" t="n"/>
+      <c r="AQ21" s="49" t="n"/>
       <c r="AR21" s="21" t="n"/>
       <c r="AS21" s="21" t="n"/>
-      <c r="AT21" s="55" t="n"/>
+      <c r="AT21" s="49" t="n"/>
       <c r="AU21" s="2" t="n"/>
     </row>
-    <row r="22" ht="27.75" customHeight="1">
+    <row r="22" hidden="1" ht="27.75" customHeight="1">
       <c r="A22" s="24" t="n"/>
-      <c r="B22" s="55" t="n"/>
+      <c r="B22" s="49" t="n"/>
       <c r="C22" s="24" t="n"/>
-      <c r="D22" s="54" t="n"/>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="55" t="n"/>
+      <c r="D22" s="48" t="n"/>
+      <c r="E22" s="48" t="n"/>
+      <c r="F22" s="49" t="n"/>
       <c r="G22" s="21" t="n"/>
-      <c r="H22" s="64" t="n"/>
-      <c r="I22" s="55" t="n"/>
+      <c r="H22" s="58" t="n"/>
+      <c r="I22" s="49" t="n"/>
       <c r="J22" s="21" t="n"/>
-      <c r="K22" s="55" t="n"/>
+      <c r="K22" s="49" t="n"/>
       <c r="L22" s="24" t="n"/>
-      <c r="M22" s="55" t="n"/>
+      <c r="M22" s="49" t="n"/>
       <c r="N22" s="24" t="n"/>
       <c r="O22" s="24" t="n"/>
       <c r="P22" s="24" t="n"/>
-      <c r="Q22" s="55" t="n"/>
+      <c r="Q22" s="49" t="n"/>
       <c r="R22" s="24" t="n"/>
-      <c r="S22" s="54" t="n"/>
-      <c r="T22" s="55" t="n"/>
+      <c r="S22" s="48" t="n"/>
+      <c r="T22" s="49" t="n"/>
       <c r="U22" s="24" t="n"/>
-      <c r="V22" s="55" t="n"/>
+      <c r="V22" s="49" t="n"/>
       <c r="W22" s="24" t="n"/>
-      <c r="X22" s="54" t="n"/>
-      <c r="Y22" s="54" t="n"/>
-      <c r="Z22" s="54" t="n"/>
-      <c r="AA22" s="55" t="n"/>
+      <c r="X22" s="48" t="n"/>
+      <c r="Y22" s="48" t="n"/>
+      <c r="Z22" s="48" t="n"/>
+      <c r="AA22" s="49" t="n"/>
       <c r="AB22" s="24" t="n"/>
-      <c r="AC22" s="54" t="n"/>
-      <c r="AD22" s="54" t="n"/>
-      <c r="AE22" s="55" t="n"/>
+      <c r="AC22" s="48" t="n"/>
+      <c r="AD22" s="48" t="n"/>
+      <c r="AE22" s="49" t="n"/>
       <c r="AF22" s="24" t="n"/>
-      <c r="AG22" s="54" t="n"/>
-      <c r="AH22" s="54" t="n"/>
-      <c r="AI22" s="54" t="n"/>
-      <c r="AJ22" s="55" t="n"/>
+      <c r="AG22" s="48" t="n"/>
+      <c r="AH22" s="48" t="n"/>
+      <c r="AI22" s="48" t="n"/>
+      <c r="AJ22" s="49" t="n"/>
       <c r="AK22" s="24" t="n"/>
-      <c r="AL22" s="54" t="n"/>
-      <c r="AM22" s="54" t="n"/>
-      <c r="AN22" s="55" t="n"/>
+      <c r="AL22" s="48" t="n"/>
+      <c r="AM22" s="48" t="n"/>
+      <c r="AN22" s="49" t="n"/>
       <c r="AO22" s="24" t="n"/>
-      <c r="AP22" s="65" t="n"/>
-      <c r="AQ22" s="55" t="n"/>
+      <c r="AP22" s="59" t="n"/>
+      <c r="AQ22" s="49" t="n"/>
       <c r="AR22" s="21" t="n"/>
       <c r="AS22" s="21" t="n"/>
-      <c r="AT22" s="55" t="n"/>
+      <c r="AT22" s="49" t="n"/>
       <c r="AU22" s="2" t="n"/>
     </row>
-    <row r="23" ht="27.75" customHeight="1">
+    <row r="23" hidden="1" ht="27.75" customHeight="1">
       <c r="A23" s="24" t="n"/>
-      <c r="B23" s="55" t="n"/>
+      <c r="B23" s="49" t="n"/>
       <c r="C23" s="24" t="n"/>
-      <c r="D23" s="54" t="n"/>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="55" t="n"/>
+      <c r="D23" s="48" t="n"/>
+      <c r="E23" s="48" t="n"/>
+      <c r="F23" s="49" t="n"/>
       <c r="G23" s="21" t="n"/>
-      <c r="H23" s="64" t="n"/>
-      <c r="I23" s="55" t="n"/>
+      <c r="H23" s="58" t="n"/>
+      <c r="I23" s="49" t="n"/>
       <c r="J23" s="21" t="n"/>
-      <c r="K23" s="55" t="n"/>
+      <c r="K23" s="49" t="n"/>
       <c r="L23" s="24" t="n"/>
-      <c r="M23" s="55" t="n"/>
+      <c r="M23" s="49" t="n"/>
       <c r="N23" s="24" t="n"/>
       <c r="O23" s="24" t="n"/>
       <c r="P23" s="24" t="n"/>
-      <c r="Q23" s="55" t="n"/>
+      <c r="Q23" s="49" t="n"/>
       <c r="R23" s="24" t="n"/>
-      <c r="S23" s="54" t="n"/>
-      <c r="T23" s="55" t="n"/>
+      <c r="S23" s="48" t="n"/>
+      <c r="T23" s="49" t="n"/>
       <c r="U23" s="24" t="n"/>
-      <c r="V23" s="55" t="n"/>
+      <c r="V23" s="49" t="n"/>
       <c r="W23" s="24" t="n"/>
-      <c r="X23" s="54" t="n"/>
-      <c r="Y23" s="54" t="n"/>
-      <c r="Z23" s="54" t="n"/>
-      <c r="AA23" s="55" t="n"/>
+      <c r="X23" s="48" t="n"/>
+      <c r="Y23" s="48" t="n"/>
+      <c r="Z23" s="48" t="n"/>
+      <c r="AA23" s="49" t="n"/>
       <c r="AB23" s="24" t="n"/>
-      <c r="AC23" s="54" t="n"/>
-      <c r="AD23" s="54" t="n"/>
-      <c r="AE23" s="55" t="n"/>
+      <c r="AC23" s="48" t="n"/>
+      <c r="AD23" s="48" t="n"/>
+      <c r="AE23" s="49" t="n"/>
       <c r="AF23" s="24" t="n"/>
-      <c r="AG23" s="54" t="n"/>
-      <c r="AH23" s="54" t="n"/>
-      <c r="AI23" s="54" t="n"/>
-      <c r="AJ23" s="55" t="n"/>
+      <c r="AG23" s="48" t="n"/>
+      <c r="AH23" s="48" t="n"/>
+      <c r="AI23" s="48" t="n"/>
+      <c r="AJ23" s="49" t="n"/>
       <c r="AK23" s="24" t="n"/>
-      <c r="AL23" s="54" t="n"/>
-      <c r="AM23" s="54" t="n"/>
-      <c r="AN23" s="55" t="n"/>
+      <c r="AL23" s="48" t="n"/>
+      <c r="AM23" s="48" t="n"/>
+      <c r="AN23" s="49" t="n"/>
       <c r="AO23" s="24" t="n"/>
-      <c r="AP23" s="65" t="n"/>
-      <c r="AQ23" s="55" t="n"/>
+      <c r="AP23" s="59" t="n"/>
+      <c r="AQ23" s="49" t="n"/>
       <c r="AR23" s="21" t="n"/>
       <c r="AS23" s="21" t="n"/>
-      <c r="AT23" s="55" t="n"/>
+      <c r="AT23" s="49" t="n"/>
       <c r="AU23" s="2" t="n"/>
     </row>
-    <row r="24" ht="37.5" customHeight="1">
+    <row r="24" hidden="1" ht="37.5" customHeight="1">
       <c r="A24" s="24" t="n"/>
-      <c r="B24" s="55" t="n"/>
+      <c r="B24" s="49" t="n"/>
       <c r="C24" s="24" t="n"/>
-      <c r="D24" s="54" t="n"/>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="55" t="n"/>
+      <c r="D24" s="48" t="n"/>
+      <c r="E24" s="48" t="n"/>
+      <c r="F24" s="49" t="n"/>
       <c r="G24" s="21" t="n"/>
-      <c r="H24" s="64" t="n"/>
-      <c r="I24" s="55" t="n"/>
+      <c r="H24" s="58" t="n"/>
+      <c r="I24" s="49" t="n"/>
       <c r="J24" s="21" t="n"/>
-      <c r="K24" s="55" t="n"/>
+      <c r="K24" s="49" t="n"/>
       <c r="L24" s="24" t="n"/>
-      <c r="M24" s="55" t="n"/>
+      <c r="M24" s="49" t="n"/>
       <c r="N24" s="24" t="n"/>
       <c r="O24" s="24" t="n"/>
       <c r="P24" s="24" t="n"/>
-      <c r="Q24" s="55" t="n"/>
+      <c r="Q24" s="49" t="n"/>
       <c r="R24" s="24" t="n"/>
-      <c r="S24" s="54" t="n"/>
-      <c r="T24" s="55" t="n"/>
+      <c r="S24" s="48" t="n"/>
+      <c r="T24" s="49" t="n"/>
       <c r="U24" s="24" t="n"/>
-      <c r="V24" s="55" t="n"/>
+      <c r="V24" s="49" t="n"/>
       <c r="W24" s="24" t="n"/>
-      <c r="X24" s="54" t="n"/>
-      <c r="Y24" s="54" t="n"/>
-      <c r="Z24" s="54" t="n"/>
-      <c r="AA24" s="55" t="n"/>
+      <c r="X24" s="48" t="n"/>
+      <c r="Y24" s="48" t="n"/>
+      <c r="Z24" s="48" t="n"/>
+      <c r="AA24" s="49" t="n"/>
       <c r="AB24" s="24" t="n"/>
-      <c r="AC24" s="54" t="n"/>
-      <c r="AD24" s="54" t="n"/>
-      <c r="AE24" s="55" t="n"/>
+      <c r="AC24" s="48" t="n"/>
+      <c r="AD24" s="48" t="n"/>
+      <c r="AE24" s="49" t="n"/>
       <c r="AF24" s="24" t="n"/>
-      <c r="AG24" s="54" t="n"/>
-      <c r="AH24" s="54" t="n"/>
-      <c r="AI24" s="54" t="n"/>
-      <c r="AJ24" s="55" t="n"/>
+      <c r="AG24" s="48" t="n"/>
+      <c r="AH24" s="48" t="n"/>
+      <c r="AI24" s="48" t="n"/>
+      <c r="AJ24" s="49" t="n"/>
       <c r="AK24" s="24" t="n"/>
-      <c r="AL24" s="54" t="n"/>
-      <c r="AM24" s="54" t="n"/>
-      <c r="AN24" s="55" t="n"/>
+      <c r="AL24" s="48" t="n"/>
+      <c r="AM24" s="48" t="n"/>
+      <c r="AN24" s="49" t="n"/>
       <c r="AO24" s="24" t="n"/>
-      <c r="AP24" s="65" t="n"/>
-      <c r="AQ24" s="55" t="n"/>
+      <c r="AP24" s="59" t="n"/>
+      <c r="AQ24" s="49" t="n"/>
       <c r="AR24" s="21" t="n"/>
       <c r="AS24" s="21" t="n"/>
-      <c r="AT24" s="55" t="n"/>
+      <c r="AT24" s="49" t="n"/>
       <c r="AU24" s="2" t="n"/>
     </row>
-    <row r="25" ht="27.75" customHeight="1">
+    <row r="25" hidden="1" ht="27.75" customHeight="1">
       <c r="A25" s="24" t="n"/>
-      <c r="B25" s="55" t="n"/>
+      <c r="B25" s="49" t="n"/>
       <c r="C25" s="24" t="n"/>
-      <c r="D25" s="54" t="n"/>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="55" t="n"/>
+      <c r="D25" s="48" t="n"/>
+      <c r="E25" s="48" t="n"/>
+      <c r="F25" s="49" t="n"/>
       <c r="G25" s="21" t="n"/>
-      <c r="H25" s="64" t="n"/>
-      <c r="I25" s="55" t="n"/>
+      <c r="H25" s="58" t="n"/>
+      <c r="I25" s="49" t="n"/>
       <c r="J25" s="21" t="n"/>
-      <c r="K25" s="55" t="n"/>
+      <c r="K25" s="49" t="n"/>
       <c r="L25" s="24" t="n"/>
-      <c r="M25" s="55" t="n"/>
+      <c r="M25" s="49" t="n"/>
       <c r="N25" s="24" t="n"/>
       <c r="O25" s="24" t="n"/>
       <c r="P25" s="24" t="n"/>
-      <c r="Q25" s="55" t="n"/>
+      <c r="Q25" s="49" t="n"/>
       <c r="R25" s="24" t="n"/>
-      <c r="S25" s="54" t="n"/>
-      <c r="T25" s="55" t="n"/>
+      <c r="S25" s="48" t="n"/>
+      <c r="T25" s="49" t="n"/>
       <c r="U25" s="24" t="n"/>
-      <c r="V25" s="55" t="n"/>
+      <c r="V25" s="49" t="n"/>
       <c r="W25" s="24" t="n"/>
-      <c r="X25" s="54" t="n"/>
-      <c r="Y25" s="54" t="n"/>
-      <c r="Z25" s="54" t="n"/>
-      <c r="AA25" s="55" t="n"/>
+      <c r="X25" s="48" t="n"/>
+      <c r="Y25" s="48" t="n"/>
+      <c r="Z25" s="48" t="n"/>
+      <c r="AA25" s="49" t="n"/>
       <c r="AB25" s="24" t="n"/>
-      <c r="AC25" s="54" t="n"/>
-      <c r="AD25" s="54" t="n"/>
-      <c r="AE25" s="55" t="n"/>
+      <c r="AC25" s="48" t="n"/>
+      <c r="AD25" s="48" t="n"/>
+      <c r="AE25" s="49" t="n"/>
       <c r="AF25" s="24" t="n"/>
-      <c r="AG25" s="54" t="n"/>
-      <c r="AH25" s="54" t="n"/>
-      <c r="AI25" s="54" t="n"/>
-      <c r="AJ25" s="55" t="n"/>
+      <c r="AG25" s="48" t="n"/>
+      <c r="AH25" s="48" t="n"/>
+      <c r="AI25" s="48" t="n"/>
+      <c r="AJ25" s="49" t="n"/>
       <c r="AK25" s="24" t="n"/>
-      <c r="AL25" s="54" t="n"/>
-      <c r="AM25" s="54" t="n"/>
-      <c r="AN25" s="55" t="n"/>
+      <c r="AL25" s="48" t="n"/>
+      <c r="AM25" s="48" t="n"/>
+      <c r="AN25" s="49" t="n"/>
       <c r="AO25" s="24" t="n"/>
-      <c r="AP25" s="65" t="n"/>
-      <c r="AQ25" s="55" t="n"/>
+      <c r="AP25" s="59" t="n"/>
+      <c r="AQ25" s="49" t="n"/>
       <c r="AR25" s="21" t="n"/>
       <c r="AS25" s="21" t="n"/>
-      <c r="AT25" s="55" t="n"/>
+      <c r="AT25" s="49" t="n"/>
       <c r="AU25" s="2" t="n"/>
     </row>
-    <row r="26" ht="27.75" customHeight="1">
+    <row r="26" hidden="1" ht="27.75" customHeight="1">
       <c r="A26" s="24" t="n"/>
-      <c r="B26" s="55" t="n"/>
+      <c r="B26" s="49" t="n"/>
       <c r="C26" s="24" t="n"/>
-      <c r="D26" s="54" t="n"/>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="55" t="n"/>
+      <c r="D26" s="48" t="n"/>
+      <c r="E26" s="48" t="n"/>
+      <c r="F26" s="49" t="n"/>
       <c r="G26" s="21" t="n"/>
-      <c r="H26" s="64" t="n"/>
-      <c r="I26" s="55" t="n"/>
+      <c r="H26" s="58" t="n"/>
+      <c r="I26" s="49" t="n"/>
       <c r="J26" s="21" t="n"/>
-      <c r="K26" s="55" t="n"/>
+      <c r="K26" s="49" t="n"/>
       <c r="L26" s="24" t="n"/>
-      <c r="M26" s="55" t="n"/>
+      <c r="M26" s="49" t="n"/>
       <c r="N26" s="24" t="n"/>
       <c r="O26" s="24" t="n"/>
       <c r="P26" s="24" t="n"/>
-      <c r="Q26" s="55" t="n"/>
+      <c r="Q26" s="49" t="n"/>
       <c r="R26" s="24" t="n"/>
-      <c r="S26" s="54" t="n"/>
-      <c r="T26" s="55" t="n"/>
+      <c r="S26" s="48" t="n"/>
+      <c r="T26" s="49" t="n"/>
       <c r="U26" s="24" t="n"/>
-      <c r="V26" s="55" t="n"/>
+      <c r="V26" s="49" t="n"/>
       <c r="W26" s="24" t="n"/>
-      <c r="X26" s="54" t="n"/>
-      <c r="Y26" s="54" t="n"/>
-      <c r="Z26" s="54" t="n"/>
-      <c r="AA26" s="55" t="n"/>
+      <c r="X26" s="48" t="n"/>
+      <c r="Y26" s="48" t="n"/>
+      <c r="Z26" s="48" t="n"/>
+      <c r="AA26" s="49" t="n"/>
       <c r="AB26" s="24" t="n"/>
-      <c r="AC26" s="54" t="n"/>
-      <c r="AD26" s="54" t="n"/>
-      <c r="AE26" s="55" t="n"/>
+      <c r="AC26" s="48" t="n"/>
+      <c r="AD26" s="48" t="n"/>
+      <c r="AE26" s="49" t="n"/>
       <c r="AF26" s="24" t="n"/>
-      <c r="AG26" s="54" t="n"/>
-      <c r="AH26" s="54" t="n"/>
-      <c r="AI26" s="54" t="n"/>
-      <c r="AJ26" s="55" t="n"/>
+      <c r="AG26" s="48" t="n"/>
+      <c r="AH26" s="48" t="n"/>
+      <c r="AI26" s="48" t="n"/>
+      <c r="AJ26" s="49" t="n"/>
       <c r="AK26" s="24" t="n"/>
-      <c r="AL26" s="54" t="n"/>
-      <c r="AM26" s="54" t="n"/>
-      <c r="AN26" s="55" t="n"/>
+      <c r="AL26" s="48" t="n"/>
+      <c r="AM26" s="48" t="n"/>
+      <c r="AN26" s="49" t="n"/>
       <c r="AO26" s="24" t="n"/>
-      <c r="AP26" s="65" t="n"/>
-      <c r="AQ26" s="55" t="n"/>
+      <c r="AP26" s="59" t="n"/>
+      <c r="AQ26" s="49" t="n"/>
       <c r="AR26" s="21" t="n"/>
       <c r="AS26" s="21" t="n"/>
-      <c r="AT26" s="55" t="n"/>
+      <c r="AT26" s="49" t="n"/>
       <c r="AU26" s="2" t="n"/>
     </row>
-    <row r="27" ht="19.5" customHeight="1">
+    <row r="27" hidden="1" ht="19.5" customHeight="1">
       <c r="A27" s="24" t="n"/>
-      <c r="B27" s="55" t="n"/>
+      <c r="B27" s="49" t="n"/>
       <c r="C27" s="24" t="n"/>
-      <c r="D27" s="54" t="n"/>
-      <c r="E27" s="54" t="n"/>
-      <c r="F27" s="55" t="n"/>
+      <c r="D27" s="48" t="n"/>
+      <c r="E27" s="48" t="n"/>
+      <c r="F27" s="49" t="n"/>
       <c r="G27" s="21" t="n"/>
-      <c r="H27" s="64" t="n"/>
-      <c r="I27" s="55" t="n"/>
+      <c r="H27" s="58" t="n"/>
+      <c r="I27" s="49" t="n"/>
       <c r="J27" s="21" t="n"/>
-      <c r="K27" s="55" t="n"/>
+      <c r="K27" s="49" t="n"/>
       <c r="L27" s="24" t="n"/>
-      <c r="M27" s="55" t="n"/>
+      <c r="M27" s="49" t="n"/>
       <c r="N27" s="24" t="n"/>
       <c r="O27" s="24" t="n"/>
       <c r="P27" s="24" t="n"/>
-      <c r="Q27" s="55" t="n"/>
+      <c r="Q27" s="49" t="n"/>
       <c r="R27" s="24" t="n"/>
-      <c r="S27" s="54" t="n"/>
-      <c r="T27" s="55" t="n"/>
+      <c r="S27" s="48" t="n"/>
+      <c r="T27" s="49" t="n"/>
       <c r="U27" s="24" t="n"/>
-      <c r="V27" s="55" t="n"/>
+      <c r="V27" s="49" t="n"/>
       <c r="W27" s="24" t="n"/>
-      <c r="X27" s="54" t="n"/>
-      <c r="Y27" s="54" t="n"/>
-      <c r="Z27" s="54" t="n"/>
-      <c r="AA27" s="55" t="n"/>
+      <c r="X27" s="48" t="n"/>
+      <c r="Y27" s="48" t="n"/>
+      <c r="Z27" s="48" t="n"/>
+      <c r="AA27" s="49" t="n"/>
       <c r="AB27" s="24" t="n"/>
-      <c r="AC27" s="54" t="n"/>
-      <c r="AD27" s="54" t="n"/>
-      <c r="AE27" s="55" t="n"/>
+      <c r="AC27" s="48" t="n"/>
+      <c r="AD27" s="48" t="n"/>
+      <c r="AE27" s="49" t="n"/>
       <c r="AF27" s="24" t="n"/>
-      <c r="AG27" s="54" t="n"/>
-      <c r="AH27" s="54" t="n"/>
-      <c r="AI27" s="54" t="n"/>
-      <c r="AJ27" s="55" t="n"/>
+      <c r="AG27" s="48" t="n"/>
+      <c r="AH27" s="48" t="n"/>
+      <c r="AI27" s="48" t="n"/>
+      <c r="AJ27" s="49" t="n"/>
       <c r="AK27" s="24" t="n"/>
-      <c r="AL27" s="54" t="n"/>
-      <c r="AM27" s="54" t="n"/>
-      <c r="AN27" s="55" t="n"/>
+      <c r="AL27" s="48" t="n"/>
+      <c r="AM27" s="48" t="n"/>
+      <c r="AN27" s="49" t="n"/>
       <c r="AO27" s="24" t="n"/>
-      <c r="AP27" s="65" t="n"/>
-      <c r="AQ27" s="55" t="n"/>
+      <c r="AP27" s="59" t="n"/>
+      <c r="AQ27" s="49" t="n"/>
       <c r="AR27" s="21" t="n"/>
       <c r="AS27" s="21" t="n"/>
-      <c r="AT27" s="55" t="n"/>
+      <c r="AT27" s="49" t="n"/>
       <c r="AU27" s="2" t="n"/>
     </row>
-    <row r="28" ht="46.5" customHeight="1">
+    <row r="28" hidden="1" ht="46.5" customHeight="1">
       <c r="A28" s="24" t="n"/>
-      <c r="B28" s="55" t="n"/>
+      <c r="B28" s="49" t="n"/>
       <c r="C28" s="24" t="n"/>
-      <c r="D28" s="54" t="n"/>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="55" t="n"/>
+      <c r="D28" s="48" t="n"/>
+      <c r="E28" s="48" t="n"/>
+      <c r="F28" s="49" t="n"/>
       <c r="G28" s="21" t="n"/>
-      <c r="H28" s="64" t="n"/>
-      <c r="I28" s="55" t="n"/>
+      <c r="H28" s="58" t="n"/>
+      <c r="I28" s="49" t="n"/>
       <c r="J28" s="21" t="n"/>
-      <c r="K28" s="55" t="n"/>
+      <c r="K28" s="49" t="n"/>
       <c r="L28" s="24" t="n"/>
-      <c r="M28" s="55" t="n"/>
+      <c r="M28" s="49" t="n"/>
       <c r="N28" s="24" t="n"/>
       <c r="O28" s="24" t="n"/>
       <c r="P28" s="24" t="n"/>
-      <c r="Q28" s="55" t="n"/>
+      <c r="Q28" s="49" t="n"/>
       <c r="R28" s="24" t="n"/>
-      <c r="S28" s="54" t="n"/>
-      <c r="T28" s="55" t="n"/>
+      <c r="S28" s="48" t="n"/>
+      <c r="T28" s="49" t="n"/>
       <c r="U28" s="24" t="n"/>
-      <c r="V28" s="55" t="n"/>
+      <c r="V28" s="49" t="n"/>
       <c r="W28" s="24" t="n"/>
-      <c r="X28" s="54" t="n"/>
-      <c r="Y28" s="54" t="n"/>
-      <c r="Z28" s="54" t="n"/>
-      <c r="AA28" s="55" t="n"/>
+      <c r="X28" s="48" t="n"/>
+      <c r="Y28" s="48" t="n"/>
+      <c r="Z28" s="48" t="n"/>
+      <c r="AA28" s="49" t="n"/>
       <c r="AB28" s="24" t="n"/>
-      <c r="AC28" s="54" t="n"/>
-      <c r="AD28" s="54" t="n"/>
-      <c r="AE28" s="55" t="n"/>
+      <c r="AC28" s="48" t="n"/>
+      <c r="AD28" s="48" t="n"/>
+      <c r="AE28" s="49" t="n"/>
       <c r="AF28" s="24" t="n"/>
-      <c r="AG28" s="54" t="n"/>
-      <c r="AH28" s="54" t="n"/>
-      <c r="AI28" s="54" t="n"/>
-      <c r="AJ28" s="55" t="n"/>
+      <c r="AG28" s="48" t="n"/>
+      <c r="AH28" s="48" t="n"/>
+      <c r="AI28" s="48" t="n"/>
+      <c r="AJ28" s="49" t="n"/>
       <c r="AK28" s="24" t="n"/>
-      <c r="AL28" s="54" t="n"/>
-      <c r="AM28" s="54" t="n"/>
-      <c r="AN28" s="55" t="n"/>
+      <c r="AL28" s="48" t="n"/>
+      <c r="AM28" s="48" t="n"/>
+      <c r="AN28" s="49" t="n"/>
       <c r="AO28" s="24" t="n"/>
-      <c r="AP28" s="65" t="n"/>
-      <c r="AQ28" s="55" t="n"/>
+      <c r="AP28" s="59" t="n"/>
+      <c r="AQ28" s="49" t="n"/>
       <c r="AR28" s="21" t="n"/>
       <c r="AS28" s="21" t="n"/>
-      <c r="AT28" s="55" t="n"/>
+      <c r="AT28" s="49" t="n"/>
       <c r="AU28" s="2" t="n"/>
     </row>
-    <row r="29" ht="27.75" customHeight="1">
+    <row r="29" hidden="1" ht="27.75" customHeight="1">
       <c r="A29" s="24" t="n"/>
-      <c r="B29" s="55" t="n"/>
+      <c r="B29" s="49" t="n"/>
       <c r="C29" s="24" t="n"/>
-      <c r="D29" s="54" t="n"/>
-      <c r="E29" s="54" t="n"/>
-      <c r="F29" s="55" t="n"/>
+      <c r="D29" s="48" t="n"/>
+      <c r="E29" s="48" t="n"/>
+      <c r="F29" s="49" t="n"/>
       <c r="G29" s="21" t="n"/>
-      <c r="H29" s="64" t="n"/>
-      <c r="I29" s="55" t="n"/>
+      <c r="H29" s="58" t="n"/>
+      <c r="I29" s="49" t="n"/>
       <c r="J29" s="21" t="n"/>
-      <c r="K29" s="55" t="n"/>
+      <c r="K29" s="49" t="n"/>
       <c r="L29" s="24" t="n"/>
-      <c r="M29" s="55" t="n"/>
+      <c r="M29" s="49" t="n"/>
       <c r="N29" s="24" t="n"/>
       <c r="O29" s="24" t="n"/>
       <c r="P29" s="24" t="n"/>
-      <c r="Q29" s="55" t="n"/>
+      <c r="Q29" s="49" t="n"/>
       <c r="R29" s="24" t="n"/>
-      <c r="S29" s="54" t="n"/>
-      <c r="T29" s="55" t="n"/>
+      <c r="S29" s="48" t="n"/>
+      <c r="T29" s="49" t="n"/>
       <c r="U29" s="24" t="n"/>
-      <c r="V29" s="55" t="n"/>
+      <c r="V29" s="49" t="n"/>
       <c r="W29" s="24" t="n"/>
-      <c r="X29" s="54" t="n"/>
-      <c r="Y29" s="54" t="n"/>
-      <c r="Z29" s="54" t="n"/>
-      <c r="AA29" s="55" t="n"/>
+      <c r="X29" s="48" t="n"/>
+      <c r="Y29" s="48" t="n"/>
+      <c r="Z29" s="48" t="n"/>
+      <c r="AA29" s="49" t="n"/>
       <c r="AB29" s="24" t="n"/>
-      <c r="AC29" s="54" t="n"/>
-      <c r="AD29" s="54" t="n"/>
-      <c r="AE29" s="55" t="n"/>
+      <c r="AC29" s="48" t="n"/>
+      <c r="AD29" s="48" t="n"/>
+      <c r="AE29" s="49" t="n"/>
       <c r="AF29" s="24" t="n"/>
-      <c r="AG29" s="54" t="n"/>
-      <c r="AH29" s="54" t="n"/>
-      <c r="AI29" s="54" t="n"/>
-      <c r="AJ29" s="55" t="n"/>
+      <c r="AG29" s="48" t="n"/>
+      <c r="AH29" s="48" t="n"/>
+      <c r="AI29" s="48" t="n"/>
+      <c r="AJ29" s="49" t="n"/>
       <c r="AK29" s="24" t="n"/>
-      <c r="AL29" s="54" t="n"/>
-      <c r="AM29" s="54" t="n"/>
-      <c r="AN29" s="55" t="n"/>
+      <c r="AL29" s="48" t="n"/>
+      <c r="AM29" s="48" t="n"/>
+      <c r="AN29" s="49" t="n"/>
       <c r="AO29" s="24" t="n"/>
-      <c r="AP29" s="65" t="n"/>
-      <c r="AQ29" s="55" t="n"/>
+      <c r="AP29" s="59" t="n"/>
+      <c r="AQ29" s="49" t="n"/>
       <c r="AR29" s="21" t="n"/>
       <c r="AS29" s="21" t="n"/>
-      <c r="AT29" s="55" t="n"/>
+      <c r="AT29" s="49" t="n"/>
       <c r="AU29" s="2" t="n"/>
     </row>
-    <row r="30" ht="27.75" customHeight="1">
+    <row r="30" hidden="1" ht="27.75" customHeight="1">
       <c r="A30" s="24" t="n"/>
-      <c r="B30" s="55" t="n"/>
+      <c r="B30" s="49" t="n"/>
       <c r="C30" s="24" t="n"/>
-      <c r="D30" s="54" t="n"/>
-      <c r="E30" s="54" t="n"/>
-      <c r="F30" s="55" t="n"/>
+      <c r="D30" s="48" t="n"/>
+      <c r="E30" s="48" t="n"/>
+      <c r="F30" s="49" t="n"/>
       <c r="G30" s="21" t="n"/>
-      <c r="H30" s="64" t="n"/>
-      <c r="I30" s="55" t="n"/>
+      <c r="H30" s="58" t="n"/>
+      <c r="I30" s="49" t="n"/>
       <c r="J30" s="21" t="n"/>
-      <c r="K30" s="55" t="n"/>
+      <c r="K30" s="49" t="n"/>
       <c r="L30" s="24" t="n"/>
-      <c r="M30" s="55" t="n"/>
+      <c r="M30" s="49" t="n"/>
       <c r="N30" s="24" t="n"/>
       <c r="O30" s="24" t="n"/>
       <c r="P30" s="24" t="n"/>
-      <c r="Q30" s="55" t="n"/>
+      <c r="Q30" s="49" t="n"/>
       <c r="R30" s="24" t="n"/>
-      <c r="S30" s="54" t="n"/>
-      <c r="T30" s="55" t="n"/>
+      <c r="S30" s="48" t="n"/>
+      <c r="T30" s="49" t="n"/>
       <c r="U30" s="24" t="n"/>
-      <c r="V30" s="55" t="n"/>
+      <c r="V30" s="49" t="n"/>
       <c r="W30" s="24" t="n"/>
-      <c r="X30" s="54" t="n"/>
-      <c r="Y30" s="54" t="n"/>
-      <c r="Z30" s="54" t="n"/>
-      <c r="AA30" s="55" t="n"/>
+      <c r="X30" s="48" t="n"/>
+      <c r="Y30" s="48" t="n"/>
+      <c r="Z30" s="48" t="n"/>
+      <c r="AA30" s="49" t="n"/>
       <c r="AB30" s="24" t="n"/>
-      <c r="AC30" s="54" t="n"/>
-      <c r="AD30" s="54" t="n"/>
-      <c r="AE30" s="55" t="n"/>
+      <c r="AC30" s="48" t="n"/>
+      <c r="AD30" s="48" t="n"/>
+      <c r="AE30" s="49" t="n"/>
       <c r="AF30" s="24" t="n"/>
-      <c r="AG30" s="54" t="n"/>
-      <c r="AH30" s="54" t="n"/>
-      <c r="AI30" s="54" t="n"/>
-      <c r="AJ30" s="55" t="n"/>
+      <c r="AG30" s="48" t="n"/>
+      <c r="AH30" s="48" t="n"/>
+      <c r="AI30" s="48" t="n"/>
+      <c r="AJ30" s="49" t="n"/>
       <c r="AK30" s="24" t="n"/>
-      <c r="AL30" s="54" t="n"/>
-      <c r="AM30" s="54" t="n"/>
-      <c r="AN30" s="55" t="n"/>
+      <c r="AL30" s="48" t="n"/>
+      <c r="AM30" s="48" t="n"/>
+      <c r="AN30" s="49" t="n"/>
       <c r="AO30" s="24" t="n"/>
-      <c r="AP30" s="65" t="n"/>
-      <c r="AQ30" s="55" t="n"/>
+      <c r="AP30" s="59" t="n"/>
+      <c r="AQ30" s="49" t="n"/>
       <c r="AR30" s="21" t="n"/>
       <c r="AS30" s="21" t="n"/>
-      <c r="AT30" s="55" t="n"/>
+      <c r="AT30" s="49" t="n"/>
       <c r="AU30" s="2" t="n"/>
     </row>
-    <row r="31" ht="37.5" customHeight="1">
+    <row r="31" hidden="1" ht="37.5" customHeight="1">
       <c r="A31" s="24" t="n"/>
-      <c r="B31" s="55" t="n"/>
+      <c r="B31" s="49" t="n"/>
       <c r="C31" s="24" t="n"/>
-      <c r="D31" s="54" t="n"/>
-      <c r="E31" s="54" t="n"/>
-      <c r="F31" s="55" t="n"/>
+      <c r="D31" s="48" t="n"/>
+      <c r="E31" s="48" t="n"/>
+      <c r="F31" s="49" t="n"/>
       <c r="G31" s="21" t="n"/>
-      <c r="H31" s="64" t="n"/>
-      <c r="I31" s="55" t="n"/>
+      <c r="H31" s="58" t="n"/>
+      <c r="I31" s="49" t="n"/>
       <c r="J31" s="21" t="n"/>
-      <c r="K31" s="55" t="n"/>
+      <c r="K31" s="49" t="n"/>
       <c r="L31" s="24" t="n"/>
-      <c r="M31" s="55" t="n"/>
+      <c r="M31" s="49" t="n"/>
       <c r="N31" s="24" t="n"/>
       <c r="O31" s="24" t="n"/>
       <c r="P31" s="24" t="n"/>
-      <c r="Q31" s="55" t="n"/>
+      <c r="Q31" s="49" t="n"/>
       <c r="R31" s="24" t="n"/>
-      <c r="S31" s="54" t="n"/>
-      <c r="T31" s="55" t="n"/>
+      <c r="S31" s="48" t="n"/>
+      <c r="T31" s="49" t="n"/>
       <c r="U31" s="24" t="n"/>
-      <c r="V31" s="55" t="n"/>
+      <c r="V31" s="49" t="n"/>
       <c r="W31" s="24" t="n"/>
-      <c r="X31" s="54" t="n"/>
-      <c r="Y31" s="54" t="n"/>
-      <c r="Z31" s="54" t="n"/>
-      <c r="AA31" s="55" t="n"/>
+      <c r="X31" s="48" t="n"/>
+      <c r="Y31" s="48" t="n"/>
+      <c r="Z31" s="48" t="n"/>
+      <c r="AA31" s="49" t="n"/>
       <c r="AB31" s="24" t="n"/>
-      <c r="AC31" s="54" t="n"/>
-      <c r="AD31" s="54" t="n"/>
-      <c r="AE31" s="55" t="n"/>
+      <c r="AC31" s="48" t="n"/>
+      <c r="AD31" s="48" t="n"/>
+      <c r="AE31" s="49" t="n"/>
       <c r="AF31" s="24" t="n"/>
-      <c r="AG31" s="54" t="n"/>
-      <c r="AH31" s="54" t="n"/>
-      <c r="AI31" s="54" t="n"/>
-      <c r="AJ31" s="55" t="n"/>
+      <c r="AG31" s="48" t="n"/>
+      <c r="AH31" s="48" t="n"/>
+      <c r="AI31" s="48" t="n"/>
+      <c r="AJ31" s="49" t="n"/>
       <c r="AK31" s="24" t="n"/>
-      <c r="AL31" s="54" t="n"/>
-      <c r="AM31" s="54" t="n"/>
-      <c r="AN31" s="55" t="n"/>
+      <c r="AL31" s="48" t="n"/>
+      <c r="AM31" s="48" t="n"/>
+      <c r="AN31" s="49" t="n"/>
       <c r="AO31" s="24" t="n"/>
-      <c r="AP31" s="65" t="n"/>
-      <c r="AQ31" s="55" t="n"/>
+      <c r="AP31" s="59" t="n"/>
+      <c r="AQ31" s="49" t="n"/>
       <c r="AR31" s="21" t="n"/>
       <c r="AS31" s="21" t="n"/>
-      <c r="AT31" s="55" t="n"/>
+      <c r="AT31" s="49" t="n"/>
       <c r="AU31" s="2" t="n"/>
     </row>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="66" t="n"/>
-      <c r="B32" s="55" t="n"/>
-      <c r="C32" s="24" t="inlineStr">
-        <is>
-          <t>&lt;=== TOTAL MALE</t>
-        </is>
-      </c>
-      <c r="D32" s="54" t="n"/>
-      <c r="E32" s="54" t="n"/>
-      <c r="F32" s="55" t="n"/>
-      <c r="G32" s="27" t="inlineStr"/>
-      <c r="H32" s="67" t="inlineStr"/>
-      <c r="I32" s="55" t="n"/>
-      <c r="J32" s="30" t="inlineStr"/>
-      <c r="K32" s="55" t="n"/>
-      <c r="L32" s="30" t="inlineStr"/>
-      <c r="M32" s="55" t="n"/>
-      <c r="N32" s="30" t="inlineStr"/>
-      <c r="O32" s="30" t="inlineStr"/>
-      <c r="P32" s="30" t="inlineStr"/>
-      <c r="Q32" s="55" t="n"/>
-      <c r="R32" s="30" t="inlineStr"/>
-      <c r="S32" s="54" t="n"/>
-      <c r="T32" s="55" t="n"/>
-      <c r="U32" s="30" t="inlineStr"/>
-      <c r="V32" s="55" t="n"/>
-      <c r="W32" s="30" t="inlineStr"/>
-      <c r="X32" s="54" t="n"/>
-      <c r="Y32" s="54" t="n"/>
-      <c r="Z32" s="54" t="n"/>
-      <c r="AA32" s="55" t="n"/>
-      <c r="AB32" s="30" t="inlineStr"/>
-      <c r="AC32" s="54" t="n"/>
-      <c r="AD32" s="54" t="n"/>
-      <c r="AE32" s="55" t="n"/>
-      <c r="AF32" s="30" t="inlineStr"/>
-      <c r="AG32" s="54" t="n"/>
-      <c r="AH32" s="54" t="n"/>
-      <c r="AI32" s="54" t="n"/>
-      <c r="AJ32" s="55" t="n"/>
-      <c r="AK32" s="27" t="inlineStr"/>
-      <c r="AL32" s="54" t="n"/>
-      <c r="AM32" s="54" t="n"/>
-      <c r="AN32" s="55" t="n"/>
-      <c r="AO32" s="27" t="inlineStr"/>
-      <c r="AP32" s="27" t="inlineStr"/>
-      <c r="AQ32" s="55" t="n"/>
-      <c r="AR32" s="27" t="inlineStr"/>
-      <c r="AS32" s="27" t="inlineStr"/>
-      <c r="AT32" s="55" t="n"/>
+    <row r="32" hidden="1" ht="37.5" customHeight="1">
+      <c r="A32" s="24" t="n"/>
+      <c r="B32" s="49" t="n"/>
+      <c r="C32" s="24" t="n"/>
+      <c r="D32" s="48" t="n"/>
+      <c r="E32" s="48" t="n"/>
+      <c r="F32" s="49" t="n"/>
+      <c r="G32" s="21" t="n"/>
+      <c r="H32" s="58" t="n"/>
+      <c r="I32" s="49" t="n"/>
+      <c r="J32" s="21" t="n"/>
+      <c r="K32" s="49" t="n"/>
+      <c r="L32" s="24" t="n"/>
+      <c r="M32" s="49" t="n"/>
+      <c r="N32" s="24" t="n"/>
+      <c r="O32" s="24" t="n"/>
+      <c r="P32" s="24" t="n"/>
+      <c r="Q32" s="49" t="n"/>
+      <c r="R32" s="24" t="n"/>
+      <c r="S32" s="48" t="n"/>
+      <c r="T32" s="49" t="n"/>
+      <c r="U32" s="24" t="n"/>
+      <c r="V32" s="49" t="n"/>
+      <c r="W32" s="24" t="n"/>
+      <c r="X32" s="48" t="n"/>
+      <c r="Y32" s="48" t="n"/>
+      <c r="Z32" s="48" t="n"/>
+      <c r="AA32" s="49" t="n"/>
+      <c r="AB32" s="24" t="n"/>
+      <c r="AC32" s="48" t="n"/>
+      <c r="AD32" s="48" t="n"/>
+      <c r="AE32" s="49" t="n"/>
+      <c r="AF32" s="24" t="n"/>
+      <c r="AG32" s="48" t="n"/>
+      <c r="AH32" s="48" t="n"/>
+      <c r="AI32" s="48" t="n"/>
+      <c r="AJ32" s="49" t="n"/>
+      <c r="AK32" s="24" t="n"/>
+      <c r="AL32" s="48" t="n"/>
+      <c r="AM32" s="48" t="n"/>
+      <c r="AN32" s="49" t="n"/>
+      <c r="AO32" s="24" t="n"/>
+      <c r="AP32" s="59" t="n"/>
+      <c r="AQ32" s="49" t="n"/>
+      <c r="AR32" s="21" t="n"/>
+      <c r="AS32" s="21" t="n"/>
+      <c r="AT32" s="49" t="n"/>
       <c r="AU32" s="2" t="n"/>
     </row>
-    <row r="33" ht="37.5" customHeight="1">
+    <row r="33" hidden="1" ht="27.75" customHeight="1">
       <c r="A33" s="24" t="n"/>
-      <c r="B33" s="55" t="n"/>
+      <c r="B33" s="49" t="n"/>
       <c r="C33" s="24" t="n"/>
-      <c r="D33" s="54" t="n"/>
-      <c r="E33" s="54" t="n"/>
-      <c r="F33" s="55" t="n"/>
+      <c r="D33" s="48" t="n"/>
+      <c r="E33" s="48" t="n"/>
+      <c r="F33" s="49" t="n"/>
       <c r="G33" s="21" t="n"/>
-      <c r="H33" s="64" t="n"/>
-      <c r="I33" s="55" t="n"/>
+      <c r="H33" s="58" t="n"/>
+      <c r="I33" s="49" t="n"/>
       <c r="J33" s="21" t="n"/>
-      <c r="K33" s="55" t="n"/>
+      <c r="K33" s="49" t="n"/>
       <c r="L33" s="24" t="n"/>
-      <c r="M33" s="55" t="n"/>
+      <c r="M33" s="49" t="n"/>
       <c r="N33" s="24" t="n"/>
       <c r="O33" s="24" t="n"/>
       <c r="P33" s="24" t="n"/>
-      <c r="Q33" s="55" t="n"/>
+      <c r="Q33" s="49" t="n"/>
       <c r="R33" s="24" t="n"/>
-      <c r="S33" s="54" t="n"/>
-      <c r="T33" s="55" t="n"/>
+      <c r="S33" s="48" t="n"/>
+      <c r="T33" s="49" t="n"/>
       <c r="U33" s="24" t="n"/>
-      <c r="V33" s="55" t="n"/>
+      <c r="V33" s="49" t="n"/>
       <c r="W33" s="24" t="n"/>
-      <c r="X33" s="54" t="n"/>
-      <c r="Y33" s="54" t="n"/>
-      <c r="Z33" s="54" t="n"/>
-      <c r="AA33" s="55" t="n"/>
+      <c r="X33" s="48" t="n"/>
+      <c r="Y33" s="48" t="n"/>
+      <c r="Z33" s="48" t="n"/>
+      <c r="AA33" s="49" t="n"/>
       <c r="AB33" s="24" t="n"/>
-      <c r="AC33" s="54" t="n"/>
-      <c r="AD33" s="54" t="n"/>
-      <c r="AE33" s="55" t="n"/>
+      <c r="AC33" s="48" t="n"/>
+      <c r="AD33" s="48" t="n"/>
+      <c r="AE33" s="49" t="n"/>
       <c r="AF33" s="24" t="n"/>
-      <c r="AG33" s="54" t="n"/>
-      <c r="AH33" s="54" t="n"/>
-      <c r="AI33" s="54" t="n"/>
-      <c r="AJ33" s="55" t="n"/>
+      <c r="AG33" s="48" t="n"/>
+      <c r="AH33" s="48" t="n"/>
+      <c r="AI33" s="48" t="n"/>
+      <c r="AJ33" s="49" t="n"/>
       <c r="AK33" s="24" t="n"/>
-      <c r="AL33" s="54" t="n"/>
-      <c r="AM33" s="54" t="n"/>
-      <c r="AN33" s="55" t="n"/>
+      <c r="AL33" s="48" t="n"/>
+      <c r="AM33" s="48" t="n"/>
+      <c r="AN33" s="49" t="n"/>
       <c r="AO33" s="24" t="n"/>
-      <c r="AP33" s="65" t="n"/>
-      <c r="AQ33" s="55" t="n"/>
+      <c r="AP33" s="59" t="n"/>
+      <c r="AQ33" s="49" t="n"/>
       <c r="AR33" s="21" t="n"/>
       <c r="AS33" s="21" t="n"/>
-      <c r="AT33" s="55" t="n"/>
+      <c r="AT33" s="49" t="n"/>
       <c r="AU33" s="2" t="n"/>
     </row>
-    <row r="34" ht="27.75" customHeight="1">
+    <row r="34" hidden="1" ht="27.75" customHeight="1">
       <c r="A34" s="24" t="n"/>
-      <c r="B34" s="55" t="n"/>
+      <c r="B34" s="49" t="n"/>
       <c r="C34" s="24" t="n"/>
-      <c r="D34" s="54" t="n"/>
-      <c r="E34" s="54" t="n"/>
-      <c r="F34" s="55" t="n"/>
+      <c r="D34" s="48" t="n"/>
+      <c r="E34" s="48" t="n"/>
+      <c r="F34" s="49" t="n"/>
       <c r="G34" s="21" t="n"/>
-      <c r="H34" s="64" t="n"/>
-      <c r="I34" s="55" t="n"/>
+      <c r="H34" s="58" t="n"/>
+      <c r="I34" s="49" t="n"/>
       <c r="J34" s="21" t="n"/>
-      <c r="K34" s="55" t="n"/>
+      <c r="K34" s="49" t="n"/>
       <c r="L34" s="24" t="n"/>
-      <c r="M34" s="55" t="n"/>
+      <c r="M34" s="49" t="n"/>
       <c r="N34" s="24" t="n"/>
       <c r="O34" s="24" t="n"/>
       <c r="P34" s="24" t="n"/>
-      <c r="Q34" s="55" t="n"/>
+      <c r="Q34" s="49" t="n"/>
       <c r="R34" s="24" t="n"/>
-      <c r="S34" s="54" t="n"/>
-      <c r="T34" s="55" t="n"/>
+      <c r="S34" s="48" t="n"/>
+      <c r="T34" s="49" t="n"/>
       <c r="U34" s="24" t="n"/>
-      <c r="V34" s="55" t="n"/>
+      <c r="V34" s="49" t="n"/>
       <c r="W34" s="24" t="n"/>
-      <c r="X34" s="54" t="n"/>
-      <c r="Y34" s="54" t="n"/>
-      <c r="Z34" s="54" t="n"/>
-      <c r="AA34" s="55" t="n"/>
+      <c r="X34" s="48" t="n"/>
+      <c r="Y34" s="48" t="n"/>
+      <c r="Z34" s="48" t="n"/>
+      <c r="AA34" s="49" t="n"/>
       <c r="AB34" s="24" t="n"/>
-      <c r="AC34" s="54" t="n"/>
-      <c r="AD34" s="54" t="n"/>
-      <c r="AE34" s="55" t="n"/>
+      <c r="AC34" s="48" t="n"/>
+      <c r="AD34" s="48" t="n"/>
+      <c r="AE34" s="49" t="n"/>
       <c r="AF34" s="24" t="n"/>
-      <c r="AG34" s="54" t="n"/>
-      <c r="AH34" s="54" t="n"/>
-      <c r="AI34" s="54" t="n"/>
-      <c r="AJ34" s="55" t="n"/>
+      <c r="AG34" s="48" t="n"/>
+      <c r="AH34" s="48" t="n"/>
+      <c r="AI34" s="48" t="n"/>
+      <c r="AJ34" s="49" t="n"/>
       <c r="AK34" s="24" t="n"/>
-      <c r="AL34" s="54" t="n"/>
-      <c r="AM34" s="54" t="n"/>
-      <c r="AN34" s="55" t="n"/>
+      <c r="AL34" s="48" t="n"/>
+      <c r="AM34" s="48" t="n"/>
+      <c r="AN34" s="49" t="n"/>
       <c r="AO34" s="24" t="n"/>
-      <c r="AP34" s="65" t="n"/>
-      <c r="AQ34" s="55" t="n"/>
+      <c r="AP34" s="59" t="n"/>
+      <c r="AQ34" s="49" t="n"/>
       <c r="AR34" s="21" t="n"/>
       <c r="AS34" s="21" t="n"/>
-      <c r="AT34" s="55" t="n"/>
+      <c r="AT34" s="49" t="n"/>
       <c r="AU34" s="2" t="n"/>
     </row>
-    <row r="35" ht="27.75" customHeight="1">
+    <row r="35" hidden="1" ht="37.5" customHeight="1">
       <c r="A35" s="24" t="n"/>
-      <c r="B35" s="55" t="n"/>
+      <c r="B35" s="49" t="n"/>
       <c r="C35" s="24" t="n"/>
-      <c r="D35" s="54" t="n"/>
-      <c r="E35" s="54" t="n"/>
-      <c r="F35" s="55" t="n"/>
+      <c r="D35" s="48" t="n"/>
+      <c r="E35" s="48" t="n"/>
+      <c r="F35" s="49" t="n"/>
       <c r="G35" s="21" t="n"/>
-      <c r="H35" s="64" t="n"/>
-      <c r="I35" s="55" t="n"/>
+      <c r="H35" s="58" t="n"/>
+      <c r="I35" s="49" t="n"/>
       <c r="J35" s="21" t="n"/>
-      <c r="K35" s="55" t="n"/>
+      <c r="K35" s="49" t="n"/>
       <c r="L35" s="24" t="n"/>
-      <c r="M35" s="55" t="n"/>
+      <c r="M35" s="49" t="n"/>
       <c r="N35" s="24" t="n"/>
       <c r="O35" s="24" t="n"/>
       <c r="P35" s="24" t="n"/>
-      <c r="Q35" s="55" t="n"/>
+      <c r="Q35" s="49" t="n"/>
       <c r="R35" s="24" t="n"/>
-      <c r="S35" s="54" t="n"/>
-      <c r="T35" s="55" t="n"/>
+      <c r="S35" s="48" t="n"/>
+      <c r="T35" s="49" t="n"/>
       <c r="U35" s="24" t="n"/>
-      <c r="V35" s="55" t="n"/>
+      <c r="V35" s="49" t="n"/>
       <c r="W35" s="24" t="n"/>
-      <c r="X35" s="54" t="n"/>
-      <c r="Y35" s="54" t="n"/>
-      <c r="Z35" s="54" t="n"/>
-      <c r="AA35" s="55" t="n"/>
+      <c r="X35" s="48" t="n"/>
+      <c r="Y35" s="48" t="n"/>
+      <c r="Z35" s="48" t="n"/>
+      <c r="AA35" s="49" t="n"/>
       <c r="AB35" s="24" t="n"/>
-      <c r="AC35" s="54" t="n"/>
-      <c r="AD35" s="54" t="n"/>
-      <c r="AE35" s="55" t="n"/>
+      <c r="AC35" s="48" t="n"/>
+      <c r="AD35" s="48" t="n"/>
+      <c r="AE35" s="49" t="n"/>
       <c r="AF35" s="24" t="n"/>
-      <c r="AG35" s="54" t="n"/>
-      <c r="AH35" s="54" t="n"/>
-      <c r="AI35" s="54" t="n"/>
-      <c r="AJ35" s="55" t="n"/>
+      <c r="AG35" s="48" t="n"/>
+      <c r="AH35" s="48" t="n"/>
+      <c r="AI35" s="48" t="n"/>
+      <c r="AJ35" s="49" t="n"/>
       <c r="AK35" s="24" t="n"/>
-      <c r="AL35" s="54" t="n"/>
-      <c r="AM35" s="54" t="n"/>
-      <c r="AN35" s="55" t="n"/>
+      <c r="AL35" s="48" t="n"/>
+      <c r="AM35" s="48" t="n"/>
+      <c r="AN35" s="49" t="n"/>
       <c r="AO35" s="24" t="n"/>
-      <c r="AP35" s="65" t="n"/>
-      <c r="AQ35" s="55" t="n"/>
+      <c r="AP35" s="59" t="n"/>
+      <c r="AQ35" s="49" t="n"/>
       <c r="AR35" s="21" t="n"/>
       <c r="AS35" s="21" t="n"/>
-      <c r="AT35" s="55" t="n"/>
+      <c r="AT35" s="49" t="n"/>
       <c r="AU35" s="2" t="n"/>
     </row>
-    <row r="36" ht="37.5" customHeight="1">
+    <row r="36" hidden="1" ht="27.75" customHeight="1">
       <c r="A36" s="24" t="n"/>
-      <c r="B36" s="55" t="n"/>
+      <c r="B36" s="49" t="n"/>
       <c r="C36" s="24" t="n"/>
-      <c r="D36" s="54" t="n"/>
-      <c r="E36" s="54" t="n"/>
-      <c r="F36" s="55" t="n"/>
+      <c r="D36" s="48" t="n"/>
+      <c r="E36" s="48" t="n"/>
+      <c r="F36" s="49" t="n"/>
       <c r="G36" s="21" t="n"/>
-      <c r="H36" s="64" t="n"/>
-      <c r="I36" s="55" t="n"/>
+      <c r="H36" s="58" t="n"/>
+      <c r="I36" s="49" t="n"/>
       <c r="J36" s="21" t="n"/>
-      <c r="K36" s="55" t="n"/>
+      <c r="K36" s="49" t="n"/>
       <c r="L36" s="24" t="n"/>
-      <c r="M36" s="55" t="n"/>
+      <c r="M36" s="49" t="n"/>
       <c r="N36" s="24" t="n"/>
       <c r="O36" s="24" t="n"/>
       <c r="P36" s="24" t="n"/>
-      <c r="Q36" s="55" t="n"/>
+      <c r="Q36" s="49" t="n"/>
       <c r="R36" s="24" t="n"/>
-      <c r="S36" s="54" t="n"/>
-      <c r="T36" s="55" t="n"/>
+      <c r="S36" s="48" t="n"/>
+      <c r="T36" s="49" t="n"/>
       <c r="U36" s="24" t="n"/>
-      <c r="V36" s="55" t="n"/>
+      <c r="V36" s="49" t="n"/>
       <c r="W36" s="24" t="n"/>
-      <c r="X36" s="54" t="n"/>
-      <c r="Y36" s="54" t="n"/>
-      <c r="Z36" s="54" t="n"/>
-      <c r="AA36" s="55" t="n"/>
+      <c r="X36" s="48" t="n"/>
+      <c r="Y36" s="48" t="n"/>
+      <c r="Z36" s="48" t="n"/>
+      <c r="AA36" s="49" t="n"/>
       <c r="AB36" s="24" t="n"/>
-      <c r="AC36" s="54" t="n"/>
-      <c r="AD36" s="54" t="n"/>
-      <c r="AE36" s="55" t="n"/>
+      <c r="AC36" s="48" t="n"/>
+      <c r="AD36" s="48" t="n"/>
+      <c r="AE36" s="49" t="n"/>
       <c r="AF36" s="24" t="n"/>
-      <c r="AG36" s="54" t="n"/>
-      <c r="AH36" s="54" t="n"/>
-      <c r="AI36" s="54" t="n"/>
-      <c r="AJ36" s="55" t="n"/>
+      <c r="AG36" s="48" t="n"/>
+      <c r="AH36" s="48" t="n"/>
+      <c r="AI36" s="48" t="n"/>
+      <c r="AJ36" s="49" t="n"/>
       <c r="AK36" s="24" t="n"/>
-      <c r="AL36" s="54" t="n"/>
-      <c r="AM36" s="54" t="n"/>
-      <c r="AN36" s="55" t="n"/>
+      <c r="AL36" s="48" t="n"/>
+      <c r="AM36" s="48" t="n"/>
+      <c r="AN36" s="49" t="n"/>
       <c r="AO36" s="24" t="n"/>
-      <c r="AP36" s="65" t="n"/>
-      <c r="AQ36" s="55" t="n"/>
+      <c r="AP36" s="59" t="n"/>
+      <c r="AQ36" s="49" t="n"/>
       <c r="AR36" s="21" t="n"/>
       <c r="AS36" s="21" t="n"/>
-      <c r="AT36" s="55" t="n"/>
+      <c r="AT36" s="49" t="n"/>
       <c r="AU36" s="2" t="n"/>
     </row>
-    <row r="37" ht="27.75" customHeight="1">
+    <row r="37" hidden="1" ht="37.5" customHeight="1">
       <c r="A37" s="24" t="n"/>
-      <c r="B37" s="55" t="n"/>
+      <c r="B37" s="49" t="n"/>
       <c r="C37" s="24" t="n"/>
-      <c r="D37" s="54" t="n"/>
-      <c r="E37" s="54" t="n"/>
-      <c r="F37" s="55" t="n"/>
+      <c r="D37" s="48" t="n"/>
+      <c r="E37" s="48" t="n"/>
+      <c r="F37" s="49" t="n"/>
       <c r="G37" s="21" t="n"/>
-      <c r="H37" s="64" t="n"/>
-      <c r="I37" s="55" t="n"/>
+      <c r="H37" s="58" t="n"/>
+      <c r="I37" s="49" t="n"/>
       <c r="J37" s="21" t="n"/>
-      <c r="K37" s="55" t="n"/>
+      <c r="K37" s="49" t="n"/>
       <c r="L37" s="24" t="n"/>
-      <c r="M37" s="55" t="n"/>
+      <c r="M37" s="49" t="n"/>
       <c r="N37" s="24" t="n"/>
       <c r="O37" s="24" t="n"/>
       <c r="P37" s="24" t="n"/>
-      <c r="Q37" s="55" t="n"/>
+      <c r="Q37" s="49" t="n"/>
       <c r="R37" s="24" t="n"/>
-      <c r="S37" s="54" t="n"/>
-      <c r="T37" s="55" t="n"/>
+      <c r="S37" s="48" t="n"/>
+      <c r="T37" s="49" t="n"/>
       <c r="U37" s="24" t="n"/>
-      <c r="V37" s="55" t="n"/>
+      <c r="V37" s="49" t="n"/>
       <c r="W37" s="24" t="n"/>
-      <c r="X37" s="54" t="n"/>
-      <c r="Y37" s="54" t="n"/>
-      <c r="Z37" s="54" t="n"/>
-      <c r="AA37" s="55" t="n"/>
+      <c r="X37" s="48" t="n"/>
+      <c r="Y37" s="48" t="n"/>
+      <c r="Z37" s="48" t="n"/>
+      <c r="AA37" s="49" t="n"/>
       <c r="AB37" s="24" t="n"/>
-      <c r="AC37" s="54" t="n"/>
-      <c r="AD37" s="54" t="n"/>
-      <c r="AE37" s="55" t="n"/>
+      <c r="AC37" s="48" t="n"/>
+      <c r="AD37" s="48" t="n"/>
+      <c r="AE37" s="49" t="n"/>
       <c r="AF37" s="24" t="n"/>
-      <c r="AG37" s="54" t="n"/>
-      <c r="AH37" s="54" t="n"/>
-      <c r="AI37" s="54" t="n"/>
-      <c r="AJ37" s="55" t="n"/>
+      <c r="AG37" s="48" t="n"/>
+      <c r="AH37" s="48" t="n"/>
+      <c r="AI37" s="48" t="n"/>
+      <c r="AJ37" s="49" t="n"/>
       <c r="AK37" s="24" t="n"/>
-      <c r="AL37" s="54" t="n"/>
-      <c r="AM37" s="54" t="n"/>
-      <c r="AN37" s="55" t="n"/>
+      <c r="AL37" s="48" t="n"/>
+      <c r="AM37" s="48" t="n"/>
+      <c r="AN37" s="49" t="n"/>
       <c r="AO37" s="24" t="n"/>
-      <c r="AP37" s="65" t="n"/>
-      <c r="AQ37" s="55" t="n"/>
+      <c r="AP37" s="59" t="n"/>
+      <c r="AQ37" s="49" t="n"/>
       <c r="AR37" s="21" t="n"/>
       <c r="AS37" s="21" t="n"/>
-      <c r="AT37" s="55" t="n"/>
+      <c r="AT37" s="49" t="n"/>
       <c r="AU37" s="2" t="n"/>
     </row>
-    <row r="38" ht="37.5" customHeight="1">
+    <row r="38" hidden="1" ht="27.75" customHeight="1">
       <c r="A38" s="24" t="n"/>
-      <c r="B38" s="55" t="n"/>
+      <c r="B38" s="49" t="n"/>
       <c r="C38" s="24" t="n"/>
-      <c r="D38" s="54" t="n"/>
-      <c r="E38" s="54" t="n"/>
-      <c r="F38" s="55" t="n"/>
+      <c r="D38" s="48" t="n"/>
+      <c r="E38" s="48" t="n"/>
+      <c r="F38" s="49" t="n"/>
       <c r="G38" s="21" t="n"/>
-      <c r="H38" s="64" t="n"/>
-      <c r="I38" s="55" t="n"/>
+      <c r="H38" s="58" t="n"/>
+      <c r="I38" s="49" t="n"/>
       <c r="J38" s="21" t="n"/>
-      <c r="K38" s="55" t="n"/>
+      <c r="K38" s="49" t="n"/>
       <c r="L38" s="24" t="n"/>
-      <c r="M38" s="55" t="n"/>
+      <c r="M38" s="49" t="n"/>
       <c r="N38" s="24" t="n"/>
       <c r="O38" s="24" t="n"/>
       <c r="P38" s="24" t="n"/>
-      <c r="Q38" s="55" t="n"/>
+      <c r="Q38" s="49" t="n"/>
       <c r="R38" s="24" t="n"/>
-      <c r="S38" s="54" t="n"/>
-      <c r="T38" s="55" t="n"/>
+      <c r="S38" s="48" t="n"/>
+      <c r="T38" s="49" t="n"/>
       <c r="U38" s="24" t="n"/>
-      <c r="V38" s="55" t="n"/>
+      <c r="V38" s="49" t="n"/>
       <c r="W38" s="24" t="n"/>
-      <c r="X38" s="54" t="n"/>
-      <c r="Y38" s="54" t="n"/>
-      <c r="Z38" s="54" t="n"/>
-      <c r="AA38" s="55" t="n"/>
+      <c r="X38" s="48" t="n"/>
+      <c r="Y38" s="48" t="n"/>
+      <c r="Z38" s="48" t="n"/>
+      <c r="AA38" s="49" t="n"/>
       <c r="AB38" s="24" t="n"/>
-      <c r="AC38" s="54" t="n"/>
-      <c r="AD38" s="54" t="n"/>
-      <c r="AE38" s="55" t="n"/>
+      <c r="AC38" s="48" t="n"/>
+      <c r="AD38" s="48" t="n"/>
+      <c r="AE38" s="49" t="n"/>
       <c r="AF38" s="24" t="n"/>
-      <c r="AG38" s="54" t="n"/>
-      <c r="AH38" s="54" t="n"/>
-      <c r="AI38" s="54" t="n"/>
-      <c r="AJ38" s="55" t="n"/>
+      <c r="AG38" s="48" t="n"/>
+      <c r="AH38" s="48" t="n"/>
+      <c r="AI38" s="48" t="n"/>
+      <c r="AJ38" s="49" t="n"/>
       <c r="AK38" s="24" t="n"/>
-      <c r="AL38" s="54" t="n"/>
-      <c r="AM38" s="54" t="n"/>
-      <c r="AN38" s="55" t="n"/>
+      <c r="AL38" s="48" t="n"/>
+      <c r="AM38" s="48" t="n"/>
+      <c r="AN38" s="49" t="n"/>
       <c r="AO38" s="24" t="n"/>
-      <c r="AP38" s="65" t="n"/>
-      <c r="AQ38" s="55" t="n"/>
+      <c r="AP38" s="59" t="n"/>
+      <c r="AQ38" s="49" t="n"/>
       <c r="AR38" s="21" t="n"/>
       <c r="AS38" s="21" t="n"/>
-      <c r="AT38" s="55" t="n"/>
+      <c r="AT38" s="49" t="n"/>
       <c r="AU38" s="2" t="n"/>
     </row>
-    <row r="39" ht="27.75" customHeight="1">
+    <row r="39" hidden="1" ht="27.75" customHeight="1">
       <c r="A39" s="24" t="n"/>
-      <c r="B39" s="55" t="n"/>
+      <c r="B39" s="49" t="n"/>
       <c r="C39" s="24" t="n"/>
-      <c r="D39" s="54" t="n"/>
-      <c r="E39" s="54" t="n"/>
-      <c r="F39" s="55" t="n"/>
+      <c r="D39" s="48" t="n"/>
+      <c r="E39" s="48" t="n"/>
+      <c r="F39" s="49" t="n"/>
       <c r="G39" s="21" t="n"/>
-      <c r="H39" s="64" t="n"/>
-      <c r="I39" s="55" t="n"/>
+      <c r="H39" s="58" t="n"/>
+      <c r="I39" s="49" t="n"/>
       <c r="J39" s="21" t="n"/>
-      <c r="K39" s="55" t="n"/>
+      <c r="K39" s="49" t="n"/>
       <c r="L39" s="24" t="n"/>
-      <c r="M39" s="55" t="n"/>
+      <c r="M39" s="49" t="n"/>
       <c r="N39" s="24" t="n"/>
       <c r="O39" s="24" t="n"/>
       <c r="P39" s="24" t="n"/>
-      <c r="Q39" s="55" t="n"/>
+      <c r="Q39" s="49" t="n"/>
       <c r="R39" s="24" t="n"/>
-      <c r="S39" s="54" t="n"/>
-      <c r="T39" s="55" t="n"/>
+      <c r="S39" s="48" t="n"/>
+      <c r="T39" s="49" t="n"/>
       <c r="U39" s="24" t="n"/>
-      <c r="V39" s="55" t="n"/>
+      <c r="V39" s="49" t="n"/>
       <c r="W39" s="24" t="n"/>
-      <c r="X39" s="54" t="n"/>
-      <c r="Y39" s="54" t="n"/>
-      <c r="Z39" s="54" t="n"/>
-      <c r="AA39" s="55" t="n"/>
+      <c r="X39" s="48" t="n"/>
+      <c r="Y39" s="48" t="n"/>
+      <c r="Z39" s="48" t="n"/>
+      <c r="AA39" s="49" t="n"/>
       <c r="AB39" s="24" t="n"/>
-      <c r="AC39" s="54" t="n"/>
-      <c r="AD39" s="54" t="n"/>
-      <c r="AE39" s="55" t="n"/>
+      <c r="AC39" s="48" t="n"/>
+      <c r="AD39" s="48" t="n"/>
+      <c r="AE39" s="49" t="n"/>
       <c r="AF39" s="24" t="n"/>
-      <c r="AG39" s="54" t="n"/>
-      <c r="AH39" s="54" t="n"/>
-      <c r="AI39" s="54" t="n"/>
-      <c r="AJ39" s="55" t="n"/>
+      <c r="AG39" s="48" t="n"/>
+      <c r="AH39" s="48" t="n"/>
+      <c r="AI39" s="48" t="n"/>
+      <c r="AJ39" s="49" t="n"/>
       <c r="AK39" s="24" t="n"/>
-      <c r="AL39" s="54" t="n"/>
-      <c r="AM39" s="54" t="n"/>
-      <c r="AN39" s="55" t="n"/>
+      <c r="AL39" s="48" t="n"/>
+      <c r="AM39" s="48" t="n"/>
+      <c r="AN39" s="49" t="n"/>
       <c r="AO39" s="24" t="n"/>
-      <c r="AP39" s="65" t="n"/>
-      <c r="AQ39" s="55" t="n"/>
+      <c r="AP39" s="59" t="n"/>
+      <c r="AQ39" s="49" t="n"/>
       <c r="AR39" s="21" t="n"/>
       <c r="AS39" s="21" t="n"/>
-      <c r="AT39" s="55" t="n"/>
+      <c r="AT39" s="49" t="n"/>
       <c r="AU39" s="2" t="n"/>
     </row>
-    <row r="40" ht="27.75" customHeight="1">
+    <row r="40" hidden="1" ht="27.75" customHeight="1">
       <c r="A40" s="24" t="n"/>
-      <c r="B40" s="55" t="n"/>
+      <c r="B40" s="49" t="n"/>
       <c r="C40" s="24" t="n"/>
-      <c r="D40" s="54" t="n"/>
-      <c r="E40" s="54" t="n"/>
-      <c r="F40" s="55" t="n"/>
+      <c r="D40" s="48" t="n"/>
+      <c r="E40" s="48" t="n"/>
+      <c r="F40" s="49" t="n"/>
       <c r="G40" s="21" t="n"/>
-      <c r="H40" s="64" t="n"/>
-      <c r="I40" s="55" t="n"/>
+      <c r="H40" s="58" t="n"/>
+      <c r="I40" s="49" t="n"/>
       <c r="J40" s="21" t="n"/>
-      <c r="K40" s="55" t="n"/>
+      <c r="K40" s="49" t="n"/>
       <c r="L40" s="24" t="n"/>
-      <c r="M40" s="55" t="n"/>
+      <c r="M40" s="49" t="n"/>
       <c r="N40" s="24" t="n"/>
       <c r="O40" s="24" t="n"/>
       <c r="P40" s="24" t="n"/>
-      <c r="Q40" s="55" t="n"/>
+      <c r="Q40" s="49" t="n"/>
       <c r="R40" s="24" t="n"/>
-      <c r="S40" s="54" t="n"/>
-      <c r="T40" s="55" t="n"/>
+      <c r="S40" s="48" t="n"/>
+      <c r="T40" s="49" t="n"/>
       <c r="U40" s="24" t="n"/>
-      <c r="V40" s="55" t="n"/>
+      <c r="V40" s="49" t="n"/>
       <c r="W40" s="24" t="n"/>
-      <c r="X40" s="54" t="n"/>
-      <c r="Y40" s="54" t="n"/>
-      <c r="Z40" s="54" t="n"/>
-      <c r="AA40" s="55" t="n"/>
+      <c r="X40" s="48" t="n"/>
+      <c r="Y40" s="48" t="n"/>
+      <c r="Z40" s="48" t="n"/>
+      <c r="AA40" s="49" t="n"/>
       <c r="AB40" s="24" t="n"/>
-      <c r="AC40" s="54" t="n"/>
-      <c r="AD40" s="54" t="n"/>
-      <c r="AE40" s="55" t="n"/>
+      <c r="AC40" s="48" t="n"/>
+      <c r="AD40" s="48" t="n"/>
+      <c r="AE40" s="49" t="n"/>
       <c r="AF40" s="24" t="n"/>
-      <c r="AG40" s="54" t="n"/>
-      <c r="AH40" s="54" t="n"/>
-      <c r="AI40" s="54" t="n"/>
-      <c r="AJ40" s="55" t="n"/>
+      <c r="AG40" s="48" t="n"/>
+      <c r="AH40" s="48" t="n"/>
+      <c r="AI40" s="48" t="n"/>
+      <c r="AJ40" s="49" t="n"/>
       <c r="AK40" s="24" t="n"/>
-      <c r="AL40" s="54" t="n"/>
-      <c r="AM40" s="54" t="n"/>
-      <c r="AN40" s="55" t="n"/>
+      <c r="AL40" s="48" t="n"/>
+      <c r="AM40" s="48" t="n"/>
+      <c r="AN40" s="49" t="n"/>
       <c r="AO40" s="24" t="n"/>
-      <c r="AP40" s="65" t="n"/>
-      <c r="AQ40" s="55" t="n"/>
+      <c r="AP40" s="59" t="n"/>
+      <c r="AQ40" s="49" t="n"/>
       <c r="AR40" s="21" t="n"/>
       <c r="AS40" s="21" t="n"/>
-      <c r="AT40" s="55" t="n"/>
+      <c r="AT40" s="49" t="n"/>
       <c r="AU40" s="2" t="n"/>
     </row>
-    <row r="41" ht="27.75" customHeight="1">
+    <row r="41" hidden="1" ht="46.5" customHeight="1">
       <c r="A41" s="24" t="n"/>
-      <c r="B41" s="55" t="n"/>
+      <c r="B41" s="49" t="n"/>
       <c r="C41" s="24" t="n"/>
-      <c r="D41" s="54" t="n"/>
-      <c r="E41" s="54" t="n"/>
-      <c r="F41" s="55" t="n"/>
+      <c r="D41" s="48" t="n"/>
+      <c r="E41" s="48" t="n"/>
+      <c r="F41" s="49" t="n"/>
       <c r="G41" s="21" t="n"/>
-      <c r="H41" s="64" t="n"/>
-      <c r="I41" s="55" t="n"/>
+      <c r="H41" s="58" t="n"/>
+      <c r="I41" s="49" t="n"/>
       <c r="J41" s="21" t="n"/>
-      <c r="K41" s="55" t="n"/>
+      <c r="K41" s="49" t="n"/>
       <c r="L41" s="24" t="n"/>
-      <c r="M41" s="55" t="n"/>
+      <c r="M41" s="49" t="n"/>
       <c r="N41" s="24" t="n"/>
       <c r="O41" s="24" t="n"/>
       <c r="P41" s="24" t="n"/>
-      <c r="Q41" s="55" t="n"/>
+      <c r="Q41" s="49" t="n"/>
       <c r="R41" s="24" t="n"/>
-      <c r="S41" s="54" t="n"/>
-      <c r="T41" s="55" t="n"/>
+      <c r="S41" s="48" t="n"/>
+      <c r="T41" s="49" t="n"/>
       <c r="U41" s="24" t="n"/>
-      <c r="V41" s="55" t="n"/>
+      <c r="V41" s="49" t="n"/>
       <c r="W41" s="24" t="n"/>
-      <c r="X41" s="54" t="n"/>
-      <c r="Y41" s="54" t="n"/>
-      <c r="Z41" s="54" t="n"/>
-      <c r="AA41" s="55" t="n"/>
+      <c r="X41" s="48" t="n"/>
+      <c r="Y41" s="48" t="n"/>
+      <c r="Z41" s="48" t="n"/>
+      <c r="AA41" s="49" t="n"/>
       <c r="AB41" s="24" t="n"/>
-      <c r="AC41" s="54" t="n"/>
-      <c r="AD41" s="54" t="n"/>
-      <c r="AE41" s="55" t="n"/>
+      <c r="AC41" s="48" t="n"/>
+      <c r="AD41" s="48" t="n"/>
+      <c r="AE41" s="49" t="n"/>
       <c r="AF41" s="24" t="n"/>
-      <c r="AG41" s="54" t="n"/>
-      <c r="AH41" s="54" t="n"/>
-      <c r="AI41" s="54" t="n"/>
-      <c r="AJ41" s="55" t="n"/>
+      <c r="AG41" s="48" t="n"/>
+      <c r="AH41" s="48" t="n"/>
+      <c r="AI41" s="48" t="n"/>
+      <c r="AJ41" s="49" t="n"/>
       <c r="AK41" s="24" t="n"/>
-      <c r="AL41" s="54" t="n"/>
-      <c r="AM41" s="54" t="n"/>
-      <c r="AN41" s="55" t="n"/>
+      <c r="AL41" s="48" t="n"/>
+      <c r="AM41" s="48" t="n"/>
+      <c r="AN41" s="49" t="n"/>
       <c r="AO41" s="24" t="n"/>
-      <c r="AP41" s="65" t="n"/>
-      <c r="AQ41" s="55" t="n"/>
+      <c r="AP41" s="59" t="n"/>
+      <c r="AQ41" s="49" t="n"/>
       <c r="AR41" s="21" t="n"/>
       <c r="AS41" s="21" t="n"/>
-      <c r="AT41" s="55" t="n"/>
+      <c r="AT41" s="49" t="n"/>
       <c r="AU41" s="2" t="n"/>
     </row>
-    <row r="42" ht="46.5" customHeight="1">
+    <row r="42" hidden="1" ht="27.75" customHeight="1">
       <c r="A42" s="24" t="n"/>
-      <c r="B42" s="55" t="n"/>
+      <c r="B42" s="49" t="n"/>
       <c r="C42" s="24" t="n"/>
-      <c r="D42" s="54" t="n"/>
-      <c r="E42" s="54" t="n"/>
-      <c r="F42" s="55" t="n"/>
+      <c r="D42" s="48" t="n"/>
+      <c r="E42" s="48" t="n"/>
+      <c r="F42" s="49" t="n"/>
       <c r="G42" s="21" t="n"/>
-      <c r="H42" s="64" t="n"/>
-      <c r="I42" s="55" t="n"/>
+      <c r="H42" s="58" t="n"/>
+      <c r="I42" s="49" t="n"/>
       <c r="J42" s="21" t="n"/>
-      <c r="K42" s="55" t="n"/>
+      <c r="K42" s="49" t="n"/>
       <c r="L42" s="24" t="n"/>
-      <c r="M42" s="55" t="n"/>
+      <c r="M42" s="49" t="n"/>
       <c r="N42" s="24" t="n"/>
       <c r="O42" s="24" t="n"/>
       <c r="P42" s="24" t="n"/>
-      <c r="Q42" s="55" t="n"/>
+      <c r="Q42" s="49" t="n"/>
       <c r="R42" s="24" t="n"/>
-      <c r="S42" s="54" t="n"/>
-      <c r="T42" s="55" t="n"/>
+      <c r="S42" s="48" t="n"/>
+      <c r="T42" s="49" t="n"/>
       <c r="U42" s="24" t="n"/>
-      <c r="V42" s="55" t="n"/>
+      <c r="V42" s="49" t="n"/>
       <c r="W42" s="24" t="n"/>
-      <c r="X42" s="54" t="n"/>
-      <c r="Y42" s="54" t="n"/>
-      <c r="Z42" s="54" t="n"/>
-      <c r="AA42" s="55" t="n"/>
+      <c r="X42" s="48" t="n"/>
+      <c r="Y42" s="48" t="n"/>
+      <c r="Z42" s="48" t="n"/>
+      <c r="AA42" s="49" t="n"/>
       <c r="AB42" s="24" t="n"/>
-      <c r="AC42" s="54" t="n"/>
-      <c r="AD42" s="54" t="n"/>
-      <c r="AE42" s="55" t="n"/>
+      <c r="AC42" s="48" t="n"/>
+      <c r="AD42" s="48" t="n"/>
+      <c r="AE42" s="49" t="n"/>
       <c r="AF42" s="24" t="n"/>
-      <c r="AG42" s="54" t="n"/>
-      <c r="AH42" s="54" t="n"/>
-      <c r="AI42" s="54" t="n"/>
-      <c r="AJ42" s="55" t="n"/>
+      <c r="AG42" s="48" t="n"/>
+      <c r="AH42" s="48" t="n"/>
+      <c r="AI42" s="48" t="n"/>
+      <c r="AJ42" s="49" t="n"/>
       <c r="AK42" s="24" t="n"/>
-      <c r="AL42" s="54" t="n"/>
-      <c r="AM42" s="54" t="n"/>
-      <c r="AN42" s="55" t="n"/>
+      <c r="AL42" s="48" t="n"/>
+      <c r="AM42" s="48" t="n"/>
+      <c r="AN42" s="49" t="n"/>
       <c r="AO42" s="24" t="n"/>
-      <c r="AP42" s="65" t="n"/>
-      <c r="AQ42" s="55" t="n"/>
+      <c r="AP42" s="59" t="n"/>
+      <c r="AQ42" s="49" t="n"/>
       <c r="AR42" s="21" t="n"/>
       <c r="AS42" s="21" t="n"/>
-      <c r="AT42" s="55" t="n"/>
+      <c r="AT42" s="49" t="n"/>
       <c r="AU42" s="2" t="n"/>
     </row>
-    <row r="43" ht="27.75" customHeight="1">
+    <row r="43" hidden="1" ht="37.5" customHeight="1">
       <c r="A43" s="24" t="n"/>
-      <c r="B43" s="55" t="n"/>
+      <c r="B43" s="49" t="n"/>
       <c r="C43" s="24" t="n"/>
-      <c r="D43" s="54" t="n"/>
-      <c r="E43" s="54" t="n"/>
-      <c r="F43" s="55" t="n"/>
+      <c r="D43" s="48" t="n"/>
+      <c r="E43" s="48" t="n"/>
+      <c r="F43" s="49" t="n"/>
       <c r="G43" s="21" t="n"/>
-      <c r="H43" s="64" t="n"/>
-      <c r="I43" s="55" t="n"/>
+      <c r="H43" s="58" t="n"/>
+      <c r="I43" s="49" t="n"/>
       <c r="J43" s="21" t="n"/>
-      <c r="K43" s="55" t="n"/>
+      <c r="K43" s="49" t="n"/>
       <c r="L43" s="24" t="n"/>
-      <c r="M43" s="55" t="n"/>
+      <c r="M43" s="49" t="n"/>
       <c r="N43" s="24" t="n"/>
       <c r="O43" s="24" t="n"/>
       <c r="P43" s="24" t="n"/>
-      <c r="Q43" s="55" t="n"/>
+      <c r="Q43" s="49" t="n"/>
       <c r="R43" s="24" t="n"/>
-      <c r="S43" s="54" t="n"/>
-      <c r="T43" s="55" t="n"/>
+      <c r="S43" s="48" t="n"/>
+      <c r="T43" s="49" t="n"/>
       <c r="U43" s="24" t="n"/>
-      <c r="V43" s="55" t="n"/>
+      <c r="V43" s="49" t="n"/>
       <c r="W43" s="24" t="n"/>
-      <c r="X43" s="54" t="n"/>
-      <c r="Y43" s="54" t="n"/>
-      <c r="Z43" s="54" t="n"/>
-      <c r="AA43" s="55" t="n"/>
+      <c r="X43" s="48" t="n"/>
+      <c r="Y43" s="48" t="n"/>
+      <c r="Z43" s="48" t="n"/>
+      <c r="AA43" s="49" t="n"/>
       <c r="AB43" s="24" t="n"/>
-      <c r="AC43" s="54" t="n"/>
-      <c r="AD43" s="54" t="n"/>
-      <c r="AE43" s="55" t="n"/>
+      <c r="AC43" s="48" t="n"/>
+      <c r="AD43" s="48" t="n"/>
+      <c r="AE43" s="49" t="n"/>
       <c r="AF43" s="24" t="n"/>
-      <c r="AG43" s="54" t="n"/>
-      <c r="AH43" s="54" t="n"/>
-      <c r="AI43" s="54" t="n"/>
-      <c r="AJ43" s="55" t="n"/>
+      <c r="AG43" s="48" t="n"/>
+      <c r="AH43" s="48" t="n"/>
+      <c r="AI43" s="48" t="n"/>
+      <c r="AJ43" s="49" t="n"/>
       <c r="AK43" s="24" t="n"/>
-      <c r="AL43" s="54" t="n"/>
-      <c r="AM43" s="54" t="n"/>
-      <c r="AN43" s="55" t="n"/>
+      <c r="AL43" s="48" t="n"/>
+      <c r="AM43" s="48" t="n"/>
+      <c r="AN43" s="49" t="n"/>
       <c r="AO43" s="24" t="n"/>
-      <c r="AP43" s="65" t="n"/>
-      <c r="AQ43" s="55" t="n"/>
+      <c r="AP43" s="59" t="n"/>
+      <c r="AQ43" s="49" t="n"/>
       <c r="AR43" s="21" t="n"/>
       <c r="AS43" s="21" t="n"/>
-      <c r="AT43" s="55" t="n"/>
+      <c r="AT43" s="49" t="n"/>
       <c r="AU43" s="2" t="n"/>
     </row>
-    <row r="44" ht="37.5" customHeight="1">
+    <row r="44" hidden="1" ht="27.75" customHeight="1">
       <c r="A44" s="24" t="n"/>
-      <c r="B44" s="55" t="n"/>
+      <c r="B44" s="49" t="n"/>
       <c r="C44" s="24" t="n"/>
-      <c r="D44" s="54" t="n"/>
-      <c r="E44" s="54" t="n"/>
-      <c r="F44" s="55" t="n"/>
+      <c r="D44" s="48" t="n"/>
+      <c r="E44" s="48" t="n"/>
+      <c r="F44" s="49" t="n"/>
       <c r="G44" s="21" t="n"/>
-      <c r="H44" s="64" t="n"/>
-      <c r="I44" s="55" t="n"/>
+      <c r="H44" s="58" t="n"/>
+      <c r="I44" s="49" t="n"/>
       <c r="J44" s="21" t="n"/>
-      <c r="K44" s="55" t="n"/>
+      <c r="K44" s="49" t="n"/>
       <c r="L44" s="24" t="n"/>
-      <c r="M44" s="55" t="n"/>
+      <c r="M44" s="49" t="n"/>
       <c r="N44" s="24" t="n"/>
       <c r="O44" s="24" t="n"/>
       <c r="P44" s="24" t="n"/>
-      <c r="Q44" s="55" t="n"/>
+      <c r="Q44" s="49" t="n"/>
       <c r="R44" s="24" t="n"/>
-      <c r="S44" s="54" t="n"/>
-      <c r="T44" s="55" t="n"/>
+      <c r="S44" s="48" t="n"/>
+      <c r="T44" s="49" t="n"/>
       <c r="U44" s="24" t="n"/>
-      <c r="V44" s="55" t="n"/>
+      <c r="V44" s="49" t="n"/>
       <c r="W44" s="24" t="n"/>
-      <c r="X44" s="54" t="n"/>
-      <c r="Y44" s="54" t="n"/>
-      <c r="Z44" s="54" t="n"/>
-      <c r="AA44" s="55" t="n"/>
+      <c r="X44" s="48" t="n"/>
+      <c r="Y44" s="48" t="n"/>
+      <c r="Z44" s="48" t="n"/>
+      <c r="AA44" s="49" t="n"/>
       <c r="AB44" s="24" t="n"/>
-      <c r="AC44" s="54" t="n"/>
-      <c r="AD44" s="54" t="n"/>
-      <c r="AE44" s="55" t="n"/>
+      <c r="AC44" s="48" t="n"/>
+      <c r="AD44" s="48" t="n"/>
+      <c r="AE44" s="49" t="n"/>
       <c r="AF44" s="24" t="n"/>
-      <c r="AG44" s="54" t="n"/>
-      <c r="AH44" s="54" t="n"/>
-      <c r="AI44" s="54" t="n"/>
-      <c r="AJ44" s="55" t="n"/>
+      <c r="AG44" s="48" t="n"/>
+      <c r="AH44" s="48" t="n"/>
+      <c r="AI44" s="48" t="n"/>
+      <c r="AJ44" s="49" t="n"/>
       <c r="AK44" s="24" t="n"/>
-      <c r="AL44" s="54" t="n"/>
-      <c r="AM44" s="54" t="n"/>
-      <c r="AN44" s="55" t="n"/>
+      <c r="AL44" s="48" t="n"/>
+      <c r="AM44" s="48" t="n"/>
+      <c r="AN44" s="49" t="n"/>
       <c r="AO44" s="24" t="n"/>
-      <c r="AP44" s="65" t="n"/>
-      <c r="AQ44" s="55" t="n"/>
+      <c r="AP44" s="59" t="n"/>
+      <c r="AQ44" s="49" t="n"/>
       <c r="AR44" s="21" t="n"/>
       <c r="AS44" s="21" t="n"/>
-      <c r="AT44" s="55" t="n"/>
+      <c r="AT44" s="49" t="n"/>
       <c r="AU44" s="2" t="n"/>
     </row>
-    <row r="45" ht="27.75" customHeight="1">
+    <row r="45" hidden="1" ht="46.5" customHeight="1">
       <c r="A45" s="24" t="n"/>
-      <c r="B45" s="55" t="n"/>
+      <c r="B45" s="49" t="n"/>
       <c r="C45" s="24" t="n"/>
-      <c r="D45" s="54" t="n"/>
-      <c r="E45" s="54" t="n"/>
-      <c r="F45" s="55" t="n"/>
+      <c r="D45" s="48" t="n"/>
+      <c r="E45" s="48" t="n"/>
+      <c r="F45" s="49" t="n"/>
       <c r="G45" s="21" t="n"/>
-      <c r="H45" s="64" t="n"/>
-      <c r="I45" s="55" t="n"/>
+      <c r="H45" s="58" t="n"/>
+      <c r="I45" s="49" t="n"/>
       <c r="J45" s="21" t="n"/>
-      <c r="K45" s="55" t="n"/>
+      <c r="K45" s="49" t="n"/>
       <c r="L45" s="24" t="n"/>
-      <c r="M45" s="55" t="n"/>
+      <c r="M45" s="49" t="n"/>
       <c r="N45" s="24" t="n"/>
       <c r="O45" s="24" t="n"/>
       <c r="P45" s="24" t="n"/>
-      <c r="Q45" s="55" t="n"/>
+      <c r="Q45" s="49" t="n"/>
       <c r="R45" s="24" t="n"/>
-      <c r="S45" s="54" t="n"/>
-      <c r="T45" s="55" t="n"/>
+      <c r="S45" s="48" t="n"/>
+      <c r="T45" s="49" t="n"/>
       <c r="U45" s="24" t="n"/>
-      <c r="V45" s="55" t="n"/>
+      <c r="V45" s="49" t="n"/>
       <c r="W45" s="24" t="n"/>
-      <c r="X45" s="54" t="n"/>
-      <c r="Y45" s="54" t="n"/>
-      <c r="Z45" s="54" t="n"/>
-      <c r="AA45" s="55" t="n"/>
+      <c r="X45" s="48" t="n"/>
+      <c r="Y45" s="48" t="n"/>
+      <c r="Z45" s="48" t="n"/>
+      <c r="AA45" s="49" t="n"/>
       <c r="AB45" s="24" t="n"/>
-      <c r="AC45" s="54" t="n"/>
-      <c r="AD45" s="54" t="n"/>
-      <c r="AE45" s="55" t="n"/>
+      <c r="AC45" s="48" t="n"/>
+      <c r="AD45" s="48" t="n"/>
+      <c r="AE45" s="49" t="n"/>
       <c r="AF45" s="24" t="n"/>
-      <c r="AG45" s="54" t="n"/>
-      <c r="AH45" s="54" t="n"/>
-      <c r="AI45" s="54" t="n"/>
-      <c r="AJ45" s="55" t="n"/>
+      <c r="AG45" s="48" t="n"/>
+      <c r="AH45" s="48" t="n"/>
+      <c r="AI45" s="48" t="n"/>
+      <c r="AJ45" s="49" t="n"/>
       <c r="AK45" s="24" t="n"/>
-      <c r="AL45" s="54" t="n"/>
-      <c r="AM45" s="54" t="n"/>
-      <c r="AN45" s="55" t="n"/>
+      <c r="AL45" s="48" t="n"/>
+      <c r="AM45" s="48" t="n"/>
+      <c r="AN45" s="49" t="n"/>
       <c r="AO45" s="24" t="n"/>
-      <c r="AP45" s="65" t="n"/>
-      <c r="AQ45" s="55" t="n"/>
+      <c r="AP45" s="59" t="n"/>
+      <c r="AQ45" s="49" t="n"/>
       <c r="AR45" s="21" t="n"/>
       <c r="AS45" s="21" t="n"/>
-      <c r="AT45" s="55" t="n"/>
+      <c r="AT45" s="49" t="n"/>
       <c r="AU45" s="2" t="n"/>
     </row>
-    <row r="46" ht="46.5" customHeight="1">
+    <row r="46" hidden="1" ht="27.75" customHeight="1">
       <c r="A46" s="24" t="n"/>
-      <c r="B46" s="55" t="n"/>
+      <c r="B46" s="49" t="n"/>
       <c r="C46" s="24" t="n"/>
-      <c r="D46" s="54" t="n"/>
-      <c r="E46" s="54" t="n"/>
-      <c r="F46" s="55" t="n"/>
+      <c r="D46" s="48" t="n"/>
+      <c r="E46" s="48" t="n"/>
+      <c r="F46" s="49" t="n"/>
       <c r="G46" s="21" t="n"/>
-      <c r="H46" s="64" t="n"/>
-      <c r="I46" s="55" t="n"/>
+      <c r="H46" s="58" t="n"/>
+      <c r="I46" s="49" t="n"/>
       <c r="J46" s="21" t="n"/>
-      <c r="K46" s="55" t="n"/>
+      <c r="K46" s="49" t="n"/>
       <c r="L46" s="24" t="n"/>
-      <c r="M46" s="55" t="n"/>
+      <c r="M46" s="49" t="n"/>
       <c r="N46" s="24" t="n"/>
       <c r="O46" s="24" t="n"/>
       <c r="P46" s="24" t="n"/>
-      <c r="Q46" s="55" t="n"/>
+      <c r="Q46" s="49" t="n"/>
       <c r="R46" s="24" t="n"/>
-      <c r="S46" s="54" t="n"/>
-      <c r="T46" s="55" t="n"/>
+      <c r="S46" s="48" t="n"/>
+      <c r="T46" s="49" t="n"/>
       <c r="U46" s="24" t="n"/>
-      <c r="V46" s="55" t="n"/>
+      <c r="V46" s="49" t="n"/>
       <c r="W46" s="24" t="n"/>
-      <c r="X46" s="54" t="n"/>
-      <c r="Y46" s="54" t="n"/>
-      <c r="Z46" s="54" t="n"/>
-      <c r="AA46" s="55" t="n"/>
+      <c r="X46" s="48" t="n"/>
+      <c r="Y46" s="48" t="n"/>
+      <c r="Z46" s="48" t="n"/>
+      <c r="AA46" s="49" t="n"/>
       <c r="AB46" s="24" t="n"/>
-      <c r="AC46" s="54" t="n"/>
-      <c r="AD46" s="54" t="n"/>
-      <c r="AE46" s="55" t="n"/>
+      <c r="AC46" s="48" t="n"/>
+      <c r="AD46" s="48" t="n"/>
+      <c r="AE46" s="49" t="n"/>
       <c r="AF46" s="24" t="n"/>
-      <c r="AG46" s="54" t="n"/>
-      <c r="AH46" s="54" t="n"/>
-      <c r="AI46" s="54" t="n"/>
-      <c r="AJ46" s="55" t="n"/>
+      <c r="AG46" s="48" t="n"/>
+      <c r="AH46" s="48" t="n"/>
+      <c r="AI46" s="48" t="n"/>
+      <c r="AJ46" s="49" t="n"/>
       <c r="AK46" s="24" t="n"/>
-      <c r="AL46" s="54" t="n"/>
-      <c r="AM46" s="54" t="n"/>
-      <c r="AN46" s="55" t="n"/>
+      <c r="AL46" s="48" t="n"/>
+      <c r="AM46" s="48" t="n"/>
+      <c r="AN46" s="49" t="n"/>
       <c r="AO46" s="24" t="n"/>
-      <c r="AP46" s="65" t="n"/>
-      <c r="AQ46" s="55" t="n"/>
+      <c r="AP46" s="59" t="n"/>
+      <c r="AQ46" s="49" t="n"/>
       <c r="AR46" s="21" t="n"/>
       <c r="AS46" s="21" t="n"/>
-      <c r="AT46" s="55" t="n"/>
+      <c r="AT46" s="49" t="n"/>
       <c r="AU46" s="2" t="n"/>
     </row>
-    <row r="47" ht="27.75" customHeight="1">
+    <row r="47" hidden="1" ht="37.5" customHeight="1">
       <c r="A47" s="24" t="n"/>
-      <c r="B47" s="55" t="n"/>
+      <c r="B47" s="49" t="n"/>
       <c r="C47" s="24" t="n"/>
-      <c r="D47" s="54" t="n"/>
-      <c r="E47" s="54" t="n"/>
-      <c r="F47" s="55" t="n"/>
+      <c r="D47" s="48" t="n"/>
+      <c r="E47" s="48" t="n"/>
+      <c r="F47" s="49" t="n"/>
       <c r="G47" s="21" t="n"/>
-      <c r="H47" s="64" t="n"/>
-      <c r="I47" s="55" t="n"/>
+      <c r="H47" s="58" t="n"/>
+      <c r="I47" s="49" t="n"/>
       <c r="J47" s="21" t="n"/>
-      <c r="K47" s="55" t="n"/>
+      <c r="K47" s="49" t="n"/>
       <c r="L47" s="24" t="n"/>
-      <c r="M47" s="55" t="n"/>
+      <c r="M47" s="49" t="n"/>
       <c r="N47" s="24" t="n"/>
       <c r="O47" s="24" t="n"/>
       <c r="P47" s="24" t="n"/>
-      <c r="Q47" s="55" t="n"/>
+      <c r="Q47" s="49" t="n"/>
       <c r="R47" s="24" t="n"/>
-      <c r="S47" s="54" t="n"/>
-      <c r="T47" s="55" t="n"/>
+      <c r="S47" s="48" t="n"/>
+      <c r="T47" s="49" t="n"/>
       <c r="U47" s="24" t="n"/>
-      <c r="V47" s="55" t="n"/>
+      <c r="V47" s="49" t="n"/>
       <c r="W47" s="24" t="n"/>
-      <c r="X47" s="54" t="n"/>
-      <c r="Y47" s="54" t="n"/>
-      <c r="Z47" s="54" t="n"/>
-      <c r="AA47" s="55" t="n"/>
+      <c r="X47" s="48" t="n"/>
+      <c r="Y47" s="48" t="n"/>
+      <c r="Z47" s="48" t="n"/>
+      <c r="AA47" s="49" t="n"/>
       <c r="AB47" s="24" t="n"/>
-      <c r="AC47" s="54" t="n"/>
-      <c r="AD47" s="54" t="n"/>
-      <c r="AE47" s="55" t="n"/>
+      <c r="AC47" s="48" t="n"/>
+      <c r="AD47" s="48" t="n"/>
+      <c r="AE47" s="49" t="n"/>
       <c r="AF47" s="24" t="n"/>
-      <c r="AG47" s="54" t="n"/>
-      <c r="AH47" s="54" t="n"/>
-      <c r="AI47" s="54" t="n"/>
-      <c r="AJ47" s="55" t="n"/>
+      <c r="AG47" s="48" t="n"/>
+      <c r="AH47" s="48" t="n"/>
+      <c r="AI47" s="48" t="n"/>
+      <c r="AJ47" s="49" t="n"/>
       <c r="AK47" s="24" t="n"/>
-      <c r="AL47" s="54" t="n"/>
-      <c r="AM47" s="54" t="n"/>
-      <c r="AN47" s="55" t="n"/>
+      <c r="AL47" s="48" t="n"/>
+      <c r="AM47" s="48" t="n"/>
+      <c r="AN47" s="49" t="n"/>
       <c r="AO47" s="24" t="n"/>
-      <c r="AP47" s="65" t="n"/>
-      <c r="AQ47" s="55" t="n"/>
+      <c r="AP47" s="59" t="n"/>
+      <c r="AQ47" s="49" t="n"/>
       <c r="AR47" s="21" t="n"/>
       <c r="AS47" s="21" t="n"/>
-      <c r="AT47" s="55" t="n"/>
+      <c r="AT47" s="49" t="n"/>
       <c r="AU47" s="2" t="n"/>
     </row>
-    <row r="48" ht="37.5" customHeight="1">
+    <row r="48" hidden="1" ht="37.5" customHeight="1">
       <c r="A48" s="24" t="n"/>
-      <c r="B48" s="55" t="n"/>
+      <c r="B48" s="49" t="n"/>
       <c r="C48" s="24" t="n"/>
-      <c r="D48" s="54" t="n"/>
-      <c r="E48" s="54" t="n"/>
-      <c r="F48" s="55" t="n"/>
+      <c r="D48" s="48" t="n"/>
+      <c r="E48" s="48" t="n"/>
+      <c r="F48" s="49" t="n"/>
       <c r="G48" s="21" t="n"/>
-      <c r="H48" s="64" t="n"/>
-      <c r="I48" s="55" t="n"/>
+      <c r="H48" s="58" t="n"/>
+      <c r="I48" s="49" t="n"/>
       <c r="J48" s="21" t="n"/>
-      <c r="K48" s="55" t="n"/>
+      <c r="K48" s="49" t="n"/>
       <c r="L48" s="24" t="n"/>
-      <c r="M48" s="55" t="n"/>
+      <c r="M48" s="49" t="n"/>
       <c r="N48" s="24" t="n"/>
       <c r="O48" s="24" t="n"/>
       <c r="P48" s="24" t="n"/>
-      <c r="Q48" s="55" t="n"/>
+      <c r="Q48" s="49" t="n"/>
       <c r="R48" s="24" t="n"/>
-      <c r="S48" s="54" t="n"/>
-      <c r="T48" s="55" t="n"/>
+      <c r="S48" s="48" t="n"/>
+      <c r="T48" s="49" t="n"/>
       <c r="U48" s="24" t="n"/>
-      <c r="V48" s="55" t="n"/>
+      <c r="V48" s="49" t="n"/>
       <c r="W48" s="24" t="n"/>
-      <c r="X48" s="54" t="n"/>
-      <c r="Y48" s="54" t="n"/>
-      <c r="Z48" s="54" t="n"/>
-      <c r="AA48" s="55" t="n"/>
+      <c r="X48" s="48" t="n"/>
+      <c r="Y48" s="48" t="n"/>
+      <c r="Z48" s="48" t="n"/>
+      <c r="AA48" s="49" t="n"/>
       <c r="AB48" s="24" t="n"/>
-      <c r="AC48" s="54" t="n"/>
-      <c r="AD48" s="54" t="n"/>
-      <c r="AE48" s="55" t="n"/>
+      <c r="AC48" s="48" t="n"/>
+      <c r="AD48" s="48" t="n"/>
+      <c r="AE48" s="49" t="n"/>
       <c r="AF48" s="24" t="n"/>
-      <c r="AG48" s="54" t="n"/>
-      <c r="AH48" s="54" t="n"/>
-      <c r="AI48" s="54" t="n"/>
-      <c r="AJ48" s="55" t="n"/>
+      <c r="AG48" s="48" t="n"/>
+      <c r="AH48" s="48" t="n"/>
+      <c r="AI48" s="48" t="n"/>
+      <c r="AJ48" s="49" t="n"/>
       <c r="AK48" s="24" t="n"/>
-      <c r="AL48" s="54" t="n"/>
-      <c r="AM48" s="54" t="n"/>
-      <c r="AN48" s="55" t="n"/>
+      <c r="AL48" s="48" t="n"/>
+      <c r="AM48" s="48" t="n"/>
+      <c r="AN48" s="49" t="n"/>
       <c r="AO48" s="24" t="n"/>
-      <c r="AP48" s="65" t="n"/>
-      <c r="AQ48" s="55" t="n"/>
+      <c r="AP48" s="59" t="n"/>
+      <c r="AQ48" s="49" t="n"/>
       <c r="AR48" s="21" t="n"/>
       <c r="AS48" s="21" t="n"/>
-      <c r="AT48" s="55" t="n"/>
+      <c r="AT48" s="49" t="n"/>
       <c r="AU48" s="2" t="n"/>
     </row>
-    <row r="49" ht="37.5" customHeight="1">
+    <row r="49" hidden="1" ht="37.5" customHeight="1">
       <c r="A49" s="24" t="n"/>
-      <c r="B49" s="55" t="n"/>
+      <c r="B49" s="49" t="n"/>
       <c r="C49" s="24" t="n"/>
-      <c r="D49" s="54" t="n"/>
-      <c r="E49" s="54" t="n"/>
-      <c r="F49" s="55" t="n"/>
+      <c r="D49" s="48" t="n"/>
+      <c r="E49" s="48" t="n"/>
+      <c r="F49" s="49" t="n"/>
       <c r="G49" s="21" t="n"/>
-      <c r="H49" s="64" t="n"/>
-      <c r="I49" s="55" t="n"/>
+      <c r="H49" s="58" t="n"/>
+      <c r="I49" s="49" t="n"/>
       <c r="J49" s="21" t="n"/>
-      <c r="K49" s="55" t="n"/>
+      <c r="K49" s="49" t="n"/>
       <c r="L49" s="24" t="n"/>
-      <c r="M49" s="55" t="n"/>
+      <c r="M49" s="49" t="n"/>
       <c r="N49" s="24" t="n"/>
       <c r="O49" s="24" t="n"/>
       <c r="P49" s="24" t="n"/>
-      <c r="Q49" s="55" t="n"/>
+      <c r="Q49" s="49" t="n"/>
       <c r="R49" s="24" t="n"/>
-      <c r="S49" s="54" t="n"/>
-      <c r="T49" s="55" t="n"/>
+      <c r="S49" s="48" t="n"/>
+      <c r="T49" s="49" t="n"/>
       <c r="U49" s="24" t="n"/>
-      <c r="V49" s="55" t="n"/>
+      <c r="V49" s="49" t="n"/>
       <c r="W49" s="24" t="n"/>
-      <c r="X49" s="54" t="n"/>
-      <c r="Y49" s="54" t="n"/>
-      <c r="Z49" s="54" t="n"/>
-      <c r="AA49" s="55" t="n"/>
+      <c r="X49" s="48" t="n"/>
+      <c r="Y49" s="48" t="n"/>
+      <c r="Z49" s="48" t="n"/>
+      <c r="AA49" s="49" t="n"/>
       <c r="AB49" s="24" t="n"/>
-      <c r="AC49" s="54" t="n"/>
-      <c r="AD49" s="54" t="n"/>
-      <c r="AE49" s="55" t="n"/>
+      <c r="AC49" s="48" t="n"/>
+      <c r="AD49" s="48" t="n"/>
+      <c r="AE49" s="49" t="n"/>
       <c r="AF49" s="24" t="n"/>
-      <c r="AG49" s="54" t="n"/>
-      <c r="AH49" s="54" t="n"/>
-      <c r="AI49" s="54" t="n"/>
-      <c r="AJ49" s="55" t="n"/>
+      <c r="AG49" s="48" t="n"/>
+      <c r="AH49" s="48" t="n"/>
+      <c r="AI49" s="48" t="n"/>
+      <c r="AJ49" s="49" t="n"/>
       <c r="AK49" s="24" t="n"/>
-      <c r="AL49" s="54" t="n"/>
-      <c r="AM49" s="54" t="n"/>
-      <c r="AN49" s="55" t="n"/>
+      <c r="AL49" s="48" t="n"/>
+      <c r="AM49" s="48" t="n"/>
+      <c r="AN49" s="49" t="n"/>
       <c r="AO49" s="24" t="n"/>
-      <c r="AP49" s="65" t="n"/>
-      <c r="AQ49" s="55" t="n"/>
+      <c r="AP49" s="59" t="n"/>
+      <c r="AQ49" s="49" t="n"/>
       <c r="AR49" s="21" t="n"/>
       <c r="AS49" s="21" t="n"/>
-      <c r="AT49" s="55" t="n"/>
+      <c r="AT49" s="49" t="n"/>
       <c r="AU49" s="2" t="n"/>
     </row>
-    <row r="50" ht="37.5" customHeight="1">
+    <row r="50" hidden="1" ht="27.75" customHeight="1">
       <c r="A50" s="24" t="n"/>
-      <c r="B50" s="55" t="n"/>
+      <c r="B50" s="49" t="n"/>
       <c r="C50" s="24" t="n"/>
-      <c r="D50" s="54" t="n"/>
-      <c r="E50" s="54" t="n"/>
-      <c r="F50" s="55" t="n"/>
+      <c r="D50" s="48" t="n"/>
+      <c r="E50" s="48" t="n"/>
+      <c r="F50" s="49" t="n"/>
       <c r="G50" s="21" t="n"/>
-      <c r="H50" s="64" t="n"/>
-      <c r="I50" s="55" t="n"/>
+      <c r="H50" s="58" t="n"/>
+      <c r="I50" s="49" t="n"/>
       <c r="J50" s="21" t="n"/>
-      <c r="K50" s="55" t="n"/>
+      <c r="K50" s="49" t="n"/>
       <c r="L50" s="24" t="n"/>
-      <c r="M50" s="55" t="n"/>
+      <c r="M50" s="49" t="n"/>
       <c r="N50" s="24" t="n"/>
       <c r="O50" s="24" t="n"/>
       <c r="P50" s="24" t="n"/>
-      <c r="Q50" s="55" t="n"/>
+      <c r="Q50" s="49" t="n"/>
       <c r="R50" s="24" t="n"/>
-      <c r="S50" s="54" t="n"/>
-      <c r="T50" s="55" t="n"/>
+      <c r="S50" s="48" t="n"/>
+      <c r="T50" s="49" t="n"/>
       <c r="U50" s="24" t="n"/>
-      <c r="V50" s="55" t="n"/>
+      <c r="V50" s="49" t="n"/>
       <c r="W50" s="24" t="n"/>
-      <c r="X50" s="54" t="n"/>
-      <c r="Y50" s="54" t="n"/>
-      <c r="Z50" s="54" t="n"/>
-      <c r="AA50" s="55" t="n"/>
+      <c r="X50" s="48" t="n"/>
+      <c r="Y50" s="48" t="n"/>
+      <c r="Z50" s="48" t="n"/>
+      <c r="AA50" s="49" t="n"/>
       <c r="AB50" s="24" t="n"/>
-      <c r="AC50" s="54" t="n"/>
-      <c r="AD50" s="54" t="n"/>
-      <c r="AE50" s="55" t="n"/>
+      <c r="AC50" s="48" t="n"/>
+      <c r="AD50" s="48" t="n"/>
+      <c r="AE50" s="49" t="n"/>
       <c r="AF50" s="24" t="n"/>
-      <c r="AG50" s="54" t="n"/>
-      <c r="AH50" s="54" t="n"/>
-      <c r="AI50" s="54" t="n"/>
-      <c r="AJ50" s="55" t="n"/>
+      <c r="AG50" s="48" t="n"/>
+      <c r="AH50" s="48" t="n"/>
+      <c r="AI50" s="48" t="n"/>
+      <c r="AJ50" s="49" t="n"/>
       <c r="AK50" s="24" t="n"/>
-      <c r="AL50" s="54" t="n"/>
-      <c r="AM50" s="54" t="n"/>
-      <c r="AN50" s="55" t="n"/>
+      <c r="AL50" s="48" t="n"/>
+      <c r="AM50" s="48" t="n"/>
+      <c r="AN50" s="49" t="n"/>
       <c r="AO50" s="24" t="n"/>
-      <c r="AP50" s="65" t="n"/>
-      <c r="AQ50" s="55" t="n"/>
+      <c r="AP50" s="59" t="n"/>
+      <c r="AQ50" s="49" t="n"/>
       <c r="AR50" s="21" t="n"/>
       <c r="AS50" s="21" t="n"/>
-      <c r="AT50" s="55" t="n"/>
+      <c r="AT50" s="49" t="n"/>
       <c r="AU50" s="2" t="n"/>
     </row>
-    <row r="51" ht="27.75" customHeight="1">
+    <row r="51" hidden="1" ht="37.5" customHeight="1">
       <c r="A51" s="24" t="n"/>
-      <c r="B51" s="55" t="n"/>
+      <c r="B51" s="49" t="n"/>
       <c r="C51" s="24" t="n"/>
-      <c r="D51" s="54" t="n"/>
-      <c r="E51" s="54" t="n"/>
-      <c r="F51" s="55" t="n"/>
+      <c r="D51" s="48" t="n"/>
+      <c r="E51" s="48" t="n"/>
+      <c r="F51" s="49" t="n"/>
       <c r="G51" s="21" t="n"/>
-      <c r="H51" s="64" t="n"/>
-      <c r="I51" s="55" t="n"/>
+      <c r="H51" s="58" t="n"/>
+      <c r="I51" s="49" t="n"/>
       <c r="J51" s="21" t="n"/>
-      <c r="K51" s="55" t="n"/>
+      <c r="K51" s="49" t="n"/>
       <c r="L51" s="24" t="n"/>
-      <c r="M51" s="55" t="n"/>
+      <c r="M51" s="49" t="n"/>
       <c r="N51" s="24" t="n"/>
       <c r="O51" s="24" t="n"/>
       <c r="P51" s="24" t="n"/>
-      <c r="Q51" s="55" t="n"/>
+      <c r="Q51" s="49" t="n"/>
       <c r="R51" s="24" t="n"/>
-      <c r="S51" s="54" t="n"/>
-      <c r="T51" s="55" t="n"/>
+      <c r="S51" s="48" t="n"/>
+      <c r="T51" s="49" t="n"/>
       <c r="U51" s="24" t="n"/>
-      <c r="V51" s="55" t="n"/>
+      <c r="V51" s="49" t="n"/>
       <c r="W51" s="24" t="n"/>
-      <c r="X51" s="54" t="n"/>
-      <c r="Y51" s="54" t="n"/>
-      <c r="Z51" s="54" t="n"/>
-      <c r="AA51" s="55" t="n"/>
+      <c r="X51" s="48" t="n"/>
+      <c r="Y51" s="48" t="n"/>
+      <c r="Z51" s="48" t="n"/>
+      <c r="AA51" s="49" t="n"/>
       <c r="AB51" s="24" t="n"/>
-      <c r="AC51" s="54" t="n"/>
-      <c r="AD51" s="54" t="n"/>
-      <c r="AE51" s="55" t="n"/>
+      <c r="AC51" s="48" t="n"/>
+      <c r="AD51" s="48" t="n"/>
+      <c r="AE51" s="49" t="n"/>
       <c r="AF51" s="24" t="n"/>
-      <c r="AG51" s="54" t="n"/>
-      <c r="AH51" s="54" t="n"/>
-      <c r="AI51" s="54" t="n"/>
-      <c r="AJ51" s="55" t="n"/>
+      <c r="AG51" s="48" t="n"/>
+      <c r="AH51" s="48" t="n"/>
+      <c r="AI51" s="48" t="n"/>
+      <c r="AJ51" s="49" t="n"/>
       <c r="AK51" s="24" t="n"/>
-      <c r="AL51" s="54" t="n"/>
-      <c r="AM51" s="54" t="n"/>
-      <c r="AN51" s="55" t="n"/>
+      <c r="AL51" s="48" t="n"/>
+      <c r="AM51" s="48" t="n"/>
+      <c r="AN51" s="49" t="n"/>
       <c r="AO51" s="24" t="n"/>
-      <c r="AP51" s="65" t="n"/>
-      <c r="AQ51" s="55" t="n"/>
+      <c r="AP51" s="59" t="n"/>
+      <c r="AQ51" s="49" t="n"/>
       <c r="AR51" s="21" t="n"/>
       <c r="AS51" s="21" t="n"/>
-      <c r="AT51" s="55" t="n"/>
+      <c r="AT51" s="49" t="n"/>
       <c r="AU51" s="2" t="n"/>
     </row>
-    <row r="52" ht="37.5" customHeight="1">
+    <row r="52" hidden="1" ht="27.75" customHeight="1">
       <c r="A52" s="24" t="n"/>
-      <c r="B52" s="55" t="n"/>
+      <c r="B52" s="49" t="n"/>
       <c r="C52" s="24" t="n"/>
-      <c r="D52" s="54" t="n"/>
-      <c r="E52" s="54" t="n"/>
-      <c r="F52" s="55" t="n"/>
+      <c r="D52" s="48" t="n"/>
+      <c r="E52" s="48" t="n"/>
+      <c r="F52" s="49" t="n"/>
       <c r="G52" s="21" t="n"/>
-      <c r="H52" s="64" t="n"/>
-      <c r="I52" s="55" t="n"/>
+      <c r="H52" s="58" t="n"/>
+      <c r="I52" s="49" t="n"/>
       <c r="J52" s="21" t="n"/>
-      <c r="K52" s="55" t="n"/>
+      <c r="K52" s="49" t="n"/>
       <c r="L52" s="24" t="n"/>
-      <c r="M52" s="55" t="n"/>
+      <c r="M52" s="49" t="n"/>
       <c r="N52" s="24" t="n"/>
       <c r="O52" s="24" t="n"/>
       <c r="P52" s="24" t="n"/>
-      <c r="Q52" s="55" t="n"/>
+      <c r="Q52" s="49" t="n"/>
       <c r="R52" s="24" t="n"/>
-      <c r="S52" s="54" t="n"/>
-      <c r="T52" s="55" t="n"/>
+      <c r="S52" s="48" t="n"/>
+      <c r="T52" s="49" t="n"/>
       <c r="U52" s="24" t="n"/>
-      <c r="V52" s="55" t="n"/>
+      <c r="V52" s="49" t="n"/>
       <c r="W52" s="24" t="n"/>
-      <c r="X52" s="54" t="n"/>
-      <c r="Y52" s="54" t="n"/>
-      <c r="Z52" s="54" t="n"/>
-      <c r="AA52" s="55" t="n"/>
+      <c r="X52" s="48" t="n"/>
+      <c r="Y52" s="48" t="n"/>
+      <c r="Z52" s="48" t="n"/>
+      <c r="AA52" s="49" t="n"/>
       <c r="AB52" s="24" t="n"/>
-      <c r="AC52" s="54" t="n"/>
-      <c r="AD52" s="54" t="n"/>
-      <c r="AE52" s="55" t="n"/>
+      <c r="AC52" s="48" t="n"/>
+      <c r="AD52" s="48" t="n"/>
+      <c r="AE52" s="49" t="n"/>
       <c r="AF52" s="24" t="n"/>
-      <c r="AG52" s="54" t="n"/>
-      <c r="AH52" s="54" t="n"/>
-      <c r="AI52" s="54" t="n"/>
-      <c r="AJ52" s="55" t="n"/>
+      <c r="AG52" s="48" t="n"/>
+      <c r="AH52" s="48" t="n"/>
+      <c r="AI52" s="48" t="n"/>
+      <c r="AJ52" s="49" t="n"/>
       <c r="AK52" s="24" t="n"/>
-      <c r="AL52" s="54" t="n"/>
-      <c r="AM52" s="54" t="n"/>
-      <c r="AN52" s="55" t="n"/>
+      <c r="AL52" s="48" t="n"/>
+      <c r="AM52" s="48" t="n"/>
+      <c r="AN52" s="49" t="n"/>
       <c r="AO52" s="24" t="n"/>
-      <c r="AP52" s="65" t="n"/>
-      <c r="AQ52" s="55" t="n"/>
+      <c r="AP52" s="59" t="n"/>
+      <c r="AQ52" s="49" t="n"/>
       <c r="AR52" s="21" t="n"/>
       <c r="AS52" s="21" t="n"/>
-      <c r="AT52" s="55" t="n"/>
+      <c r="AT52" s="49" t="n"/>
       <c r="AU52" s="2" t="n"/>
     </row>
-    <row r="53" ht="27.75" customHeight="1">
+    <row r="53" hidden="1" ht="27.75" customHeight="1">
       <c r="A53" s="24" t="n"/>
-      <c r="B53" s="55" t="n"/>
+      <c r="B53" s="49" t="n"/>
       <c r="C53" s="24" t="n"/>
-      <c r="D53" s="54" t="n"/>
-      <c r="E53" s="54" t="n"/>
-      <c r="F53" s="55" t="n"/>
+      <c r="D53" s="48" t="n"/>
+      <c r="E53" s="48" t="n"/>
+      <c r="F53" s="49" t="n"/>
       <c r="G53" s="21" t="n"/>
-      <c r="H53" s="64" t="n"/>
-      <c r="I53" s="55" t="n"/>
+      <c r="H53" s="58" t="n"/>
+      <c r="I53" s="49" t="n"/>
       <c r="J53" s="21" t="n"/>
-      <c r="K53" s="55" t="n"/>
+      <c r="K53" s="49" t="n"/>
       <c r="L53" s="24" t="n"/>
-      <c r="M53" s="55" t="n"/>
+      <c r="M53" s="49" t="n"/>
       <c r="N53" s="24" t="n"/>
       <c r="O53" s="24" t="n"/>
       <c r="P53" s="24" t="n"/>
-      <c r="Q53" s="55" t="n"/>
+      <c r="Q53" s="49" t="n"/>
       <c r="R53" s="24" t="n"/>
-      <c r="S53" s="54" t="n"/>
-      <c r="T53" s="55" t="n"/>
+      <c r="S53" s="48" t="n"/>
+      <c r="T53" s="49" t="n"/>
       <c r="U53" s="24" t="n"/>
-      <c r="V53" s="55" t="n"/>
+      <c r="V53" s="49" t="n"/>
       <c r="W53" s="24" t="n"/>
-      <c r="X53" s="54" t="n"/>
-      <c r="Y53" s="54" t="n"/>
-      <c r="Z53" s="54" t="n"/>
-      <c r="AA53" s="55" t="n"/>
+      <c r="X53" s="48" t="n"/>
+      <c r="Y53" s="48" t="n"/>
+      <c r="Z53" s="48" t="n"/>
+      <c r="AA53" s="49" t="n"/>
       <c r="AB53" s="24" t="n"/>
-      <c r="AC53" s="54" t="n"/>
-      <c r="AD53" s="54" t="n"/>
-      <c r="AE53" s="55" t="n"/>
+      <c r="AC53" s="48" t="n"/>
+      <c r="AD53" s="48" t="n"/>
+      <c r="AE53" s="49" t="n"/>
       <c r="AF53" s="24" t="n"/>
-      <c r="AG53" s="54" t="n"/>
-      <c r="AH53" s="54" t="n"/>
-      <c r="AI53" s="54" t="n"/>
-      <c r="AJ53" s="55" t="n"/>
+      <c r="AG53" s="48" t="n"/>
+      <c r="AH53" s="48" t="n"/>
+      <c r="AI53" s="48" t="n"/>
+      <c r="AJ53" s="49" t="n"/>
       <c r="AK53" s="24" t="n"/>
-      <c r="AL53" s="54" t="n"/>
-      <c r="AM53" s="54" t="n"/>
-      <c r="AN53" s="55" t="n"/>
+      <c r="AL53" s="48" t="n"/>
+      <c r="AM53" s="48" t="n"/>
+      <c r="AN53" s="49" t="n"/>
       <c r="AO53" s="24" t="n"/>
-      <c r="AP53" s="65" t="n"/>
-      <c r="AQ53" s="55" t="n"/>
+      <c r="AP53" s="59" t="n"/>
+      <c r="AQ53" s="49" t="n"/>
       <c r="AR53" s="21" t="n"/>
       <c r="AS53" s="21" t="n"/>
-      <c r="AT53" s="55" t="n"/>
+      <c r="AT53" s="49" t="n"/>
       <c r="AU53" s="2" t="n"/>
     </row>
-    <row r="54" ht="27.75" customHeight="1">
+    <row r="54" hidden="1" ht="27.75" customHeight="1">
       <c r="A54" s="24" t="n"/>
-      <c r="B54" s="55" t="n"/>
+      <c r="B54" s="49" t="n"/>
       <c r="C54" s="24" t="n"/>
-      <c r="D54" s="54" t="n"/>
-      <c r="E54" s="54" t="n"/>
-      <c r="F54" s="55" t="n"/>
+      <c r="D54" s="48" t="n"/>
+      <c r="E54" s="48" t="n"/>
+      <c r="F54" s="49" t="n"/>
       <c r="G54" s="21" t="n"/>
-      <c r="H54" s="64" t="n"/>
-      <c r="I54" s="55" t="n"/>
+      <c r="H54" s="58" t="n"/>
+      <c r="I54" s="49" t="n"/>
       <c r="J54" s="21" t="n"/>
-      <c r="K54" s="55" t="n"/>
+      <c r="K54" s="49" t="n"/>
       <c r="L54" s="24" t="n"/>
-      <c r="M54" s="55" t="n"/>
+      <c r="M54" s="49" t="n"/>
       <c r="N54" s="24" t="n"/>
       <c r="O54" s="24" t="n"/>
       <c r="P54" s="24" t="n"/>
-      <c r="Q54" s="55" t="n"/>
+      <c r="Q54" s="49" t="n"/>
       <c r="R54" s="24" t="n"/>
-      <c r="S54" s="54" t="n"/>
-      <c r="T54" s="55" t="n"/>
+      <c r="S54" s="48" t="n"/>
+      <c r="T54" s="49" t="n"/>
       <c r="U54" s="24" t="n"/>
-      <c r="V54" s="55" t="n"/>
+      <c r="V54" s="49" t="n"/>
       <c r="W54" s="24" t="n"/>
-      <c r="X54" s="54" t="n"/>
-      <c r="Y54" s="54" t="n"/>
-      <c r="Z54" s="54" t="n"/>
-      <c r="AA54" s="55" t="n"/>
+      <c r="X54" s="48" t="n"/>
+      <c r="Y54" s="48" t="n"/>
+      <c r="Z54" s="48" t="n"/>
+      <c r="AA54" s="49" t="n"/>
       <c r="AB54" s="24" t="n"/>
-      <c r="AC54" s="54" t="n"/>
-      <c r="AD54" s="54" t="n"/>
-      <c r="AE54" s="55" t="n"/>
+      <c r="AC54" s="48" t="n"/>
+      <c r="AD54" s="48" t="n"/>
+      <c r="AE54" s="49" t="n"/>
       <c r="AF54" s="24" t="n"/>
-      <c r="AG54" s="54" t="n"/>
-      <c r="AH54" s="54" t="n"/>
-      <c r="AI54" s="54" t="n"/>
-      <c r="AJ54" s="55" t="n"/>
+      <c r="AG54" s="48" t="n"/>
+      <c r="AH54" s="48" t="n"/>
+      <c r="AI54" s="48" t="n"/>
+      <c r="AJ54" s="49" t="n"/>
       <c r="AK54" s="24" t="n"/>
-      <c r="AL54" s="54" t="n"/>
-      <c r="AM54" s="54" t="n"/>
-      <c r="AN54" s="55" t="n"/>
+      <c r="AL54" s="48" t="n"/>
+      <c r="AM54" s="48" t="n"/>
+      <c r="AN54" s="49" t="n"/>
       <c r="AO54" s="24" t="n"/>
-      <c r="AP54" s="65" t="n"/>
-      <c r="AQ54" s="55" t="n"/>
+      <c r="AP54" s="59" t="n"/>
+      <c r="AQ54" s="49" t="n"/>
       <c r="AR54" s="21" t="n"/>
       <c r="AS54" s="21" t="n"/>
-      <c r="AT54" s="55" t="n"/>
+      <c r="AT54" s="49" t="n"/>
       <c r="AU54" s="2" t="n"/>
     </row>
-    <row r="55" ht="27.75" customHeight="1">
+    <row r="55" hidden="1" ht="37.5" customHeight="1">
       <c r="A55" s="24" t="n"/>
-      <c r="B55" s="55" t="n"/>
+      <c r="B55" s="49" t="n"/>
       <c r="C55" s="24" t="n"/>
-      <c r="D55" s="54" t="n"/>
-      <c r="E55" s="54" t="n"/>
-      <c r="F55" s="55" t="n"/>
+      <c r="D55" s="48" t="n"/>
+      <c r="E55" s="48" t="n"/>
+      <c r="F55" s="49" t="n"/>
       <c r="G55" s="21" t="n"/>
-      <c r="H55" s="64" t="n"/>
-      <c r="I55" s="55" t="n"/>
+      <c r="H55" s="58" t="n"/>
+      <c r="I55" s="49" t="n"/>
       <c r="J55" s="21" t="n"/>
-      <c r="K55" s="55" t="n"/>
+      <c r="K55" s="49" t="n"/>
       <c r="L55" s="24" t="n"/>
-      <c r="M55" s="55" t="n"/>
+      <c r="M55" s="49" t="n"/>
       <c r="N55" s="24" t="n"/>
       <c r="O55" s="24" t="n"/>
       <c r="P55" s="24" t="n"/>
-      <c r="Q55" s="55" t="n"/>
+      <c r="Q55" s="49" t="n"/>
       <c r="R55" s="24" t="n"/>
-      <c r="S55" s="54" t="n"/>
-      <c r="T55" s="55" t="n"/>
+      <c r="S55" s="48" t="n"/>
+      <c r="T55" s="49" t="n"/>
       <c r="U55" s="24" t="n"/>
-      <c r="V55" s="55" t="n"/>
+      <c r="V55" s="49" t="n"/>
       <c r="W55" s="24" t="n"/>
-      <c r="X55" s="54" t="n"/>
-      <c r="Y55" s="54" t="n"/>
-      <c r="Z55" s="54" t="n"/>
-      <c r="AA55" s="55" t="n"/>
+      <c r="X55" s="48" t="n"/>
+      <c r="Y55" s="48" t="n"/>
+      <c r="Z55" s="48" t="n"/>
+      <c r="AA55" s="49" t="n"/>
       <c r="AB55" s="24" t="n"/>
-      <c r="AC55" s="54" t="n"/>
-      <c r="AD55" s="54" t="n"/>
-      <c r="AE55" s="55" t="n"/>
+      <c r="AC55" s="48" t="n"/>
+      <c r="AD55" s="48" t="n"/>
+      <c r="AE55" s="49" t="n"/>
       <c r="AF55" s="24" t="n"/>
-      <c r="AG55" s="54" t="n"/>
-      <c r="AH55" s="54" t="n"/>
-      <c r="AI55" s="54" t="n"/>
-      <c r="AJ55" s="55" t="n"/>
+      <c r="AG55" s="48" t="n"/>
+      <c r="AH55" s="48" t="n"/>
+      <c r="AI55" s="48" t="n"/>
+      <c r="AJ55" s="49" t="n"/>
       <c r="AK55" s="24" t="n"/>
-      <c r="AL55" s="54" t="n"/>
-      <c r="AM55" s="54" t="n"/>
-      <c r="AN55" s="55" t="n"/>
+      <c r="AL55" s="48" t="n"/>
+      <c r="AM55" s="48" t="n"/>
+      <c r="AN55" s="49" t="n"/>
       <c r="AO55" s="24" t="n"/>
-      <c r="AP55" s="65" t="n"/>
-      <c r="AQ55" s="55" t="n"/>
+      <c r="AP55" s="59" t="n"/>
+      <c r="AQ55" s="49" t="n"/>
       <c r="AR55" s="21" t="n"/>
       <c r="AS55" s="21" t="n"/>
-      <c r="AT55" s="55" t="n"/>
+      <c r="AT55" s="49" t="n"/>
       <c r="AU55" s="2" t="n"/>
     </row>
-    <row r="56" ht="37.5" customHeight="1">
+    <row r="56" hidden="1" ht="27.75" customHeight="1">
       <c r="A56" s="24" t="n"/>
-      <c r="B56" s="55" t="n"/>
+      <c r="B56" s="49" t="n"/>
       <c r="C56" s="24" t="n"/>
-      <c r="D56" s="54" t="n"/>
-      <c r="E56" s="54" t="n"/>
-      <c r="F56" s="55" t="n"/>
+      <c r="D56" s="48" t="n"/>
+      <c r="E56" s="48" t="n"/>
+      <c r="F56" s="49" t="n"/>
       <c r="G56" s="21" t="n"/>
-      <c r="H56" s="64" t="n"/>
-      <c r="I56" s="55" t="n"/>
+      <c r="H56" s="58" t="n"/>
+      <c r="I56" s="49" t="n"/>
       <c r="J56" s="21" t="n"/>
-      <c r="K56" s="55" t="n"/>
+      <c r="K56" s="49" t="n"/>
       <c r="L56" s="24" t="n"/>
-      <c r="M56" s="55" t="n"/>
+      <c r="M56" s="49" t="n"/>
       <c r="N56" s="24" t="n"/>
       <c r="O56" s="24" t="n"/>
       <c r="P56" s="24" t="n"/>
-      <c r="Q56" s="55" t="n"/>
+      <c r="Q56" s="49" t="n"/>
       <c r="R56" s="24" t="n"/>
-      <c r="S56" s="54" t="n"/>
-      <c r="T56" s="55" t="n"/>
+      <c r="S56" s="48" t="n"/>
+      <c r="T56" s="49" t="n"/>
       <c r="U56" s="24" t="n"/>
-      <c r="V56" s="55" t="n"/>
+      <c r="V56" s="49" t="n"/>
       <c r="W56" s="24" t="n"/>
-      <c r="X56" s="54" t="n"/>
-      <c r="Y56" s="54" t="n"/>
-      <c r="Z56" s="54" t="n"/>
-      <c r="AA56" s="55" t="n"/>
+      <c r="X56" s="48" t="n"/>
+      <c r="Y56" s="48" t="n"/>
+      <c r="Z56" s="48" t="n"/>
+      <c r="AA56" s="49" t="n"/>
       <c r="AB56" s="24" t="n"/>
-      <c r="AC56" s="54" t="n"/>
-      <c r="AD56" s="54" t="n"/>
-      <c r="AE56" s="55" t="n"/>
+      <c r="AC56" s="48" t="n"/>
+      <c r="AD56" s="48" t="n"/>
+      <c r="AE56" s="49" t="n"/>
       <c r="AF56" s="24" t="n"/>
-      <c r="AG56" s="54" t="n"/>
-      <c r="AH56" s="54" t="n"/>
-      <c r="AI56" s="54" t="n"/>
-      <c r="AJ56" s="55" t="n"/>
+      <c r="AG56" s="48" t="n"/>
+      <c r="AH56" s="48" t="n"/>
+      <c r="AI56" s="48" t="n"/>
+      <c r="AJ56" s="49" t="n"/>
       <c r="AK56" s="24" t="n"/>
-      <c r="AL56" s="54" t="n"/>
-      <c r="AM56" s="54" t="n"/>
-      <c r="AN56" s="55" t="n"/>
+      <c r="AL56" s="48" t="n"/>
+      <c r="AM56" s="48" t="n"/>
+      <c r="AN56" s="49" t="n"/>
       <c r="AO56" s="24" t="n"/>
-      <c r="AP56" s="65" t="n"/>
-      <c r="AQ56" s="55" t="n"/>
+      <c r="AP56" s="59" t="n"/>
+      <c r="AQ56" s="49" t="n"/>
       <c r="AR56" s="21" t="n"/>
       <c r="AS56" s="21" t="n"/>
-      <c r="AT56" s="55" t="n"/>
+      <c r="AT56" s="49" t="n"/>
       <c r="AU56" s="2" t="n"/>
     </row>
-    <row r="57" ht="27.75" customHeight="1">
-      <c r="A57" s="24" t="n"/>
-      <c r="B57" s="55" t="n"/>
-      <c r="C57" s="24" t="n"/>
-      <c r="D57" s="54" t="n"/>
-      <c r="E57" s="54" t="n"/>
-      <c r="F57" s="55" t="n"/>
-      <c r="G57" s="21" t="n"/>
-      <c r="H57" s="64" t="n"/>
-      <c r="I57" s="55" t="n"/>
-      <c r="J57" s="21" t="n"/>
-      <c r="K57" s="55" t="n"/>
-      <c r="L57" s="24" t="n"/>
-      <c r="M57" s="55" t="n"/>
-      <c r="N57" s="24" t="n"/>
-      <c r="O57" s="24" t="n"/>
-      <c r="P57" s="24" t="n"/>
-      <c r="Q57" s="55" t="n"/>
-      <c r="R57" s="24" t="n"/>
-      <c r="S57" s="54" t="n"/>
-      <c r="T57" s="55" t="n"/>
-      <c r="U57" s="24" t="n"/>
-      <c r="V57" s="55" t="n"/>
-      <c r="W57" s="24" t="n"/>
-      <c r="X57" s="54" t="n"/>
-      <c r="Y57" s="54" t="n"/>
-      <c r="Z57" s="54" t="n"/>
-      <c r="AA57" s="55" t="n"/>
-      <c r="AB57" s="24" t="n"/>
-      <c r="AC57" s="54" t="n"/>
-      <c r="AD57" s="54" t="n"/>
-      <c r="AE57" s="55" t="n"/>
-      <c r="AF57" s="24" t="n"/>
-      <c r="AG57" s="54" t="n"/>
-      <c r="AH57" s="54" t="n"/>
-      <c r="AI57" s="54" t="n"/>
-      <c r="AJ57" s="55" t="n"/>
-      <c r="AK57" s="24" t="n"/>
-      <c r="AL57" s="54" t="n"/>
-      <c r="AM57" s="54" t="n"/>
-      <c r="AN57" s="55" t="n"/>
-      <c r="AO57" s="24" t="n"/>
-      <c r="AP57" s="65" t="n"/>
-      <c r="AQ57" s="55" t="n"/>
-      <c r="AR57" s="21" t="n"/>
-      <c r="AS57" s="21" t="n"/>
-      <c r="AT57" s="55" t="n"/>
+    <row r="57">
+      <c r="A57" s="26" t="inlineStr">
+        <is>
+          <t>List and Code of Indicators under REMARKS column</t>
+        </is>
+      </c>
+      <c r="T57" s="27" t="inlineStr"/>
+      <c r="V57" s="28" t="inlineStr"/>
+      <c r="AT57" s="2" t="n"/>
       <c r="AU57" s="2" t="n"/>
     </row>
-    <row r="58" ht="19.5" customHeight="1">
-      <c r="A58" s="66" t="n"/>
-      <c r="B58" s="55" t="n"/>
-      <c r="C58" s="24" t="inlineStr">
-        <is>
-          <t>&lt;=== TOTAL FEMALE</t>
-        </is>
-      </c>
-      <c r="D58" s="54" t="n"/>
-      <c r="E58" s="54" t="n"/>
-      <c r="F58" s="55" t="n"/>
-      <c r="G58" s="27" t="inlineStr"/>
-      <c r="H58" s="67" t="inlineStr"/>
-      <c r="I58" s="55" t="n"/>
-      <c r="J58" s="30" t="inlineStr"/>
-      <c r="K58" s="55" t="n"/>
-      <c r="L58" s="30" t="inlineStr"/>
-      <c r="M58" s="55" t="n"/>
-      <c r="N58" s="30" t="inlineStr"/>
-      <c r="O58" s="30" t="inlineStr"/>
-      <c r="P58" s="30" t="inlineStr"/>
-      <c r="Q58" s="55" t="n"/>
-      <c r="R58" s="30" t="inlineStr"/>
-      <c r="S58" s="54" t="n"/>
-      <c r="T58" s="55" t="n"/>
-      <c r="U58" s="30" t="inlineStr"/>
-      <c r="V58" s="55" t="n"/>
-      <c r="W58" s="30" t="inlineStr"/>
-      <c r="X58" s="54" t="n"/>
-      <c r="Y58" s="54" t="n"/>
-      <c r="Z58" s="54" t="n"/>
-      <c r="AA58" s="55" t="n"/>
-      <c r="AB58" s="30" t="inlineStr"/>
-      <c r="AC58" s="54" t="n"/>
-      <c r="AD58" s="54" t="n"/>
-      <c r="AE58" s="55" t="n"/>
-      <c r="AF58" s="30" t="inlineStr"/>
-      <c r="AG58" s="54" t="n"/>
-      <c r="AH58" s="54" t="n"/>
-      <c r="AI58" s="54" t="n"/>
-      <c r="AJ58" s="55" t="n"/>
-      <c r="AK58" s="27" t="inlineStr"/>
-      <c r="AL58" s="54" t="n"/>
-      <c r="AM58" s="54" t="n"/>
-      <c r="AN58" s="55" t="n"/>
-      <c r="AO58" s="27" t="inlineStr"/>
-      <c r="AP58" s="27" t="inlineStr"/>
-      <c r="AQ58" s="55" t="n"/>
-      <c r="AR58" s="27" t="inlineStr"/>
-      <c r="AS58" s="27" t="inlineStr"/>
-      <c r="AT58" s="55" t="n"/>
+    <row r="58">
+      <c r="A58" s="29" t="inlineStr">
+        <is>
+          <t>Indicator</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C58" s="49" t="n"/>
+      <c r="D58" s="29" t="inlineStr">
+        <is>
+          <t>Required Information</t>
+        </is>
+      </c>
+      <c r="E58" s="48" t="n"/>
+      <c r="F58" s="48" t="n"/>
+      <c r="G58" s="48" t="n"/>
+      <c r="H58" s="49" t="n"/>
+      <c r="I58" s="29" t="inlineStr">
+        <is>
+          <t>Indicator</t>
+        </is>
+      </c>
+      <c r="J58" s="48" t="n"/>
+      <c r="K58" s="48" t="n"/>
+      <c r="L58" s="49" t="n"/>
+      <c r="M58" s="19" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="N58" s="29" t="inlineStr">
+        <is>
+          <t>Required Information</t>
+        </is>
+      </c>
+      <c r="O58" s="48" t="n"/>
+      <c r="P58" s="48" t="n"/>
+      <c r="Q58" s="48" t="n"/>
+      <c r="R58" s="48" t="n"/>
+      <c r="S58" s="49" t="n"/>
+      <c r="V58" s="19" t="inlineStr">
+        <is>
+          <t>REGISTERED</t>
+        </is>
+      </c>
+      <c r="W58" s="49" t="n"/>
+      <c r="X58" s="19" t="inlineStr">
+        <is>
+          <t>BoSY</t>
+        </is>
+      </c>
+      <c r="Y58" s="48" t="n"/>
+      <c r="Z58" s="49" t="n"/>
+      <c r="AA58" s="19" t="inlineStr">
+        <is>
+          <t>EoSY</t>
+        </is>
+      </c>
+      <c r="AB58" s="49" t="n"/>
+      <c r="AC58" s="27" t="inlineStr"/>
+      <c r="AE58" s="31" t="inlineStr">
+        <is>
+          <t>Prepared by;</t>
+        </is>
+      </c>
+      <c r="AL58" s="27" t="inlineStr"/>
+      <c r="AN58" s="31" t="inlineStr">
+        <is>
+          <t>Certified Correct:</t>
+        </is>
+      </c>
+      <c r="AT58" s="2" t="n"/>
       <c r="AU58" s="2" t="n"/>
     </row>
-    <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="66" t="n"/>
-      <c r="B59" s="55" t="n"/>
-      <c r="C59" s="24" t="inlineStr">
-        <is>
-          <t>&lt;=== COMBINED</t>
-        </is>
-      </c>
-      <c r="D59" s="54" t="n"/>
-      <c r="E59" s="54" t="n"/>
-      <c r="F59" s="55" t="n"/>
-      <c r="G59" s="27" t="inlineStr"/>
-      <c r="H59" s="67" t="inlineStr"/>
-      <c r="I59" s="55" t="n"/>
-      <c r="J59" s="30" t="inlineStr"/>
-      <c r="K59" s="55" t="n"/>
-      <c r="L59" s="30" t="inlineStr"/>
-      <c r="M59" s="55" t="n"/>
-      <c r="N59" s="30" t="inlineStr"/>
-      <c r="O59" s="30" t="inlineStr"/>
-      <c r="P59" s="30" t="inlineStr"/>
-      <c r="Q59" s="55" t="n"/>
-      <c r="R59" s="30" t="inlineStr"/>
-      <c r="S59" s="54" t="n"/>
-      <c r="T59" s="55" t="n"/>
-      <c r="U59" s="30" t="inlineStr"/>
-      <c r="V59" s="55" t="n"/>
-      <c r="W59" s="30" t="inlineStr"/>
-      <c r="X59" s="54" t="n"/>
-      <c r="Y59" s="54" t="n"/>
-      <c r="Z59" s="54" t="n"/>
-      <c r="AA59" s="55" t="n"/>
-      <c r="AB59" s="30" t="inlineStr"/>
-      <c r="AC59" s="54" t="n"/>
-      <c r="AD59" s="54" t="n"/>
-      <c r="AE59" s="55" t="n"/>
-      <c r="AF59" s="30" t="inlineStr"/>
-      <c r="AG59" s="54" t="n"/>
-      <c r="AH59" s="54" t="n"/>
-      <c r="AI59" s="54" t="n"/>
-      <c r="AJ59" s="55" t="n"/>
-      <c r="AK59" s="27" t="inlineStr"/>
-      <c r="AL59" s="54" t="n"/>
-      <c r="AM59" s="54" t="n"/>
-      <c r="AN59" s="55" t="n"/>
-      <c r="AO59" s="27" t="inlineStr"/>
-      <c r="AP59" s="27" t="inlineStr"/>
-      <c r="AQ59" s="55" t="n"/>
-      <c r="AR59" s="27" t="inlineStr"/>
-      <c r="AS59" s="27" t="inlineStr"/>
-      <c r="AT59" s="55" t="n"/>
-      <c r="AU59" s="2" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="32" t="inlineStr">
-        <is>
-          <t>List and Code of Indicators under REMARKS column</t>
-        </is>
-      </c>
-      <c r="T60" s="33" t="inlineStr"/>
-      <c r="V60" s="34" t="inlineStr"/>
-      <c r="AT60" s="2" t="n"/>
-      <c r="AU60" s="2" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="35" t="inlineStr">
-        <is>
-          <t>Indicator</t>
-        </is>
-      </c>
-      <c r="B61" s="19" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C61" s="55" t="n"/>
-      <c r="D61" s="35" t="inlineStr">
-        <is>
-          <t>Required Information</t>
-        </is>
-      </c>
-      <c r="E61" s="54" t="n"/>
-      <c r="F61" s="54" t="n"/>
-      <c r="G61" s="54" t="n"/>
-      <c r="H61" s="55" t="n"/>
-      <c r="I61" s="35" t="inlineStr">
-        <is>
-          <t>Indicator</t>
-        </is>
-      </c>
-      <c r="J61" s="54" t="n"/>
-      <c r="K61" s="54" t="n"/>
-      <c r="L61" s="55" t="n"/>
-      <c r="M61" s="19" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="N61" s="35" t="inlineStr">
-        <is>
-          <t>Required Information</t>
-        </is>
-      </c>
-      <c r="O61" s="54" t="n"/>
-      <c r="P61" s="54" t="n"/>
-      <c r="Q61" s="54" t="n"/>
-      <c r="R61" s="54" t="n"/>
-      <c r="S61" s="55" t="n"/>
-      <c r="V61" s="19" t="inlineStr">
-        <is>
-          <t>REGISTERED</t>
-        </is>
-      </c>
-      <c r="W61" s="55" t="n"/>
-      <c r="X61" s="19" t="inlineStr">
-        <is>
-          <t>BoSY</t>
-        </is>
-      </c>
-      <c r="Y61" s="54" t="n"/>
-      <c r="Z61" s="55" t="n"/>
-      <c r="AA61" s="19" t="inlineStr">
-        <is>
-          <t>EoSY</t>
-        </is>
-      </c>
-      <c r="AB61" s="55" t="n"/>
-      <c r="AC61" s="33" t="inlineStr"/>
-      <c r="AE61" s="37" t="inlineStr">
-        <is>
-          <t>Prepared by;</t>
-        </is>
-      </c>
-      <c r="AL61" s="33" t="inlineStr"/>
-      <c r="AN61" s="37" t="inlineStr">
-        <is>
-          <t>Certified Correct:</t>
-        </is>
-      </c>
-      <c r="AT61" s="2" t="n"/>
-      <c r="AU61" s="2" t="n"/>
-    </row>
-    <row r="62" ht="13.5" customHeight="1">
-      <c r="A62" s="68" t="inlineStr">
+    <row r="59" ht="13.5" customHeight="1">
+      <c r="A59" s="60" t="inlineStr">
         <is>
           <t>Transfered Out
 Transfered In
@@ -5208,7 +5029,7 @@
 Late Enrollment</t>
         </is>
       </c>
-      <c r="B62" s="69" t="inlineStr">
+      <c r="B59" s="61" t="inlineStr">
         <is>
           <t>T/O
 T/I
@@ -5216,8 +5037,8 @@
 LE</t>
         </is>
       </c>
-      <c r="C62" s="56" t="n"/>
-      <c r="D62" s="68" t="inlineStr">
+      <c r="C59" s="50" t="n"/>
+      <c r="D59" s="60" t="inlineStr">
         <is>
           <t>Name of  Public (P) Private (PR) School  &amp; Effectivity Date
 Name of  Public (P) Private (PR) School  &amp; Effectivity Date
@@ -5225,11 +5046,11 @@
 Reason (Enrollment beyond 1st Friday of SY)</t>
         </is>
       </c>
-      <c r="E62" s="57" t="n"/>
-      <c r="F62" s="57" t="n"/>
-      <c r="G62" s="57" t="n"/>
-      <c r="H62" s="56" t="n"/>
-      <c r="I62" s="68" t="inlineStr">
+      <c r="E59" s="51" t="n"/>
+      <c r="F59" s="51" t="n"/>
+      <c r="G59" s="51" t="n"/>
+      <c r="H59" s="50" t="n"/>
+      <c r="I59" s="60" t="inlineStr">
         <is>
           <t>CCT Receipient
 Balik Aral
@@ -5237,10 +5058,10 @@
 Accelerated</t>
         </is>
       </c>
-      <c r="J62" s="57" t="n"/>
-      <c r="K62" s="57" t="n"/>
-      <c r="L62" s="56" t="n"/>
-      <c r="M62" s="69" t="inlineStr">
+      <c r="J59" s="51" t="n"/>
+      <c r="K59" s="51" t="n"/>
+      <c r="L59" s="50" t="n"/>
+      <c r="M59" s="61" t="inlineStr">
         <is>
           <t>CCT
 B/A
@@ -5248,7 +5069,7 @@
 ACL</t>
         </is>
       </c>
-      <c r="N62" s="68" t="inlineStr">
+      <c r="N59" s="60" t="inlineStr">
         <is>
           <t>CCT Control/reference number &amp; Effectivity Date
 Name of school last attended &amp; Year
@@ -5256,236 +5077,351 @@
 Specify Level &amp; Effectivity Data</t>
         </is>
       </c>
-      <c r="O62" s="57" t="n"/>
-      <c r="P62" s="57" t="n"/>
-      <c r="Q62" s="57" t="n"/>
-      <c r="R62" s="57" t="n"/>
-      <c r="S62" s="56" t="n"/>
+      <c r="O59" s="51" t="n"/>
+      <c r="P59" s="51" t="n"/>
+      <c r="Q59" s="51" t="n"/>
+      <c r="R59" s="51" t="n"/>
+      <c r="S59" s="50" t="n"/>
+      <c r="V59" s="19" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="W59" s="50" t="n"/>
+      <c r="X59" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y59" s="51" t="n"/>
+      <c r="Z59" s="50" t="n"/>
+      <c r="AA59" s="19" t="inlineStr"/>
+      <c r="AB59" s="50" t="n"/>
+      <c r="AE59" s="62" t="inlineStr">
+        <is>
+          <t>CRIS IVY GUMBAN CAMPANAN</t>
+        </is>
+      </c>
+      <c r="AN59" s="37" t="inlineStr">
+        <is>
+          <t>LOURDES ABELLA MONTEFRIO</t>
+        </is>
+      </c>
+      <c r="AT59" s="2" t="n"/>
+      <c r="AU59" s="2" t="n"/>
+    </row>
+    <row r="60" ht="0.75" customHeight="1">
+      <c r="A60" s="63" t="n"/>
+      <c r="B60" s="64" t="n"/>
+      <c r="C60" s="65" t="n"/>
+      <c r="D60" s="64" t="n"/>
+      <c r="H60" s="65" t="n"/>
+      <c r="I60" s="64" t="n"/>
+      <c r="L60" s="65" t="n"/>
+      <c r="M60" s="63" t="n"/>
+      <c r="N60" s="64" t="n"/>
+      <c r="S60" s="65" t="n"/>
+      <c r="V60" s="64" t="n"/>
+      <c r="W60" s="65" t="n"/>
+      <c r="X60" s="64" t="n"/>
+      <c r="Z60" s="65" t="n"/>
+      <c r="AA60" s="64" t="n"/>
+      <c r="AB60" s="65" t="n"/>
+      <c r="AN60" s="2" t="n"/>
+      <c r="AO60" s="2" t="n"/>
+      <c r="AP60" s="2" t="n"/>
+      <c r="AQ60" s="2" t="n"/>
+      <c r="AR60" s="2" t="n"/>
+      <c r="AS60" s="2" t="n"/>
+      <c r="AT60" s="2" t="n"/>
+      <c r="AU60" s="2" t="n"/>
+    </row>
+    <row r="61" ht="9.75" customHeight="1">
+      <c r="A61" s="63" t="n"/>
+      <c r="B61" s="64" t="n"/>
+      <c r="C61" s="65" t="n"/>
+      <c r="D61" s="64" t="n"/>
+      <c r="H61" s="65" t="n"/>
+      <c r="I61" s="64" t="n"/>
+      <c r="L61" s="65" t="n"/>
+      <c r="M61" s="63" t="n"/>
+      <c r="N61" s="64" t="n"/>
+      <c r="S61" s="65" t="n"/>
+      <c r="V61" s="54" t="n"/>
+      <c r="W61" s="55" t="n"/>
+      <c r="X61" s="54" t="n"/>
+      <c r="Y61" s="56" t="n"/>
+      <c r="Z61" s="55" t="n"/>
+      <c r="AA61" s="54" t="n"/>
+      <c r="AB61" s="55" t="n"/>
+      <c r="AE61" s="66" t="n"/>
+      <c r="AF61" s="66" t="n"/>
+      <c r="AG61" s="66" t="n"/>
+      <c r="AH61" s="66" t="n"/>
+      <c r="AI61" s="66" t="n"/>
+      <c r="AJ61" s="66" t="n"/>
+      <c r="AK61" s="66" t="n"/>
+      <c r="AN61" s="42" t="inlineStr">
+        <is>
+          <t>(Signature of School Head over Printed Name)</t>
+        </is>
+      </c>
+      <c r="AT61" s="2" t="n"/>
+      <c r="AU61" s="2" t="n"/>
+    </row>
+    <row r="62" ht="9.75" customHeight="1">
+      <c r="A62" s="63" t="n"/>
+      <c r="B62" s="64" t="n"/>
+      <c r="C62" s="65" t="n"/>
+      <c r="D62" s="64" t="n"/>
+      <c r="H62" s="65" t="n"/>
+      <c r="I62" s="64" t="n"/>
+      <c r="L62" s="65" t="n"/>
+      <c r="M62" s="63" t="n"/>
+      <c r="N62" s="64" t="n"/>
+      <c r="S62" s="65" t="n"/>
       <c r="V62" s="19" t="inlineStr">
         <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="W62" s="56" t="n"/>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="W62" s="50" t="n"/>
       <c r="X62" s="19" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y62" s="57" t="n"/>
-      <c r="Z62" s="56" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="Y62" s="51" t="n"/>
+      <c r="Z62" s="50" t="n"/>
       <c r="AA62" s="19" t="inlineStr"/>
-      <c r="AB62" s="56" t="n"/>
-      <c r="AE62" s="70" t="inlineStr">
-        <is>
-          <t>CRIS IVY GUMBAN CAMPANAN</t>
-        </is>
-      </c>
-      <c r="AN62" s="43" t="inlineStr">
-        <is>
-          <t>LOURDES ABELLA MONTEFRIO</t>
+      <c r="AB62" s="50" t="n"/>
+      <c r="AE62" s="42" t="inlineStr">
+        <is>
+          <t>(Signature of Adviser over Printed Name)</t>
         </is>
       </c>
       <c r="AT62" s="2" t="n"/>
       <c r="AU62" s="2" t="n"/>
     </row>
-    <row r="63" ht="0.75" customHeight="1">
-      <c r="A63" s="71" t="n"/>
-      <c r="B63" s="72" t="n"/>
-      <c r="C63" s="73" t="n"/>
-      <c r="D63" s="72" t="n"/>
-      <c r="H63" s="73" t="n"/>
-      <c r="I63" s="72" t="n"/>
-      <c r="L63" s="73" t="n"/>
-      <c r="M63" s="71" t="n"/>
-      <c r="N63" s="72" t="n"/>
-      <c r="S63" s="73" t="n"/>
-      <c r="V63" s="72" t="n"/>
-      <c r="W63" s="73" t="n"/>
-      <c r="X63" s="72" t="n"/>
-      <c r="Z63" s="73" t="n"/>
-      <c r="AA63" s="72" t="n"/>
-      <c r="AB63" s="73" t="n"/>
-      <c r="AN63" s="2" t="n"/>
-      <c r="AO63" s="2" t="n"/>
-      <c r="AP63" s="2" t="n"/>
-      <c r="AQ63" s="2" t="n"/>
-      <c r="AR63" s="2" t="n"/>
-      <c r="AS63" s="2" t="n"/>
+    <row r="63" ht="9.75" customHeight="1">
+      <c r="A63" s="63" t="n"/>
+      <c r="B63" s="64" t="n"/>
+      <c r="C63" s="65" t="n"/>
+      <c r="D63" s="64" t="n"/>
+      <c r="H63" s="65" t="n"/>
+      <c r="I63" s="64" t="n"/>
+      <c r="L63" s="65" t="n"/>
+      <c r="M63" s="63" t="n"/>
+      <c r="N63" s="64" t="n"/>
+      <c r="S63" s="65" t="n"/>
+      <c r="V63" s="54" t="n"/>
+      <c r="W63" s="55" t="n"/>
+      <c r="X63" s="54" t="n"/>
+      <c r="Y63" s="56" t="n"/>
+      <c r="Z63" s="55" t="n"/>
+      <c r="AA63" s="54" t="n"/>
+      <c r="AB63" s="55" t="n"/>
+      <c r="AN63" s="67" t="inlineStr">
+        <is>
+          <t>BoSY Date:</t>
+        </is>
+      </c>
+      <c r="AQ63" s="67" t="inlineStr">
+        <is>
+          <t>EoSY Date:</t>
+        </is>
+      </c>
       <c r="AT63" s="2" t="n"/>
       <c r="AU63" s="2" t="n"/>
     </row>
     <row r="64" ht="9.75" customHeight="1">
-      <c r="A64" s="71" t="n"/>
-      <c r="B64" s="72" t="n"/>
-      <c r="C64" s="73" t="n"/>
-      <c r="D64" s="72" t="n"/>
-      <c r="H64" s="73" t="n"/>
-      <c r="I64" s="72" t="n"/>
-      <c r="L64" s="73" t="n"/>
-      <c r="M64" s="71" t="n"/>
-      <c r="N64" s="72" t="n"/>
-      <c r="S64" s="73" t="n"/>
-      <c r="V64" s="60" t="n"/>
-      <c r="W64" s="61" t="n"/>
-      <c r="X64" s="60" t="n"/>
-      <c r="Y64" s="62" t="n"/>
-      <c r="Z64" s="61" t="n"/>
-      <c r="AA64" s="60" t="n"/>
-      <c r="AB64" s="61" t="n"/>
-      <c r="AE64" s="74" t="n"/>
-      <c r="AF64" s="74" t="n"/>
-      <c r="AG64" s="74" t="n"/>
-      <c r="AH64" s="74" t="n"/>
-      <c r="AI64" s="74" t="n"/>
-      <c r="AJ64" s="74" t="n"/>
-      <c r="AK64" s="74" t="n"/>
-      <c r="AN64" s="48" t="inlineStr">
-        <is>
-          <t>(Signature of School Head over Printed Name)</t>
-        </is>
-      </c>
+      <c r="A64" s="63" t="n"/>
+      <c r="B64" s="64" t="n"/>
+      <c r="C64" s="65" t="n"/>
+      <c r="D64" s="64" t="n"/>
+      <c r="H64" s="65" t="n"/>
+      <c r="I64" s="64" t="n"/>
+      <c r="L64" s="65" t="n"/>
+      <c r="M64" s="63" t="n"/>
+      <c r="N64" s="64" t="n"/>
+      <c r="S64" s="65" t="n"/>
+      <c r="V64" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="W64" s="50" t="n"/>
+      <c r="X64" s="19" t="n">
+        <v>51</v>
+      </c>
+      <c r="Y64" s="51" t="n"/>
+      <c r="Z64" s="50" t="n"/>
+      <c r="AA64" s="19" t="inlineStr"/>
+      <c r="AB64" s="50" t="n"/>
+      <c r="AE64" s="67" t="inlineStr">
+        <is>
+          <t>BoSY Date:</t>
+        </is>
+      </c>
+      <c r="AI64" s="67" t="inlineStr">
+        <is>
+          <t>EoSY Date:</t>
+        </is>
+      </c>
+      <c r="AN64" s="66" t="n"/>
+      <c r="AO64" s="66" t="n"/>
+      <c r="AP64" s="66" t="n"/>
+      <c r="AQ64" s="66" t="n"/>
+      <c r="AR64" s="66" t="n"/>
+      <c r="AS64" s="66" t="n"/>
       <c r="AT64" s="2" t="n"/>
       <c r="AU64" s="2" t="n"/>
     </row>
-    <row r="65" ht="9.75" customHeight="1">
-      <c r="A65" s="71" t="n"/>
-      <c r="B65" s="72" t="n"/>
-      <c r="C65" s="73" t="n"/>
-      <c r="D65" s="72" t="n"/>
-      <c r="H65" s="73" t="n"/>
-      <c r="I65" s="72" t="n"/>
-      <c r="L65" s="73" t="n"/>
-      <c r="M65" s="71" t="n"/>
-      <c r="N65" s="72" t="n"/>
-      <c r="S65" s="73" t="n"/>
-      <c r="V65" s="19" t="inlineStr">
-        <is>
-          <t>FEMALE</t>
-        </is>
-      </c>
-      <c r="W65" s="56" t="n"/>
-      <c r="X65" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y65" s="57" t="n"/>
-      <c r="Z65" s="56" t="n"/>
-      <c r="AA65" s="19" t="inlineStr"/>
-      <c r="AB65" s="56" t="n"/>
-      <c r="AE65" s="48" t="inlineStr">
-        <is>
-          <t>(Signature of Adviser over Printed Name)</t>
-        </is>
-      </c>
+    <row r="65">
+      <c r="A65" s="57" t="n"/>
+      <c r="B65" s="54" t="n"/>
+      <c r="C65" s="55" t="n"/>
+      <c r="D65" s="54" t="n"/>
+      <c r="E65" s="56" t="n"/>
+      <c r="F65" s="56" t="n"/>
+      <c r="G65" s="56" t="n"/>
+      <c r="H65" s="55" t="n"/>
+      <c r="I65" s="54" t="n"/>
+      <c r="J65" s="56" t="n"/>
+      <c r="K65" s="56" t="n"/>
+      <c r="L65" s="55" t="n"/>
+      <c r="M65" s="57" t="n"/>
+      <c r="N65" s="54" t="n"/>
+      <c r="O65" s="56" t="n"/>
+      <c r="P65" s="56" t="n"/>
+      <c r="Q65" s="56" t="n"/>
+      <c r="R65" s="56" t="n"/>
+      <c r="S65" s="55" t="n"/>
+      <c r="V65" s="54" t="n"/>
+      <c r="W65" s="55" t="n"/>
+      <c r="X65" s="54" t="n"/>
+      <c r="Y65" s="56" t="n"/>
+      <c r="Z65" s="55" t="n"/>
+      <c r="AA65" s="54" t="n"/>
+      <c r="AB65" s="55" t="n"/>
+      <c r="AE65" s="66" t="n"/>
+      <c r="AF65" s="66" t="n"/>
+      <c r="AG65" s="66" t="n"/>
+      <c r="AH65" s="66" t="n"/>
+      <c r="AI65" s="66" t="n"/>
+      <c r="AJ65" s="66" t="n"/>
+      <c r="AK65" s="66" t="n"/>
+      <c r="AN65" s="2" t="n"/>
+      <c r="AO65" s="2" t="n"/>
+      <c r="AP65" s="2" t="n"/>
+      <c r="AQ65" s="2" t="n"/>
+      <c r="AR65" s="2" t="n"/>
+      <c r="AS65" s="2" t="n"/>
       <c r="AT65" s="2" t="n"/>
       <c r="AU65" s="2" t="n"/>
     </row>
     <row r="66" ht="9.75" customHeight="1">
-      <c r="A66" s="71" t="n"/>
-      <c r="B66" s="72" t="n"/>
-      <c r="C66" s="73" t="n"/>
-      <c r="D66" s="72" t="n"/>
-      <c r="H66" s="73" t="n"/>
-      <c r="I66" s="72" t="n"/>
-      <c r="L66" s="73" t="n"/>
-      <c r="M66" s="71" t="n"/>
-      <c r="N66" s="72" t="n"/>
-      <c r="S66" s="73" t="n"/>
-      <c r="V66" s="60" t="n"/>
-      <c r="W66" s="61" t="n"/>
-      <c r="X66" s="60" t="n"/>
-      <c r="Y66" s="62" t="n"/>
-      <c r="Z66" s="61" t="n"/>
-      <c r="AA66" s="60" t="n"/>
-      <c r="AB66" s="61" t="n"/>
-      <c r="AN66" s="75" t="inlineStr">
-        <is>
-          <t>BoSY Date:</t>
-        </is>
-      </c>
-      <c r="AQ66" s="75" t="inlineStr">
-        <is>
-          <t>EoSY Date:</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="n"/>
+      <c r="F66" s="2" t="n"/>
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="n"/>
+      <c r="J66" s="2" t="n"/>
+      <c r="K66" s="2" t="n"/>
+      <c r="L66" s="2" t="n"/>
+      <c r="M66" s="2" t="n"/>
+      <c r="N66" s="2" t="n"/>
+      <c r="O66" s="2" t="n"/>
+      <c r="P66" s="2" t="n"/>
+      <c r="Q66" s="2" t="n"/>
+      <c r="R66" s="2" t="n"/>
+      <c r="S66" s="2" t="n"/>
+      <c r="T66" s="2" t="n"/>
+      <c r="U66" s="2" t="n"/>
+      <c r="V66" s="2" t="n"/>
+      <c r="W66" s="2" t="n"/>
+      <c r="X66" s="2" t="n"/>
+      <c r="Y66" s="2" t="n"/>
+      <c r="Z66" s="2" t="n"/>
+      <c r="AA66" s="2" t="n"/>
+      <c r="AB66" s="2" t="n"/>
+      <c r="AC66" s="2" t="n"/>
+      <c r="AD66" s="2" t="n"/>
+      <c r="AE66" s="2" t="n"/>
+      <c r="AF66" s="2" t="n"/>
+      <c r="AG66" s="2" t="n"/>
+      <c r="AH66" s="2" t="n"/>
+      <c r="AI66" s="2" t="n"/>
+      <c r="AJ66" s="2" t="n"/>
+      <c r="AK66" s="2" t="n"/>
+      <c r="AN66" s="2" t="n"/>
+      <c r="AO66" s="2" t="n"/>
+      <c r="AP66" s="2" t="n"/>
+      <c r="AQ66" s="2" t="n"/>
+      <c r="AR66" s="2" t="n"/>
+      <c r="AS66" s="2" t="n"/>
       <c r="AT66" s="2" t="n"/>
       <c r="AU66" s="2" t="n"/>
     </row>
     <row r="67" ht="9.75" customHeight="1">
-      <c r="A67" s="71" t="n"/>
-      <c r="B67" s="72" t="n"/>
-      <c r="C67" s="73" t="n"/>
-      <c r="D67" s="72" t="n"/>
-      <c r="H67" s="73" t="n"/>
-      <c r="I67" s="72" t="n"/>
-      <c r="L67" s="73" t="n"/>
-      <c r="M67" s="71" t="n"/>
-      <c r="N67" s="72" t="n"/>
-      <c r="S67" s="73" t="n"/>
-      <c r="V67" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="W67" s="56" t="n"/>
-      <c r="X67" s="19" t="n">
-        <v>51</v>
-      </c>
-      <c r="Y67" s="57" t="n"/>
-      <c r="Z67" s="56" t="n"/>
-      <c r="AA67" s="19" t="inlineStr"/>
-      <c r="AB67" s="56" t="n"/>
-      <c r="AE67" s="75" t="inlineStr">
-        <is>
-          <t>BoSY Date:</t>
-        </is>
-      </c>
-      <c r="AI67" s="75" t="inlineStr">
-        <is>
-          <t>EoSY Date:</t>
-        </is>
-      </c>
-      <c r="AN67" s="74" t="n"/>
-      <c r="AO67" s="74" t="n"/>
-      <c r="AP67" s="74" t="n"/>
-      <c r="AQ67" s="74" t="n"/>
-      <c r="AR67" s="74" t="n"/>
-      <c r="AS67" s="74" t="n"/>
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="n"/>
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="n"/>
+      <c r="J67" s="2" t="n"/>
+      <c r="K67" s="2" t="n"/>
+      <c r="L67" s="2" t="n"/>
+      <c r="M67" s="2" t="n"/>
+      <c r="N67" s="2" t="n"/>
+      <c r="O67" s="2" t="n"/>
+      <c r="P67" s="2" t="n"/>
+      <c r="Q67" s="2" t="n"/>
+      <c r="R67" s="2" t="n"/>
+      <c r="S67" s="2" t="n"/>
+      <c r="T67" s="2" t="n"/>
+      <c r="U67" s="2" t="n"/>
+      <c r="V67" s="2" t="n"/>
+      <c r="W67" s="2" t="n"/>
+      <c r="X67" s="2" t="n"/>
+      <c r="Y67" s="2" t="n"/>
+      <c r="Z67" s="2" t="n"/>
+      <c r="AA67" s="2" t="n"/>
+      <c r="AB67" s="2" t="n"/>
+      <c r="AC67" s="2" t="n"/>
+      <c r="AD67" s="2" t="n"/>
+      <c r="AE67" s="2" t="n"/>
+      <c r="AF67" s="2" t="n"/>
+      <c r="AG67" s="2" t="n"/>
+      <c r="AH67" s="2" t="n"/>
+      <c r="AI67" s="2" t="n"/>
+      <c r="AJ67" s="2" t="n"/>
+      <c r="AK67" s="2" t="n"/>
+      <c r="AN67" s="44" t="inlineStr">
+        <is>
+          <t>Generated thru LIS</t>
+        </is>
+      </c>
+      <c r="AO67" s="68" t="n"/>
+      <c r="AP67" s="68" t="n"/>
+      <c r="AQ67" s="68" t="n"/>
+      <c r="AR67" s="68" t="n"/>
+      <c r="AS67" s="68" t="n"/>
       <c r="AT67" s="2" t="n"/>
       <c r="AU67" s="2" t="n"/>
     </row>
-    <row r="68">
-      <c r="A68" s="63" t="n"/>
-      <c r="B68" s="60" t="n"/>
-      <c r="C68" s="61" t="n"/>
-      <c r="D68" s="60" t="n"/>
-      <c r="E68" s="62" t="n"/>
-      <c r="F68" s="62" t="n"/>
-      <c r="G68" s="62" t="n"/>
-      <c r="H68" s="61" t="n"/>
-      <c r="I68" s="60" t="n"/>
-      <c r="J68" s="62" t="n"/>
-      <c r="K68" s="62" t="n"/>
-      <c r="L68" s="61" t="n"/>
-      <c r="M68" s="63" t="n"/>
-      <c r="N68" s="60" t="n"/>
-      <c r="O68" s="62" t="n"/>
-      <c r="P68" s="62" t="n"/>
-      <c r="Q68" s="62" t="n"/>
-      <c r="R68" s="62" t="n"/>
-      <c r="S68" s="61" t="n"/>
-      <c r="V68" s="60" t="n"/>
-      <c r="W68" s="61" t="n"/>
-      <c r="X68" s="60" t="n"/>
-      <c r="Y68" s="62" t="n"/>
-      <c r="Z68" s="61" t="n"/>
-      <c r="AA68" s="60" t="n"/>
-      <c r="AB68" s="61" t="n"/>
-      <c r="AE68" s="74" t="n"/>
-      <c r="AF68" s="74" t="n"/>
-      <c r="AG68" s="74" t="n"/>
-      <c r="AH68" s="74" t="n"/>
-      <c r="AI68" s="74" t="n"/>
-      <c r="AJ68" s="74" t="n"/>
-      <c r="AK68" s="74" t="n"/>
+    <row r="68" ht="19.5" customHeight="1">
+      <c r="A68" s="46" t="inlineStr">
+        <is>
+          <t>Generated on: Monday, February 2, 2026</t>
+        </is>
+      </c>
+      <c r="AL68" s="2" t="n"/>
+      <c r="AM68" s="2" t="n"/>
       <c r="AN68" s="2" t="n"/>
       <c r="AO68" s="2" t="n"/>
       <c r="AP68" s="2" t="n"/>
@@ -5495,121 +5431,9 @@
       <c r="AT68" s="2" t="n"/>
       <c r="AU68" s="2" t="n"/>
     </row>
-    <row r="69" ht="9.75" customHeight="1">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="2" t="n"/>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="n"/>
-      <c r="G69" s="2" t="n"/>
-      <c r="H69" s="2" t="n"/>
-      <c r="I69" s="2" t="n"/>
-      <c r="J69" s="2" t="n"/>
-      <c r="K69" s="2" t="n"/>
-      <c r="L69" s="2" t="n"/>
-      <c r="M69" s="2" t="n"/>
-      <c r="N69" s="2" t="n"/>
-      <c r="O69" s="2" t="n"/>
-      <c r="P69" s="2" t="n"/>
-      <c r="Q69" s="2" t="n"/>
-      <c r="R69" s="2" t="n"/>
-      <c r="S69" s="2" t="n"/>
-      <c r="T69" s="2" t="n"/>
-      <c r="U69" s="2" t="n"/>
-      <c r="V69" s="2" t="n"/>
-      <c r="W69" s="2" t="n"/>
-      <c r="X69" s="2" t="n"/>
-      <c r="Y69" s="2" t="n"/>
-      <c r="Z69" s="2" t="n"/>
-      <c r="AA69" s="2" t="n"/>
-      <c r="AB69" s="2" t="n"/>
-      <c r="AC69" s="2" t="n"/>
-      <c r="AD69" s="2" t="n"/>
-      <c r="AE69" s="2" t="n"/>
-      <c r="AF69" s="2" t="n"/>
-      <c r="AG69" s="2" t="n"/>
-      <c r="AH69" s="2" t="n"/>
-      <c r="AI69" s="2" t="n"/>
-      <c r="AJ69" s="2" t="n"/>
-      <c r="AK69" s="2" t="n"/>
-      <c r="AN69" s="2" t="n"/>
-      <c r="AO69" s="2" t="n"/>
-      <c r="AP69" s="2" t="n"/>
-      <c r="AQ69" s="2" t="n"/>
-      <c r="AR69" s="2" t="n"/>
-      <c r="AS69" s="2" t="n"/>
-      <c r="AT69" s="2" t="n"/>
-      <c r="AU69" s="2" t="n"/>
-    </row>
-    <row r="70" ht="9.75" customHeight="1">
-      <c r="A70" s="2" t="n"/>
-      <c r="B70" s="2" t="n"/>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="n"/>
-      <c r="F70" s="2" t="n"/>
-      <c r="G70" s="2" t="n"/>
-      <c r="H70" s="2" t="n"/>
-      <c r="I70" s="2" t="n"/>
-      <c r="J70" s="2" t="n"/>
-      <c r="K70" s="2" t="n"/>
-      <c r="L70" s="2" t="n"/>
-      <c r="M70" s="2" t="n"/>
-      <c r="N70" s="2" t="n"/>
-      <c r="O70" s="2" t="n"/>
-      <c r="P70" s="2" t="n"/>
-      <c r="Q70" s="2" t="n"/>
-      <c r="R70" s="2" t="n"/>
-      <c r="S70" s="2" t="n"/>
-      <c r="T70" s="2" t="n"/>
-      <c r="U70" s="2" t="n"/>
-      <c r="V70" s="2" t="n"/>
-      <c r="W70" s="2" t="n"/>
-      <c r="X70" s="2" t="n"/>
-      <c r="Y70" s="2" t="n"/>
-      <c r="Z70" s="2" t="n"/>
-      <c r="AA70" s="2" t="n"/>
-      <c r="AB70" s="2" t="n"/>
-      <c r="AC70" s="2" t="n"/>
-      <c r="AD70" s="2" t="n"/>
-      <c r="AE70" s="2" t="n"/>
-      <c r="AF70" s="2" t="n"/>
-      <c r="AG70" s="2" t="n"/>
-      <c r="AH70" s="2" t="n"/>
-      <c r="AI70" s="2" t="n"/>
-      <c r="AJ70" s="2" t="n"/>
-      <c r="AK70" s="2" t="n"/>
-      <c r="AN70" s="50" t="inlineStr">
-        <is>
-          <t>Generated thru LIS</t>
-        </is>
-      </c>
-      <c r="AO70" s="76" t="n"/>
-      <c r="AP70" s="76" t="n"/>
-      <c r="AQ70" s="76" t="n"/>
-      <c r="AR70" s="76" t="n"/>
-      <c r="AS70" s="76" t="n"/>
-      <c r="AT70" s="2" t="n"/>
-      <c r="AU70" s="2" t="n"/>
-    </row>
-    <row r="71" ht="19.5" customHeight="1">
-      <c r="A71" s="52" t="inlineStr">
-        <is>
-          <t>Generated on: Monday, February 2, 2026</t>
-        </is>
-      </c>
-      <c r="AL71" s="2" t="n"/>
-      <c r="AM71" s="2" t="n"/>
-      <c r="AN71" s="2" t="n"/>
-      <c r="AO71" s="2" t="n"/>
-      <c r="AP71" s="2" t="n"/>
-      <c r="AQ71" s="2" t="n"/>
-      <c r="AR71" s="2" t="n"/>
-      <c r="AS71" s="2" t="n"/>
-      <c r="AT71" s="2" t="n"/>
-      <c r="AU71" s="2" t="n"/>
-    </row>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
     <row r="72" ht="12.75" customHeight="1"/>
     <row r="73" ht="12.75" customHeight="1"/>
     <row r="74" ht="12.75" customHeight="1"/>
@@ -6535,19 +6359,13 @@
     <row r="994" ht="12.75" customHeight="1"/>
     <row r="995" ht="12.75" customHeight="1"/>
     <row r="996" ht="12.75" customHeight="1"/>
-    <row r="997" ht="12.75" customHeight="1"/>
-    <row r="998" ht="12.75" customHeight="1"/>
-    <row r="999" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="818">
+  <mergeCells count="776">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="AS55:AT55"/>
     <mergeCell ref="W25:AA25"/>
-    <mergeCell ref="AB57:AE57"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="AS38:AT38"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="AP58:AQ58"/>
     <mergeCell ref="AP52:AQ52"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="J9:K9"/>
@@ -6555,12 +6373,14 @@
     <mergeCell ref="AB42:AE42"/>
     <mergeCell ref="P6:Q6"/>
     <mergeCell ref="AK42:AN42"/>
+    <mergeCell ref="AE64:AH65"/>
     <mergeCell ref="AF16:AJ16"/>
     <mergeCell ref="AK7:AN7"/>
     <mergeCell ref="H5:I6"/>
     <mergeCell ref="AF6:AJ6"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="J5:K6"/>
+    <mergeCell ref="T57:U65"/>
     <mergeCell ref="L29:M29"/>
     <mergeCell ref="AS8:AT8"/>
     <mergeCell ref="W16:AA16"/>
@@ -6574,6 +6394,7 @@
     <mergeCell ref="AB44:AE44"/>
     <mergeCell ref="W18:AA18"/>
     <mergeCell ref="A35:B35"/>
+    <mergeCell ref="X59:Z61"/>
     <mergeCell ref="AB31:AE31"/>
     <mergeCell ref="AP7:AQ7"/>
     <mergeCell ref="U20:V20"/>
@@ -6582,15 +6403,12 @@
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="AB39:AE39"/>
     <mergeCell ref="AK20:AN20"/>
-    <mergeCell ref="W57:AA57"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="U22:V22"/>
     <mergeCell ref="P26:Q26"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="AE62:AK63"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="L42:M42"/>
     <mergeCell ref="AS46:AT46"/>
@@ -6605,11 +6423,9 @@
     <mergeCell ref="J11:K11"/>
     <mergeCell ref="AS48:AT48"/>
     <mergeCell ref="AB50:AE50"/>
-    <mergeCell ref="M62:M68"/>
     <mergeCell ref="W12:AA12"/>
     <mergeCell ref="R9:T9"/>
     <mergeCell ref="H19:I19"/>
-    <mergeCell ref="U58:V58"/>
     <mergeCell ref="AK15:AN15"/>
     <mergeCell ref="P37:Q37"/>
     <mergeCell ref="U8:V8"/>
@@ -6621,7 +6437,6 @@
     <mergeCell ref="R13:T13"/>
     <mergeCell ref="AF47:AJ47"/>
     <mergeCell ref="AB12:AE12"/>
-    <mergeCell ref="AA62:AB64"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="P14:Q14"/>
     <mergeCell ref="H14:I14"/>
@@ -6629,7 +6444,6 @@
     <mergeCell ref="AK10:AN10"/>
     <mergeCell ref="AP13:AQ13"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="T60:U68"/>
     <mergeCell ref="R15:T15"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="H43:I43"/>
@@ -6638,28 +6452,27 @@
     <mergeCell ref="L47:M47"/>
     <mergeCell ref="AP8:AQ8"/>
     <mergeCell ref="AS9:AT9"/>
-    <mergeCell ref="V65:W66"/>
-    <mergeCell ref="X62:Z64"/>
     <mergeCell ref="AB55:AE55"/>
+    <mergeCell ref="D59:H65"/>
     <mergeCell ref="AP10:AQ10"/>
     <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="B62:C68"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="AK28:AN28"/>
     <mergeCell ref="C45:F45"/>
     <mergeCell ref="AF12:AJ12"/>
     <mergeCell ref="U21:V21"/>
     <mergeCell ref="R33:T33"/>
-    <mergeCell ref="L58:M58"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="J25:K25"/>
-    <mergeCell ref="AE65:AK66"/>
+    <mergeCell ref="AE58:AK58"/>
     <mergeCell ref="L50:M50"/>
     <mergeCell ref="L25:M25"/>
     <mergeCell ref="AK30:AN30"/>
     <mergeCell ref="AS23:AT23"/>
     <mergeCell ref="C47:F47"/>
+    <mergeCell ref="M59:M65"/>
     <mergeCell ref="AB25:AE25"/>
+    <mergeCell ref="D58:H58"/>
     <mergeCell ref="AF41:AJ41"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="W9:AA9"/>
@@ -6698,16 +6511,19 @@
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="AB15:AE15"/>
     <mergeCell ref="J55:K55"/>
+    <mergeCell ref="V62:W63"/>
     <mergeCell ref="AJ4:AL4"/>
     <mergeCell ref="L55:M55"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="AS17:AT17"/>
     <mergeCell ref="AS11:AT11"/>
     <mergeCell ref="C35:F35"/>
+    <mergeCell ref="V64:W65"/>
     <mergeCell ref="AK25:AN25"/>
     <mergeCell ref="AS19:AT19"/>
     <mergeCell ref="AF31:AJ31"/>
     <mergeCell ref="U54:V54"/>
+    <mergeCell ref="N59:S65"/>
     <mergeCell ref="AB5:AJ5"/>
     <mergeCell ref="AP16:AQ16"/>
     <mergeCell ref="U29:V29"/>
@@ -6717,7 +6533,6 @@
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="AF38:AJ38"/>
     <mergeCell ref="AK29:AN29"/>
-    <mergeCell ref="C59:F59"/>
     <mergeCell ref="H8:I8"/>
     <mergeCell ref="R7:T7"/>
     <mergeCell ref="J8:K8"/>
@@ -6737,27 +6552,27 @@
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="Q4:S4"/>
     <mergeCell ref="R36:T36"/>
+    <mergeCell ref="N58:S58"/>
+    <mergeCell ref="V58:W58"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="L53:M53"/>
     <mergeCell ref="AB10:AE10"/>
     <mergeCell ref="L28:M28"/>
-    <mergeCell ref="AF57:AJ57"/>
     <mergeCell ref="H39:I39"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="P59:Q59"/>
     <mergeCell ref="AK32:AN32"/>
     <mergeCell ref="AP29:AQ29"/>
     <mergeCell ref="P46:Q46"/>
     <mergeCell ref="T3:AF3"/>
+    <mergeCell ref="A68:AK68"/>
     <mergeCell ref="AS40:AT40"/>
     <mergeCell ref="AP44:AQ44"/>
-    <mergeCell ref="U57:V57"/>
     <mergeCell ref="AP31:AQ31"/>
     <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="AK57:AN57"/>
     <mergeCell ref="C54:F54"/>
     <mergeCell ref="U42:V42"/>
     <mergeCell ref="C41:F41"/>
+    <mergeCell ref="AE59:AK61"/>
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="L21:M21"/>
     <mergeCell ref="P43:Q43"/>
@@ -6768,6 +6583,7 @@
     <mergeCell ref="J23:K23"/>
     <mergeCell ref="AF28:AJ28"/>
     <mergeCell ref="R49:T49"/>
+    <mergeCell ref="AN61:AS62"/>
     <mergeCell ref="AK16:AN16"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="R24:T24"/>
@@ -6778,9 +6594,7 @@
     <mergeCell ref="W34:AA34"/>
     <mergeCell ref="AS20:AT20"/>
     <mergeCell ref="H54:I54"/>
-    <mergeCell ref="AI67:AK68"/>
     <mergeCell ref="A45:B45"/>
-    <mergeCell ref="N61:S61"/>
     <mergeCell ref="H41:I41"/>
     <mergeCell ref="R26:T26"/>
     <mergeCell ref="AP42:AQ42"/>
@@ -6794,7 +6608,6 @@
     <mergeCell ref="J34:K34"/>
     <mergeCell ref="AB18:AE18"/>
     <mergeCell ref="H56:I56"/>
-    <mergeCell ref="AN62:AS62"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="H49:I49"/>
     <mergeCell ref="AP19:AQ19"/>
@@ -6805,28 +6618,25 @@
     <mergeCell ref="P36:Q36"/>
     <mergeCell ref="J49:K49"/>
     <mergeCell ref="J36:K36"/>
-    <mergeCell ref="A62:A68"/>
+    <mergeCell ref="A59:A65"/>
     <mergeCell ref="L30:M30"/>
     <mergeCell ref="U47:V47"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="W31:AA31"/>
     <mergeCell ref="AK47:AN47"/>
     <mergeCell ref="R52:T52"/>
-    <mergeCell ref="AF58:AJ58"/>
     <mergeCell ref="R39:T39"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="L44:M44"/>
     <mergeCell ref="AK38:AN38"/>
     <mergeCell ref="AK21:AN21"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="X61:Z61"/>
     <mergeCell ref="AP32:AQ32"/>
     <mergeCell ref="AS33:AT33"/>
     <mergeCell ref="U50:V50"/>
     <mergeCell ref="U44:V44"/>
     <mergeCell ref="AF18:AJ18"/>
     <mergeCell ref="AK50:AN50"/>
-    <mergeCell ref="V61:W61"/>
     <mergeCell ref="AP47:AQ47"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="AF34:AJ34"/>
@@ -6839,9 +6649,8 @@
     <mergeCell ref="AF49:AJ49"/>
     <mergeCell ref="H31:I31"/>
     <mergeCell ref="AK37:AN37"/>
-    <mergeCell ref="C57:F57"/>
-    <mergeCell ref="H58:I58"/>
     <mergeCell ref="U45:V45"/>
+    <mergeCell ref="B58:C58"/>
     <mergeCell ref="W26:AA26"/>
     <mergeCell ref="J24:K24"/>
     <mergeCell ref="AF29:AJ29"/>
@@ -6850,25 +6659,17 @@
     <mergeCell ref="AB49:AE49"/>
     <mergeCell ref="L18:M18"/>
     <mergeCell ref="AM4:AU4"/>
-    <mergeCell ref="AS59:AT59"/>
-    <mergeCell ref="AQ66:AS67"/>
     <mergeCell ref="AB24:AE24"/>
     <mergeCell ref="AK53:AN53"/>
-    <mergeCell ref="AA67:AB68"/>
     <mergeCell ref="AF44:AJ44"/>
     <mergeCell ref="AP50:AQ50"/>
-    <mergeCell ref="C58:F58"/>
-    <mergeCell ref="AN70:AS70"/>
     <mergeCell ref="J26:K26"/>
-    <mergeCell ref="AN64:AS65"/>
     <mergeCell ref="L26:M26"/>
     <mergeCell ref="P17:Q17"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="AB32:AE32"/>
     <mergeCell ref="AB26:AE26"/>
-    <mergeCell ref="A57:B57"/>
     <mergeCell ref="A32:B32"/>
-    <mergeCell ref="H57:I57"/>
     <mergeCell ref="AP27:AQ27"/>
     <mergeCell ref="P19:Q19"/>
     <mergeCell ref="H22:I22"/>
@@ -6886,7 +6687,6 @@
     <mergeCell ref="J42:K42"/>
     <mergeCell ref="W37:AA37"/>
     <mergeCell ref="J52:K52"/>
-    <mergeCell ref="AN66:AP67"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="J44:K44"/>
     <mergeCell ref="AB52:AE52"/>
@@ -6918,36 +6718,36 @@
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="A47:B47"/>
-    <mergeCell ref="R58:T58"/>
-    <mergeCell ref="AE62:AK64"/>
+    <mergeCell ref="X62:Z63"/>
     <mergeCell ref="AB40:AE40"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="R8:T8"/>
     <mergeCell ref="W27:AA27"/>
     <mergeCell ref="H47:I47"/>
     <mergeCell ref="J47:K47"/>
+    <mergeCell ref="X64:Z65"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="R10:T10"/>
     <mergeCell ref="L27:M27"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A57:S57"/>
     <mergeCell ref="AP53:AQ53"/>
     <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="AP57:AQ57"/>
     <mergeCell ref="AK8:AN8"/>
-    <mergeCell ref="AL61:AM70"/>
     <mergeCell ref="P22:Q22"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="AB33:AE33"/>
     <mergeCell ref="R42:T42"/>
+    <mergeCell ref="X58:Z58"/>
     <mergeCell ref="W55:AA55"/>
     <mergeCell ref="AK23:AN23"/>
     <mergeCell ref="J53:K53"/>
-    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="AN58:AS58"/>
     <mergeCell ref="U16:V16"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="J45:K45"/>
+    <mergeCell ref="V59:W61"/>
     <mergeCell ref="L45:M45"/>
     <mergeCell ref="R46:T46"/>
     <mergeCell ref="AB45:AE45"/>
@@ -6966,42 +6766,31 @@
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="H13:I13"/>
-    <mergeCell ref="AS57:AT57"/>
-    <mergeCell ref="AB59:AE59"/>
     <mergeCell ref="A1:AT1"/>
     <mergeCell ref="L40:M40"/>
     <mergeCell ref="AK51:AN51"/>
     <mergeCell ref="A53:B53"/>
-    <mergeCell ref="W58:AA58"/>
     <mergeCell ref="AB46:AE46"/>
-    <mergeCell ref="AC61:AD68"/>
     <mergeCell ref="W8:AA8"/>
     <mergeCell ref="P15:Q15"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="AP41:AQ41"/>
     <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="P58:Q58"/>
     <mergeCell ref="AB48:AE48"/>
-    <mergeCell ref="J58:K58"/>
     <mergeCell ref="AP56:AQ56"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="W53:AA53"/>
     <mergeCell ref="AP43:AQ43"/>
     <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="V62:W64"/>
     <mergeCell ref="U6:V6"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="AK6:AN6"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="H25:I25"/>
-    <mergeCell ref="AE67:AH68"/>
     <mergeCell ref="AS12:AT12"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="C30:F30"/>
-    <mergeCell ref="V60:AS60"/>
-    <mergeCell ref="A60:S60"/>
-    <mergeCell ref="I61:L61"/>
     <mergeCell ref="W46:AA46"/>
     <mergeCell ref="W21:AA21"/>
     <mergeCell ref="AS7:AT7"/>
@@ -7010,6 +6799,7 @@
     <mergeCell ref="P28:Q28"/>
     <mergeCell ref="U18:V18"/>
     <mergeCell ref="H28:I28"/>
+    <mergeCell ref="V57:AS57"/>
     <mergeCell ref="AP5:AQ6"/>
     <mergeCell ref="AK24:AN24"/>
     <mergeCell ref="AF8:AJ8"/>
@@ -7019,17 +6809,14 @@
     <mergeCell ref="AB36:AE36"/>
     <mergeCell ref="P30:Q30"/>
     <mergeCell ref="J46:K46"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="AE61:AK61"/>
     <mergeCell ref="L46:M46"/>
     <mergeCell ref="AK26:AN26"/>
-    <mergeCell ref="D62:H68"/>
+    <mergeCell ref="AQ63:AS64"/>
     <mergeCell ref="R31:T31"/>
     <mergeCell ref="U19:V19"/>
     <mergeCell ref="J48:K48"/>
     <mergeCell ref="R6:T6"/>
     <mergeCell ref="L48:M48"/>
-    <mergeCell ref="AS58:AT58"/>
     <mergeCell ref="W10:AA10"/>
     <mergeCell ref="AF39:AJ39"/>
     <mergeCell ref="AP24:AQ24"/>
@@ -7042,6 +6829,7 @@
     <mergeCell ref="AP51:AQ51"/>
     <mergeCell ref="AP26:AQ26"/>
     <mergeCell ref="C34:F34"/>
+    <mergeCell ref="AA64:AB65"/>
     <mergeCell ref="P49:Q49"/>
     <mergeCell ref="U37:V37"/>
     <mergeCell ref="AB51:AE51"/>
@@ -7068,6 +6856,7 @@
     <mergeCell ref="R44:T44"/>
     <mergeCell ref="R19:T19"/>
     <mergeCell ref="AF50:AJ50"/>
+    <mergeCell ref="AA59:AB61"/>
     <mergeCell ref="L11:M11"/>
     <mergeCell ref="W29:AA29"/>
     <mergeCell ref="AS15:AT15"/>
@@ -7083,6 +6872,7 @@
     <mergeCell ref="P54:Q54"/>
     <mergeCell ref="AP12:AQ12"/>
     <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="AI64:AK65"/>
     <mergeCell ref="H29:I29"/>
     <mergeCell ref="W6:AA6"/>
     <mergeCell ref="A2:AT2"/>
@@ -7098,15 +6888,17 @@
     <mergeCell ref="C49:F49"/>
     <mergeCell ref="R32:T32"/>
     <mergeCell ref="W51:AA51"/>
+    <mergeCell ref="B59:C65"/>
     <mergeCell ref="U25:V25"/>
     <mergeCell ref="AB6:AE6"/>
     <mergeCell ref="C42:F42"/>
     <mergeCell ref="AF9:AJ9"/>
+    <mergeCell ref="AL58:AM67"/>
     <mergeCell ref="AF45:AJ45"/>
     <mergeCell ref="L51:M51"/>
+    <mergeCell ref="AN63:AP64"/>
     <mergeCell ref="AF55:AJ55"/>
     <mergeCell ref="AF11:AJ11"/>
-    <mergeCell ref="P57:Q57"/>
     <mergeCell ref="C55:F55"/>
     <mergeCell ref="W42:AA42"/>
     <mergeCell ref="AS28:AT28"/>
@@ -7131,7 +6923,6 @@
     <mergeCell ref="H53:I53"/>
     <mergeCell ref="AK22:AN22"/>
     <mergeCell ref="U40:V40"/>
-    <mergeCell ref="AK59:AN59"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="AB17:AE17"/>
     <mergeCell ref="AK46:AN46"/>
@@ -7139,7 +6930,6 @@
     <mergeCell ref="U15:V15"/>
     <mergeCell ref="AF37:AJ37"/>
     <mergeCell ref="AK40:AN40"/>
-    <mergeCell ref="A71:AK71"/>
     <mergeCell ref="J19:K19"/>
     <mergeCell ref="AF24:AJ24"/>
     <mergeCell ref="R45:T45"/>
@@ -7150,16 +6940,16 @@
     <mergeCell ref="R20:T20"/>
     <mergeCell ref="AP9:AQ9"/>
     <mergeCell ref="AB19:AE19"/>
-    <mergeCell ref="AA65:AB66"/>
+    <mergeCell ref="AA58:AB58"/>
+    <mergeCell ref="AA62:AB63"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="L12:M12"/>
+    <mergeCell ref="AC58:AD65"/>
     <mergeCell ref="R47:T47"/>
     <mergeCell ref="AP20:AQ20"/>
     <mergeCell ref="A41:B41"/>
-    <mergeCell ref="X67:Z68"/>
     <mergeCell ref="R22:T22"/>
-    <mergeCell ref="AB58:AE58"/>
     <mergeCell ref="L39:M39"/>
     <mergeCell ref="L14:M14"/>
     <mergeCell ref="A27:B27"/>
@@ -7170,6 +6960,7 @@
     <mergeCell ref="AP22:AQ22"/>
     <mergeCell ref="P39:Q39"/>
     <mergeCell ref="AB14:AE14"/>
+    <mergeCell ref="I59:L65"/>
     <mergeCell ref="H45:I45"/>
     <mergeCell ref="AP15:AQ15"/>
     <mergeCell ref="AS16:AT16"/>
@@ -7183,6 +6974,7 @@
     <mergeCell ref="C50:F50"/>
     <mergeCell ref="AF17:AJ17"/>
     <mergeCell ref="R38:T38"/>
+    <mergeCell ref="I58:L58"/>
     <mergeCell ref="AS34:AT34"/>
     <mergeCell ref="AK35:AN35"/>
     <mergeCell ref="AF19:AJ19"/>
@@ -7203,7 +6995,6 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="AF48:AJ48"/>
     <mergeCell ref="AB7:AE7"/>
-    <mergeCell ref="U59:V59"/>
     <mergeCell ref="AS29:AT29"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="AP33:AQ33"/>
@@ -7234,8 +7025,6 @@
     <mergeCell ref="L20:M20"/>
     <mergeCell ref="AP30:AQ30"/>
     <mergeCell ref="U43:V43"/>
-    <mergeCell ref="AP59:AQ59"/>
-    <mergeCell ref="V67:W68"/>
     <mergeCell ref="P5:AA5"/>
     <mergeCell ref="AP46:AQ46"/>
     <mergeCell ref="J22:K22"/>
@@ -7254,7 +7043,6 @@
     <mergeCell ref="R37:T37"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="W40:AA40"/>
-    <mergeCell ref="I62:L68"/>
     <mergeCell ref="R12:T12"/>
     <mergeCell ref="U49:V49"/>
     <mergeCell ref="W33:AA33"/>
@@ -7265,12 +7053,12 @@
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="AK36:AN36"/>
     <mergeCell ref="R54:T54"/>
+    <mergeCell ref="AN59:AS59"/>
     <mergeCell ref="C53:F53"/>
     <mergeCell ref="R41:T41"/>
     <mergeCell ref="W35:AA35"/>
     <mergeCell ref="L33:M33"/>
     <mergeCell ref="R56:T56"/>
-    <mergeCell ref="AN61:AS61"/>
     <mergeCell ref="L8:M8"/>
     <mergeCell ref="R43:T43"/>
     <mergeCell ref="A12:B12"/>
@@ -7283,19 +7071,16 @@
     <mergeCell ref="AB41:AE41"/>
     <mergeCell ref="L10:M10"/>
     <mergeCell ref="AB35:AE35"/>
-    <mergeCell ref="W59:AA59"/>
     <mergeCell ref="AF51:AJ51"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="AP49:AQ49"/>
     <mergeCell ref="AK39:AN39"/>
-    <mergeCell ref="X65:Z66"/>
     <mergeCell ref="AS32:AT32"/>
     <mergeCell ref="AP36:AQ36"/>
     <mergeCell ref="AS37:AT37"/>
     <mergeCell ref="P53:Q53"/>
     <mergeCell ref="AS47:AT47"/>
     <mergeCell ref="A43:B43"/>
-    <mergeCell ref="R59:T59"/>
     <mergeCell ref="U51:V51"/>
     <mergeCell ref="C46:F46"/>
     <mergeCell ref="C21:F21"/>
@@ -7303,13 +7088,11 @@
     <mergeCell ref="C48:F48"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="AF33:AJ33"/>
-    <mergeCell ref="N62:S68"/>
     <mergeCell ref="AB34:AE34"/>
     <mergeCell ref="AB28:AE28"/>
     <mergeCell ref="AS50:AT50"/>
     <mergeCell ref="AP54:AQ54"/>
     <mergeCell ref="J30:K30"/>
-    <mergeCell ref="H59:I59"/>
     <mergeCell ref="U17:V17"/>
     <mergeCell ref="P21:Q21"/>
     <mergeCell ref="A25:B25"/>
@@ -7322,23 +7105,21 @@
     <mergeCell ref="L23:M23"/>
     <mergeCell ref="W41:AA41"/>
     <mergeCell ref="AS27:AT27"/>
-    <mergeCell ref="D61:H61"/>
     <mergeCell ref="AB29:AE29"/>
     <mergeCell ref="P23:Q23"/>
     <mergeCell ref="AK19:AN19"/>
     <mergeCell ref="W56:AA56"/>
+    <mergeCell ref="AN67:AS67"/>
     <mergeCell ref="W43:AA43"/>
     <mergeCell ref="P16:Q16"/>
     <mergeCell ref="J54:K54"/>
     <mergeCell ref="R18:T18"/>
     <mergeCell ref="L54:M54"/>
-    <mergeCell ref="AF59:AJ59"/>
     <mergeCell ref="J41:K41"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="L41:M41"/>
     <mergeCell ref="U52:V52"/>
     <mergeCell ref="H27:I27"/>
-    <mergeCell ref="AK58:AN58"/>
     <mergeCell ref="U39:V39"/>
     <mergeCell ref="P18:Q18"/>
     <mergeCell ref="J56:K56"/>
@@ -7348,14 +7129,12 @@
     <mergeCell ref="L34:M34"/>
     <mergeCell ref="J43:K43"/>
     <mergeCell ref="L56:M56"/>
-    <mergeCell ref="R57:T57"/>
     <mergeCell ref="AB56:AE56"/>
     <mergeCell ref="AB43:AE43"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="L49:M49"/>
     <mergeCell ref="AS53:AT53"/>
     <mergeCell ref="C11:F11"/>
-    <mergeCell ref="AA61:AB61"/>
     <mergeCell ref="L36:M36"/>
     <mergeCell ref="C5:F6"/>
   </mergeCells>
